--- a/data/processed/sam_auto_dashboard_2025_Q1/sam_occ_segment_major_totals_2030.xlsx
+++ b/data/processed/sam_auto_dashboard_2025_Q1/sam_occ_segment_major_totals_2030.xlsx
@@ -5454,13 +5454,13 @@
         <v>72</v>
       </c>
       <c r="I56">
-        <v>458634.7950781548</v>
+        <v>460030.357203405</v>
       </c>
       <c r="J56">
-        <v>458634.7950781548</v>
+        <v>460030.357203405</v>
       </c>
       <c r="K56">
-        <v>718900.4815054857</v>
+        <v>719739.9291816649</v>
       </c>
       <c r="L56">
         <v>0.5</v>
@@ -5469,7 +5469,7 @@
         <v>0.5</v>
       </c>
       <c r="N56">
-        <v>0.04228699871457732</v>
+        <v>0.04229743857594604</v>
       </c>
       <c r="O56" t="s">
         <v>90</v>
@@ -5484,7 +5484,7 @@
         <v>105</v>
       </c>
       <c r="S56">
-        <v>57131.31705880688</v>
+        <v>57135.57023865626</v>
       </c>
       <c r="T56">
         <v>684650</v>
@@ -5493,7 +5493,7 @@
         <v>66882.7</v>
       </c>
       <c r="V56">
-        <v>47131.69089229908</v>
+        <v>47277.51170296894</v>
       </c>
       <c r="W56">
         <v>458122.0572615974</v>
@@ -5502,16 +5502,16 @@
         <v>717160</v>
       </c>
       <c r="Y56">
-        <v>512.7378165574046</v>
+        <v>1908.299941807636</v>
       </c>
       <c r="Z56">
-        <v>1740.481505485717</v>
+        <v>2579.929181664949</v>
       </c>
       <c r="AA56">
-        <v>0.001119216611446893</v>
+        <v>0.00416548365563188</v>
       </c>
       <c r="AB56">
-        <v>0.002426908228966642</v>
+        <v>0.003597424816867853</v>
       </c>
     </row>
     <row r="57" spans="1:28">
@@ -5540,22 +5540,22 @@
         <v>73</v>
       </c>
       <c r="I57">
-        <v>28646.65486576431</v>
+        <v>28739.17020520304</v>
       </c>
       <c r="J57">
-        <v>28646.65486576431</v>
+        <v>28739.17020520304</v>
       </c>
       <c r="K57">
-        <v>53536.52466742366</v>
+        <v>53521.14107534428</v>
       </c>
       <c r="L57">
-        <v>0.03123035492856872</v>
+        <v>0.03123616708679059</v>
       </c>
       <c r="M57">
         <v>0.03092595537399445</v>
       </c>
       <c r="N57">
-        <v>0.01200942505303073</v>
+        <v>0.01200595579994197</v>
       </c>
       <c r="O57" t="s">
         <v>91</v>
@@ -5570,7 +5570,7 @@
         <v>106</v>
       </c>
       <c r="S57">
-        <v>125239.0776585259</v>
+        <v>125240.4107053371</v>
       </c>
       <c r="T57">
         <v>48080</v>
@@ -5579,7 +5579,7 @@
         <v>7123.1</v>
       </c>
       <c r="V57">
-        <v>2209.718756862254</v>
+        <v>2216.854893669824</v>
       </c>
       <c r="W57">
         <v>28335.72459742938</v>
@@ -5588,16 +5588,16 @@
         <v>52655.43570125593</v>
       </c>
       <c r="Y57">
-        <v>310.9302683349306</v>
+        <v>403.4456077736577</v>
       </c>
       <c r="Z57">
-        <v>881.0889661677284</v>
+        <v>865.7053740883421</v>
       </c>
       <c r="AA57">
-        <v>0.01097308336922283</v>
+        <v>0.0142380550878963</v>
       </c>
       <c r="AB57">
-        <v>0.01673310560312604</v>
+        <v>0.01644094978151882</v>
       </c>
     </row>
     <row r="58" spans="1:28">
@@ -5626,22 +5626,22 @@
         <v>74</v>
       </c>
       <c r="I58">
-        <v>17966.15139245693</v>
+        <v>18029.44811709052</v>
       </c>
       <c r="J58">
-        <v>17966.15139245693</v>
+        <v>18029.44811709052</v>
       </c>
       <c r="K58">
-        <v>37456.7972833494</v>
+        <v>37424.1216029953</v>
       </c>
       <c r="L58">
-        <v>0.01958655512540797</v>
+        <v>0.01959593300178525</v>
       </c>
       <c r="M58">
         <v>0.01916168784421483</v>
       </c>
       <c r="N58">
-        <v>0.004988164980981555</v>
+        <v>0.004990504023802541</v>
       </c>
       <c r="O58" t="s">
         <v>91</v>
@@ -5656,7 +5656,7 @@
         <v>106</v>
       </c>
       <c r="S58">
-        <v>81337.05174509587</v>
+        <v>81336.75207339901</v>
       </c>
       <c r="T58">
         <v>31580</v>
@@ -5665,7 +5665,7 @@
         <v>6576.299999999999</v>
       </c>
       <c r="V58">
-        <v>1553.069562127998</v>
+        <v>1558.615463674763</v>
       </c>
       <c r="W58">
         <v>17556.78371159248</v>
@@ -5674,16 +5674,16 @@
         <v>36480.28109703345</v>
       </c>
       <c r="Y58">
-        <v>409.367680864445</v>
+        <v>472.6644054980388</v>
       </c>
       <c r="Z58">
-        <v>976.5161863159447</v>
+        <v>943.8405059618453</v>
       </c>
       <c r="AA58">
-        <v>0.02331678099982205</v>
+        <v>0.02692203841333111</v>
       </c>
       <c r="AB58">
-        <v>0.02676832954544734</v>
+        <v>0.02587262152534778</v>
       </c>
     </row>
     <row r="59" spans="1:28">
@@ -5712,22 +5712,22 @@
         <v>75</v>
       </c>
       <c r="I59">
-        <v>5081.387138157875</v>
+        <v>5096.750304091261</v>
       </c>
       <c r="J59">
-        <v>5081.387138157875</v>
+        <v>5096.750304091261</v>
       </c>
       <c r="K59">
-        <v>18824.05758736182</v>
+        <v>18714.16961804023</v>
       </c>
       <c r="L59">
-        <v>0.005539687778477393</v>
+        <v>0.005539580404079403</v>
       </c>
       <c r="M59">
         <v>0.005340537590381067</v>
       </c>
       <c r="N59">
-        <v>0.003428379789378008</v>
+        <v>0.003429164038666276</v>
       </c>
       <c r="O59" t="s">
         <v>91</v>
@@ -5742,7 +5742,7 @@
         <v>106</v>
       </c>
       <c r="S59">
-        <v>110501.7978344178</v>
+        <v>110491.0188552152</v>
       </c>
       <c r="T59">
         <v>12510</v>
@@ -5751,7 +5751,7 @@
         <v>2050</v>
       </c>
       <c r="V59">
-        <v>309.804729005831</v>
+        <v>310.7334840745106</v>
       </c>
       <c r="W59">
         <v>4893.236135576537</v>
@@ -5760,16 +5760,16 @@
         <v>17614.85524396554</v>
       </c>
       <c r="Y59">
-        <v>188.1510025813377</v>
+        <v>203.5141685147237</v>
       </c>
       <c r="Z59">
-        <v>1209.202343396279</v>
+        <v>1099.314374074693</v>
       </c>
       <c r="AA59">
-        <v>0.03845124113536555</v>
+        <v>0.04159091506642464</v>
       </c>
       <c r="AB59">
-        <v>0.06864673746385311</v>
+        <v>0.06240836832600674</v>
       </c>
     </row>
     <row r="60" spans="1:28">
@@ -5798,22 +5798,22 @@
         <v>76</v>
       </c>
       <c r="I60">
-        <v>24214.42008265774</v>
+        <v>24290.58110277347</v>
       </c>
       <c r="J60">
-        <v>24214.42008265774</v>
+        <v>24290.58110277347</v>
       </c>
       <c r="K60">
-        <v>85135.1427369521</v>
+        <v>84727.8366374492</v>
       </c>
       <c r="L60">
-        <v>0.02639836787626572</v>
+        <v>0.02640106323682597</v>
       </c>
       <c r="M60">
         <v>0.02504344063929142</v>
       </c>
       <c r="N60">
-        <v>0.01457357320313963</v>
+        <v>0.01458353325395363</v>
       </c>
       <c r="O60" t="s">
         <v>91</v>
@@ -5828,7 +5828,7 @@
         <v>106</v>
       </c>
       <c r="S60">
-        <v>97049.47197624846</v>
+        <v>97049.7688565523</v>
       </c>
       <c r="T60">
         <v>80230</v>
@@ -5837,7 +5837,7 @@
         <v>805.7</v>
       </c>
       <c r="V60">
-        <v>1616.801437651302</v>
+        <v>1621.853618951292</v>
       </c>
       <c r="W60">
         <v>22945.90509316176</v>
@@ -5846,16 +5846,16 @@
         <v>81353.7654291361</v>
       </c>
       <c r="Y60">
-        <v>1268.514989495983</v>
+        <v>1344.676009611714</v>
       </c>
       <c r="Z60">
-        <v>3781.377307816001</v>
+        <v>3374.071208313107</v>
       </c>
       <c r="AA60">
-        <v>0.0552828482618461</v>
+        <v>0.05860200345779556</v>
       </c>
       <c r="AB60">
-        <v>0.04648066734058921</v>
+        <v>0.04147406319197507</v>
       </c>
     </row>
     <row r="61" spans="1:28">
@@ -5884,22 +5884,22 @@
         <v>77</v>
       </c>
       <c r="I61">
-        <v>949.0064514804636</v>
+        <v>953.5612321261893</v>
       </c>
       <c r="J61">
-        <v>949.0064514804636</v>
+        <v>953.5612321261893</v>
       </c>
       <c r="K61">
-        <v>7485.618187880531</v>
+        <v>7435.282620493243</v>
       </c>
       <c r="L61">
-        <v>0.001034599273392183</v>
+        <v>0.001036411203298663</v>
       </c>
       <c r="M61">
         <v>0.00103807430866032</v>
       </c>
       <c r="N61">
-        <v>0.0008177654520015625</v>
+        <v>0.0008188900569851289</v>
       </c>
       <c r="O61" t="s">
         <v>91</v>
@@ -5914,7 +5914,7 @@
         <v>106</v>
       </c>
       <c r="S61">
-        <v>79801.59603030942</v>
+        <v>79789.21445125075</v>
       </c>
       <c r="T61">
         <v>6660</v>
@@ -5923,7 +5923,7 @@
         <v>254.1</v>
       </c>
       <c r="V61">
-        <v>95.57128420969842</v>
+        <v>96.02573088590653</v>
       </c>
       <c r="W61">
         <v>951.1294757477525</v>
@@ -5932,16 +5932,16 @@
         <v>7179.916772351964</v>
       </c>
       <c r="Y61">
-        <v>-2.123024267288883</v>
+        <v>2.43175637843683</v>
       </c>
       <c r="Z61">
-        <v>305.7014155285669</v>
+        <v>255.3658481412785</v>
       </c>
       <c r="AA61">
-        <v>-0.002232108583975718</v>
+        <v>0.002556703835221854</v>
       </c>
       <c r="AB61">
-        <v>0.04257729235883979</v>
+        <v>0.03556668638898818</v>
       </c>
     </row>
     <row r="62" spans="1:28">
@@ -5970,22 +5970,22 @@
         <v>78</v>
       </c>
       <c r="I62">
-        <v>172.716245934011</v>
+        <v>173.0869743318446</v>
       </c>
       <c r="J62">
-        <v>172.716245934011</v>
+        <v>173.0869743318446</v>
       </c>
       <c r="K62">
-        <v>428.7387906643661</v>
+        <v>426.2751243930925</v>
       </c>
       <c r="L62">
-        <v>0.0001882938754184349</v>
+        <v>0.0001881256004321833</v>
       </c>
       <c r="M62">
         <v>0.0001820090381061429</v>
       </c>
       <c r="N62">
-        <v>0.0001956761391437235</v>
+        <v>0.0001954632844921471</v>
       </c>
       <c r="O62" t="s">
         <v>92</v>
@@ -6000,7 +6000,7 @@
         <v>107</v>
       </c>
       <c r="S62">
-        <v>105456.8545816922</v>
+        <v>105494.0035056268</v>
       </c>
       <c r="T62">
         <v>270</v>
@@ -6009,7 +6009,7 @@
         <v>143.2</v>
       </c>
       <c r="V62">
-        <v>11.57653368805022</v>
+        <v>11.59693032042444</v>
       </c>
       <c r="W62">
         <v>166.7647099547813</v>
@@ -6018,16 +6018,16 @@
         <v>411.4543117920458</v>
       </c>
       <c r="Y62">
-        <v>5.951535979229703</v>
+        <v>6.322264377063277</v>
       </c>
       <c r="Z62">
-        <v>17.28447887232039</v>
+        <v>14.82081260104673</v>
       </c>
       <c r="AA62">
-        <v>0.03568822193162736</v>
+        <v>0.03791128458039818</v>
       </c>
       <c r="AB62">
-        <v>0.04200825796924978</v>
+        <v>0.03602055483753772</v>
       </c>
     </row>
     <row r="63" spans="1:28">
@@ -6056,22 +6056,22 @@
         <v>79</v>
       </c>
       <c r="I63">
-        <v>470.3799428380971</v>
+        <v>471.4517571709206</v>
       </c>
       <c r="J63">
-        <v>470.3799428380971</v>
+        <v>471.4517571709206</v>
       </c>
       <c r="K63">
-        <v>3891.832547287571</v>
+        <v>3858.888794640299</v>
       </c>
       <c r="L63">
-        <v>0.0005128044665232398</v>
+        <v>0.0005124137459503195</v>
       </c>
       <c r="M63">
         <v>0.0004869204363027354</v>
       </c>
       <c r="N63">
-        <v>0.0003616176972557497</v>
+        <v>0.0003616659949897518</v>
       </c>
       <c r="O63" t="s">
         <v>91</v>
@@ -6086,7 +6086,7 @@
         <v>106</v>
       </c>
       <c r="S63">
-        <v>71039.56212869595</v>
+        <v>71049.60909161094</v>
       </c>
       <c r="T63">
         <v>4460</v>
@@ -6095,7 +6095,7 @@
         <v>188.8</v>
       </c>
       <c r="V63">
-        <v>37.67580512912472</v>
+        <v>37.75838011620611</v>
       </c>
       <c r="W63">
         <v>446.1379840034475</v>
@@ -6104,16 +6104,16 @@
         <v>3735.368271235882</v>
       </c>
       <c r="Y63">
-        <v>24.24195883464967</v>
+        <v>25.31377316747313</v>
       </c>
       <c r="Z63">
-        <v>156.464276051689</v>
+        <v>123.5205234044174</v>
       </c>
       <c r="AA63">
-        <v>0.05433735683546358</v>
+        <v>0.05673978471933366</v>
       </c>
       <c r="AB63">
-        <v>0.04188724235212325</v>
+        <v>0.03306783011345478</v>
       </c>
     </row>
     <row r="64" spans="1:28">
@@ -6142,22 +6142,22 @@
         <v>80</v>
       </c>
       <c r="I64">
-        <v>102.5990446473618</v>
+        <v>102.6939150718847</v>
       </c>
       <c r="J64">
-        <v>102.5990446473618</v>
+        <v>102.6939150718847</v>
       </c>
       <c r="K64">
-        <v>987.0204820224494</v>
+        <v>977.324029538358</v>
       </c>
       <c r="L64">
-        <v>0.0001118526611460848</v>
+        <v>0.0001116164547228761</v>
       </c>
       <c r="M64">
         <v>0.0001016328185822026</v>
       </c>
       <c r="N64">
-        <v>0.0002079406081762007</v>
+        <v>0.0002079582949047089</v>
       </c>
       <c r="O64" t="s">
         <v>91</v>
@@ -6172,7 +6172,7 @@
         <v>106</v>
       </c>
       <c r="S64">
-        <v>91530.91698707784</v>
+        <v>91555.83560616118</v>
       </c>
       <c r="T64">
         <v>430</v>
@@ -6181,7 +6181,7 @@
         <v>415</v>
       </c>
       <c r="V64">
-        <v>5.648609304480838</v>
+        <v>5.653061856090656</v>
       </c>
       <c r="W64">
         <v>93.12047186834673</v>
@@ -6190,16 +6190,16 @@
         <v>930.7118012344204</v>
       </c>
       <c r="Y64">
-        <v>9.478572779015053</v>
+        <v>9.573443203538019</v>
       </c>
       <c r="Z64">
-        <v>56.30868078802905</v>
+        <v>46.61222830393763</v>
       </c>
       <c r="AA64">
-        <v>0.1017882812322495</v>
+        <v>0.1028070735839151</v>
       </c>
       <c r="AB64">
-        <v>0.06050066273291668</v>
+        <v>0.05008234368804066</v>
       </c>
     </row>
     <row r="65" spans="1:28">
@@ -6228,22 +6228,22 @@
         <v>81</v>
       </c>
       <c r="I65">
-        <v>139.4634045133716</v>
+        <v>139.9032465339321</v>
       </c>
       <c r="J65">
-        <v>139.4634045133716</v>
+        <v>139.9032465339321</v>
       </c>
       <c r="K65">
-        <v>248.7119372834014</v>
+        <v>249.0682871352266</v>
       </c>
       <c r="L65">
-        <v>0.0001520418926017224</v>
+        <v>0.0001520587112820395</v>
       </c>
       <c r="M65">
         <v>0.0001612574478443295</v>
       </c>
       <c r="N65">
-        <v>0.000284616330526886</v>
+        <v>0.0002849251694671791</v>
       </c>
       <c r="O65" t="s">
         <v>90</v>
@@ -6267,7 +6267,7 @@
         <v>483</v>
       </c>
       <c r="V65">
-        <v>17.75550223521495</v>
+        <v>17.81149983549191</v>
       </c>
       <c r="W65">
         <v>147.751187510398</v>
@@ -6276,16 +6276,16 @@
         <v>259.5904230422387</v>
       </c>
       <c r="Y65">
-        <v>-8.287782997026397</v>
+        <v>-7.847940976465878</v>
       </c>
       <c r="Z65">
-        <v>-10.87848575883731</v>
+        <v>-10.52213590701211</v>
       </c>
       <c r="AA65">
-        <v>-0.05609283510119435</v>
+        <v>-0.05311592487819146</v>
       </c>
       <c r="AB65">
-        <v>-0.04190634473856242</v>
+        <v>-0.04053360591542326</v>
       </c>
     </row>
     <row r="66" spans="1:28">
@@ -6314,22 +6314,22 @@
         <v>82</v>
       </c>
       <c r="I66">
-        <v>1738.686908893129</v>
+        <v>1748.263755568993</v>
       </c>
       <c r="J66">
-        <v>1738.686908893129</v>
+        <v>1748.263755568993</v>
       </c>
       <c r="K66">
-        <v>1738.686908893129</v>
+        <v>1748.263755568993</v>
       </c>
       <c r="L66">
-        <v>0.001895502617280536</v>
+        <v>0.00190016129174274</v>
       </c>
       <c r="M66">
         <v>0.002045376440641899</v>
       </c>
       <c r="N66">
-        <v>0.002311460679878795</v>
+        <v>0.002315386167970759</v>
       </c>
       <c r="O66" t="s">
         <v>93</v>
@@ -6353,7 +6353,7 @@
         <v>1236.2</v>
       </c>
       <c r="V66">
-        <v>375.2886217071746</v>
+        <v>377.3557457942672</v>
       </c>
       <c r="W66">
         <v>1874.064125722541</v>
@@ -6362,16 +6362,16 @@
         <v>1874.064125722541</v>
       </c>
       <c r="Y66">
-        <v>-135.3772168294115</v>
+        <v>-125.8003701535483</v>
       </c>
       <c r="Z66">
-        <v>-135.3772168294115</v>
+        <v>-125.8003701535483</v>
       </c>
       <c r="AA66">
-        <v>-0.07223723829472332</v>
+        <v>-0.06712703606395876</v>
       </c>
       <c r="AB66">
-        <v>-0.07223723829472332</v>
+        <v>-0.06712703606395876</v>
       </c>
     </row>
     <row r="67" spans="1:28">
@@ -6400,22 +6400,22 @@
         <v>83</v>
       </c>
       <c r="I67">
-        <v>1387.058677675745</v>
+        <v>1390.836371325327</v>
       </c>
       <c r="J67">
-        <v>1387.058677675745</v>
+        <v>1390.836371325327</v>
       </c>
       <c r="K67">
-        <v>2437.695468484309</v>
+        <v>2442.180430449165</v>
       </c>
       <c r="L67">
-        <v>0.001512160320761729</v>
+        <v>0.001511678902866795</v>
       </c>
       <c r="M67">
         <v>0.001519438595114184</v>
       </c>
       <c r="N67">
-        <v>0.002744468219083022</v>
+        <v>0.002743024113726852</v>
       </c>
       <c r="O67" t="s">
         <v>93</v>
@@ -6430,7 +6430,7 @@
         <v>105</v>
       </c>
       <c r="S67">
-        <v>36030.55781409221</v>
+        <v>36030.81129049438</v>
       </c>
       <c r="T67">
         <v>2490</v>
@@ -6439,7 +6439,7 @@
         <v>3829.4</v>
       </c>
       <c r="V67">
-        <v>196.3874635110152</v>
+        <v>196.9204052518199</v>
       </c>
       <c r="W67">
         <v>1392.176670152762</v>
@@ -6448,16 +6448,16 @@
         <v>2441.569612912939</v>
       </c>
       <c r="Y67">
-        <v>-5.117992477017651</v>
+        <v>-1.340298827435618</v>
       </c>
       <c r="Z67">
-        <v>-3.874144428630643</v>
+        <v>0.6108175362255679</v>
       </c>
       <c r="AA67">
-        <v>-0.003676252150135556</v>
+        <v>-0.0009627361642890825</v>
       </c>
       <c r="AB67">
-        <v>-0.001586743383494422</v>
+        <v>0.0002501741228245489</v>
       </c>
     </row>
     <row r="68" spans="1:28">
@@ -6486,22 +6486,22 @@
         <v>84</v>
       </c>
       <c r="I68">
-        <v>59003.76781835884</v>
+        <v>59215.19028860226</v>
       </c>
       <c r="J68">
-        <v>59003.76781835884</v>
+        <v>59215.19028860226</v>
       </c>
       <c r="K68">
-        <v>66411.30352939029</v>
+        <v>66602.04957576167</v>
       </c>
       <c r="L68">
-        <v>0.06432543763748251</v>
+        <v>0.06436008989556741</v>
       </c>
       <c r="M68">
         <v>0.06565967988004998</v>
       </c>
       <c r="N68">
-        <v>0.02436672357165643</v>
+        <v>0.02437436668875797</v>
       </c>
       <c r="O68" t="s">
         <v>93</v>
@@ -6516,7 +6516,7 @@
         <v>105</v>
       </c>
       <c r="S68">
-        <v>43082.22153183669</v>
+        <v>43089.06057425532</v>
       </c>
       <c r="T68">
         <v>62520</v>
@@ -6525,7 +6525,7 @@
         <v>6089.999999999999</v>
       </c>
       <c r="V68">
-        <v>7716.227732407124</v>
+        <v>7744.665049832372</v>
       </c>
       <c r="W68">
         <v>60160.29525157281</v>
@@ -6534,16 +6534,16 @@
         <v>67610.77531390781</v>
       </c>
       <c r="Y68">
-        <v>-1156.527433213974</v>
+        <v>-945.1049629705522</v>
       </c>
       <c r="Z68">
-        <v>-1199.471784517518</v>
+        <v>-1008.725738146139</v>
       </c>
       <c r="AA68">
-        <v>-0.01922409835885469</v>
+        <v>-0.01570977933233869</v>
       </c>
       <c r="AB68">
-        <v>-0.01774083759502137</v>
+        <v>-0.01491960021849712</v>
       </c>
     </row>
     <row r="69" spans="1:28">
@@ -6572,22 +6572,22 @@
         <v>85</v>
       </c>
       <c r="I69">
-        <v>30655.91798244201</v>
+        <v>30748.80574440461</v>
       </c>
       <c r="J69">
-        <v>30655.91798244201</v>
+        <v>30748.80574440461</v>
       </c>
       <c r="K69">
-        <v>47801.44147442091</v>
+        <v>47880.45179352314</v>
       </c>
       <c r="L69">
-        <v>0.03342083757210136</v>
+        <v>0.03342040939573131</v>
       </c>
       <c r="M69">
         <v>0.03536068949271266</v>
       </c>
       <c r="N69">
-        <v>0.008830533810728689</v>
+        <v>0.008825619245862275</v>
       </c>
       <c r="O69" t="s">
         <v>90</v>
@@ -6602,7 +6602,7 @@
         <v>105</v>
       </c>
       <c r="S69">
-        <v>47209.48256187818</v>
+        <v>47211.00724158143</v>
       </c>
       <c r="T69">
         <v>51090</v>
@@ -6611,7 +6611,7 @@
         <v>13969.9</v>
       </c>
       <c r="V69">
-        <v>3146.277958454903</v>
+        <v>3155.476827812757</v>
       </c>
       <c r="W69">
         <v>32399.02363318014</v>
@@ -6620,16 +6620,16 @@
         <v>50414.66539336824</v>
       </c>
       <c r="Y69">
-        <v>-1743.105650738136</v>
+        <v>-1650.217888775533</v>
       </c>
       <c r="Z69">
-        <v>-2613.223918947326</v>
+        <v>-2534.213599845098</v>
       </c>
       <c r="AA69">
-        <v>-0.05380117840813591</v>
+        <v>-0.05093418577853467</v>
       </c>
       <c r="AB69">
-        <v>-0.0518345980987326</v>
+        <v>-0.05026738906370801</v>
       </c>
     </row>
     <row r="70" spans="1:28">
@@ -6658,22 +6658,22 @@
         <v>86</v>
       </c>
       <c r="I70">
-        <v>5530.90512145165</v>
+        <v>5544.579119201193</v>
       </c>
       <c r="J70">
-        <v>5530.90512145165</v>
+        <v>5544.579119201193</v>
       </c>
       <c r="K70">
-        <v>7704.330478919856</v>
+        <v>7706.097169516122</v>
       </c>
       <c r="L70">
-        <v>0.00602974870289676</v>
+        <v>0.006026318733515261</v>
       </c>
       <c r="M70">
         <v>0.005662005840285715</v>
       </c>
       <c r="N70">
-        <v>0.006539629015514912</v>
+        <v>0.006542466202266254</v>
       </c>
       <c r="O70" t="s">
         <v>90</v>
@@ -6688,7 +6688,7 @@
         <v>105</v>
       </c>
       <c r="S70">
-        <v>62068.81925669406</v>
+        <v>62067.57746174934</v>
       </c>
       <c r="T70">
         <v>6440</v>
@@ -6697,7 +6697,7 @@
         <v>1579.5</v>
       </c>
       <c r="V70">
-        <v>505.7830019459363</v>
+        <v>507.0223086176677</v>
       </c>
       <c r="W70">
         <v>5187.779527557743</v>
@@ -6706,16 +6706,16 @@
         <v>7343.14190380297</v>
       </c>
       <c r="Y70">
-        <v>343.1255938939075</v>
+        <v>356.7995916434502</v>
       </c>
       <c r="Z70">
-        <v>361.1885751168857</v>
+        <v>362.9552657131526</v>
       </c>
       <c r="AA70">
-        <v>0.0661411287953174</v>
+        <v>0.06877693813858377</v>
       </c>
       <c r="AB70">
-        <v>0.04918719804799472</v>
+        <v>0.04942778860438203</v>
       </c>
     </row>
     <row r="71" spans="1:28">
@@ -6744,22 +6744,22 @@
         <v>87</v>
       </c>
       <c r="I71">
-        <v>54634.7530818946</v>
+        <v>54702.53637428236</v>
       </c>
       <c r="J71">
-        <v>54634.7530818946</v>
+        <v>54702.53637428236</v>
       </c>
       <c r="K71">
-        <v>62439.56280777944</v>
+        <v>62529.18205497491</v>
       </c>
       <c r="L71">
-        <v>0.059562372576403</v>
+        <v>0.05945535497573188</v>
       </c>
       <c r="M71">
         <v>0.05755340664173174</v>
       </c>
       <c r="N71">
-        <v>0.02214327098281568</v>
+        <v>0.02207075705868983</v>
       </c>
       <c r="O71" t="s">
         <v>90</v>
@@ -6774,7 +6774,7 @@
         <v>105</v>
       </c>
       <c r="S71">
-        <v>55496.65226698504</v>
+        <v>55503.46449889614</v>
       </c>
       <c r="T71">
         <v>55630</v>
@@ -6783,7 +6783,7 @@
         <v>3288.9</v>
       </c>
       <c r="V71">
-        <v>4949.083930668198</v>
+        <v>4956.15256236516</v>
       </c>
       <c r="W71">
         <v>52732.97010624685</v>
@@ -6792,16 +6792,16 @@
         <v>60302.07820681902</v>
       </c>
       <c r="Y71">
-        <v>1901.782975647744</v>
+        <v>1969.566268035509</v>
       </c>
       <c r="Z71">
-        <v>2137.484600960423</v>
+        <v>2227.103848155894</v>
       </c>
       <c r="AA71">
-        <v>0.03606440092063874</v>
+        <v>0.03734980722813848</v>
       </c>
       <c r="AB71">
-        <v>0.03544628418326574</v>
+        <v>0.03693245596806066</v>
       </c>
     </row>
     <row r="72" spans="1:28">
@@ -6830,22 +6830,22 @@
         <v>88</v>
       </c>
       <c r="I72">
-        <v>151398.3565900836</v>
+        <v>151855.4817774482</v>
       </c>
       <c r="J72">
-        <v>151398.3565900836</v>
+        <v>151855.4817774482</v>
       </c>
       <c r="K72">
-        <v>237215.992429528</v>
+        <v>238013.9832016906</v>
       </c>
       <c r="L72">
-        <v>0.1650532822790781</v>
+        <v>0.1650494140219364</v>
       </c>
       <c r="M72">
         <v>0.1632699410985861</v>
       </c>
       <c r="N72">
-        <v>0.08855358834555666</v>
+        <v>0.08859803199207071</v>
       </c>
       <c r="O72" t="s">
         <v>90</v>
@@ -6860,7 +6860,7 @@
         <v>105</v>
       </c>
       <c r="S72">
-        <v>46595.70302630735</v>
+        <v>46597.65656627798</v>
       </c>
       <c r="T72">
         <v>235530</v>
@@ -6869,7 +6869,7 @@
         <v>5083.8</v>
       </c>
       <c r="V72">
-        <v>15407.24490409293</v>
+        <v>15453.49389105771</v>
       </c>
       <c r="W72">
         <v>149595.1226101282</v>
@@ -6878,16 +6878,16 @@
         <v>238519.2132284619</v>
       </c>
       <c r="Y72">
-        <v>1803.233979955461</v>
+        <v>2260.359167320014</v>
       </c>
       <c r="Z72">
-        <v>-1303.220798933908</v>
+        <v>-505.2300267712853</v>
       </c>
       <c r="AA72">
-        <v>0.0120540960727377</v>
+        <v>0.01510984534710344</v>
       </c>
       <c r="AB72">
-        <v>-0.005463797994695035</v>
+        <v>-0.002118194253338236</v>
       </c>
     </row>
     <row r="73" spans="1:28">
@@ -6916,22 +6916,22 @@
         <v>89</v>
       </c>
       <c r="I73">
-        <v>76542.57032890509</v>
+        <v>76828.016918179</v>
       </c>
       <c r="J73">
-        <v>76542.57032890509</v>
+        <v>76828.016918179</v>
       </c>
       <c r="K73">
-        <v>85157.02418784445</v>
+        <v>85483.61341015113</v>
       </c>
       <c r="L73">
-        <v>0.08344610041619462</v>
+        <v>0.08350320333774088</v>
       </c>
       <c r="M73">
         <v>0.08648794651350025</v>
       </c>
       <c r="N73">
-        <v>0.03007881774148646</v>
+        <v>0.03009725643968056</v>
       </c>
       <c r="O73" t="s">
         <v>93</v>
@@ -6946,7 +6946,7 @@
         <v>105</v>
       </c>
       <c r="S73">
-        <v>46709.60746439645</v>
+        <v>46723.63967383048</v>
       </c>
       <c r="T73">
         <v>84500</v>
@@ -6955,7 +6955,7 @@
         <v>13765.8</v>
       </c>
       <c r="V73">
-        <v>8977.775059297852</v>
+        <v>9009.521848852681</v>
       </c>
       <c r="W73">
         <v>79244.07197019146</v>
@@ -6964,16 +6964,16 @@
         <v>88033.11316395696</v>
       </c>
       <c r="Y73">
-        <v>-2701.501641286377</v>
+        <v>-2416.055052012467</v>
       </c>
       <c r="Z73">
-        <v>-2876.088976112515</v>
+        <v>-2549.499753805838</v>
       </c>
       <c r="AA73">
-        <v>-0.0340908988410209</v>
+        <v>-0.03048877968968193</v>
       </c>
       <c r="AB73">
-        <v>-0.03267053581026894</v>
+        <v>-0.02896069061033353</v>
       </c>
     </row>
     <row r="74" spans="1:28">
@@ -12420,16 +12420,16 @@
         <v>72</v>
       </c>
       <c r="I137">
-        <v>19846.69871497192</v>
+        <v>20049.52327347857</v>
       </c>
       <c r="J137">
-        <v>19846.69871497192</v>
+        <v>20049.52327347857</v>
       </c>
       <c r="K137">
-        <v>67511.77838058303</v>
+        <v>68203.18361748566</v>
       </c>
       <c r="L137">
-        <v>0.4999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="M137">
         <v>0.5</v>
@@ -12450,7 +12450,7 @@
         <v>105</v>
       </c>
       <c r="S137">
-        <v>58473.74221061087</v>
+        <v>58473.74221061086</v>
       </c>
       <c r="T137">
         <v>70170</v>
@@ -12459,7 +12459,7 @@
         <v>7143.3</v>
       </c>
       <c r="V137">
-        <v>1931.730733991772</v>
+        <v>1951.472175069831</v>
       </c>
       <c r="W137">
         <v>20928.03175770726</v>
@@ -12468,16 +12468,16 @@
         <v>70604.00000000003</v>
       </c>
       <c r="Y137">
-        <v>-1081.333042735339</v>
+        <v>-878.508484228696</v>
       </c>
       <c r="Z137">
-        <v>-3092.221619417003</v>
+        <v>-2400.816382514371</v>
       </c>
       <c r="AA137">
-        <v>-0.0516691227944602</v>
+        <v>-0.04197759705258301</v>
       </c>
       <c r="AB137">
-        <v>-0.04379669168059886</v>
+        <v>-0.03400397119871919</v>
       </c>
     </row>
     <row r="138" spans="1:28">
@@ -12506,16 +12506,16 @@
         <v>73</v>
       </c>
       <c r="I138">
-        <v>1256.514927113509</v>
+        <v>1269.355958713215</v>
       </c>
       <c r="J138">
-        <v>1256.514927113509</v>
+        <v>1269.355958713215</v>
       </c>
       <c r="K138">
-        <v>4274.240190243229</v>
+        <v>4318.013767568571</v>
       </c>
       <c r="L138">
-        <v>0.03165551473217106</v>
+        <v>0.03165551473217107</v>
       </c>
       <c r="M138">
         <v>0.0311411453253447</v>
@@ -12545,7 +12545,7 @@
         <v>770.4</v>
       </c>
       <c r="V138">
-        <v>94.81939067853658</v>
+        <v>95.78840327496073</v>
       </c>
       <c r="W138">
         <v>1303.445756680382</v>
@@ -12554,16 +12554,16 @@
         <v>4397.378849101274</v>
       </c>
       <c r="Y138">
-        <v>-46.9308295668734</v>
+        <v>-34.08979796716699</v>
       </c>
       <c r="Z138">
-        <v>-123.1386588580444</v>
+        <v>-79.36508153270279</v>
       </c>
       <c r="AA138">
-        <v>-0.03600520338214681</v>
+        <v>-0.0261535992521752</v>
       </c>
       <c r="AB138">
-        <v>-0.02800274051511646</v>
+        <v>-0.01804827017552132</v>
       </c>
     </row>
     <row r="139" spans="1:28">
@@ -12592,13 +12592,13 @@
         <v>74</v>
       </c>
       <c r="I139">
-        <v>852.8851677694015</v>
+        <v>861.6012802117795</v>
       </c>
       <c r="J139">
-        <v>852.8851677694015</v>
+        <v>861.6012802117795</v>
       </c>
       <c r="K139">
-        <v>2901.227819168598</v>
+        <v>2930.940028737612</v>
       </c>
       <c r="L139">
         <v>0.02148682710455022</v>
@@ -12622,7 +12622,7 @@
         <v>106</v>
       </c>
       <c r="S139">
-        <v>80291.97653504327</v>
+        <v>80291.97653504324</v>
       </c>
       <c r="T139">
         <v>3200</v>
@@ -12631,7 +12631,7 @@
         <v>742.2</v>
       </c>
       <c r="V139">
-        <v>73.12703789733685</v>
+        <v>73.87436415997803</v>
       </c>
       <c r="W139">
         <v>874.7958098526053</v>
@@ -12640,16 +12640,16 @@
         <v>2951.26097255119</v>
       </c>
       <c r="Y139">
-        <v>-21.91064208320381</v>
+        <v>-13.19452964082586</v>
       </c>
       <c r="Z139">
-        <v>-50.03315338259245</v>
+        <v>-20.32094381357774</v>
       </c>
       <c r="AA139">
-        <v>-0.02504657868319642</v>
+        <v>-0.01508298221392832</v>
       </c>
       <c r="AB139">
-        <v>-0.01695314438402299</v>
+        <v>-0.006885512329332058</v>
       </c>
     </row>
     <row r="140" spans="1:28">
@@ -12678,16 +12678,16 @@
         <v>75</v>
       </c>
       <c r="I140">
-        <v>149.0656851551895</v>
+        <v>150.5890710953047</v>
       </c>
       <c r="J140">
-        <v>149.0656851551895</v>
+        <v>150.5890710953047</v>
       </c>
       <c r="K140">
-        <v>507.0712084098443</v>
+        <v>512.2642531997583</v>
       </c>
       <c r="L140">
-        <v>0.003755427723673196</v>
+        <v>0.003755427723673195</v>
       </c>
       <c r="M140">
         <v>0.003692350564302525</v>
@@ -12717,7 +12717,7 @@
         <v>227.9</v>
       </c>
       <c r="V140">
-        <v>8.90679363821266</v>
+        <v>8.997817163753329</v>
       </c>
       <c r="W140">
         <v>154.5472597406232</v>
@@ -12726,16 +12726,16 @@
         <v>521.3894384840308</v>
       </c>
       <c r="Y140">
-        <v>-5.481574585433634</v>
+        <v>-3.958188645318444</v>
       </c>
       <c r="Z140">
-        <v>-14.31823007418654</v>
+        <v>-9.125185284272561</v>
       </c>
       <c r="AA140">
-        <v>-0.03546859772624482</v>
+        <v>-0.02561150972176068</v>
       </c>
       <c r="AB140">
-        <v>-0.02746168030525821</v>
+        <v>-0.01750166883089261</v>
       </c>
     </row>
     <row r="141" spans="1:28">
@@ -12764,13 +12764,13 @@
         <v>76</v>
       </c>
       <c r="I141">
-        <v>1139.749572729776</v>
+        <v>1151.397313606835</v>
       </c>
       <c r="J141">
-        <v>1139.749572729776</v>
+        <v>1151.397313606835</v>
       </c>
       <c r="K141">
-        <v>3877.043818146442</v>
+        <v>3916.749606734267</v>
       </c>
       <c r="L141">
         <v>0.02871383269072286</v>
@@ -12794,7 +12794,7 @@
         <v>106</v>
       </c>
       <c r="S141">
-        <v>94881.43372252793</v>
+        <v>94881.43372252792</v>
       </c>
       <c r="T141">
         <v>3540</v>
@@ -12803,7 +12803,7 @@
         <v>79.7</v>
       </c>
       <c r="V141">
-        <v>78.86400552113221</v>
+        <v>79.66996107734883</v>
       </c>
       <c r="W141">
         <v>1143.066524874072</v>
@@ -12812,16 +12812,16 @@
         <v>3856.314337466895</v>
       </c>
       <c r="Y141">
-        <v>-3.31695214429601</v>
+        <v>8.330788732762812</v>
       </c>
       <c r="Z141">
-        <v>20.72948067954758</v>
+        <v>60.43526926737195</v>
       </c>
       <c r="AA141">
-        <v>-0.002901801489341512</v>
+        <v>0.007288104892828163</v>
       </c>
       <c r="AB141">
-        <v>0.005375464463087362</v>
+        <v>0.01567176946137389</v>
       </c>
     </row>
     <row r="142" spans="1:28">
@@ -12850,16 +12850,16 @@
         <v>77</v>
       </c>
       <c r="I142">
-        <v>286.9546019765193</v>
+        <v>289.8871521851557</v>
       </c>
       <c r="J142">
-        <v>286.9546019765193</v>
+        <v>289.8871521851557</v>
       </c>
       <c r="K142">
-        <v>976.1228188198745</v>
+        <v>986.1195400584655</v>
       </c>
       <c r="L142">
-        <v>0.007229277929231798</v>
+        <v>0.007229277929231796</v>
       </c>
       <c r="M142">
         <v>0.007106033161487999</v>
@@ -12889,7 +12889,7 @@
         <v>41.9</v>
       </c>
       <c r="V142">
-        <v>26.08743379787287</v>
+        <v>26.35403593249555</v>
       </c>
       <c r="W142">
         <v>297.4305753498836</v>
@@ -12898,16 +12898,16 @@
         <v>1003.428730667397</v>
       </c>
       <c r="Y142">
-        <v>-10.4759733733643</v>
+        <v>-7.543423164727869</v>
       </c>
       <c r="Z142">
-        <v>-27.30591184752245</v>
+        <v>-17.30919060893143</v>
       </c>
       <c r="AA142">
-        <v>-0.0352215751895744</v>
+        <v>-0.02536196272307962</v>
       </c>
       <c r="AB142">
-        <v>-0.0272126071468582</v>
+        <v>-0.01725004485113637</v>
       </c>
     </row>
     <row r="143" spans="1:28">
@@ -12936,16 +12936,16 @@
         <v>79</v>
       </c>
       <c r="I143">
-        <v>30.53725953480395</v>
+        <v>30.84933693730298</v>
       </c>
       <c r="J143">
-        <v>30.53725953480395</v>
+        <v>30.84933693730298</v>
       </c>
       <c r="K143">
-        <v>103.8774623262046</v>
+        <v>104.9412977512414</v>
       </c>
       <c r="L143">
-        <v>0.000769328440295395</v>
+        <v>0.0007693284402953951</v>
       </c>
       <c r="M143">
         <v>0.0007663369095722053</v>
@@ -12966,7 +12966,7 @@
         <v>106</v>
       </c>
       <c r="S143">
-        <v>72735.74095208403</v>
+        <v>72735.74095208402</v>
       </c>
       <c r="T143">
         <v>150</v>
@@ -12975,7 +12975,7 @@
         <v>22.5</v>
       </c>
       <c r="V143">
-        <v>2.38750987071771</v>
+        <v>2.411909174723532</v>
       </c>
       <c r="W143">
         <v>32.0758463612607</v>
@@ -12984,16 +12984,16 @@
         <v>108.2129023268719</v>
       </c>
       <c r="Y143">
-        <v>-1.538586826456754</v>
+        <v>-1.226509423957722</v>
       </c>
       <c r="Z143">
-        <v>-4.335440000667319</v>
+        <v>-3.271604575630562</v>
       </c>
       <c r="AA143">
-        <v>-0.0479671466538438</v>
+        <v>-0.0382377883390484</v>
       </c>
       <c r="AB143">
-        <v>-0.04006398412244343</v>
+        <v>-0.03023303603620418</v>
       </c>
     </row>
     <row r="144" spans="1:28">
@@ -13022,13 +13022,13 @@
         <v>81</v>
       </c>
       <c r="I144">
-        <v>21.98921302961482</v>
+        <v>22.2139331449696</v>
       </c>
       <c r="J144">
-        <v>21.98921302961482</v>
+        <v>22.2139331449696</v>
       </c>
       <c r="K144">
-        <v>74.79988980227152</v>
+        <v>75.5659344358092</v>
       </c>
       <c r="L144">
         <v>0.0005539765919111429</v>
@@ -13061,7 +13061,7 @@
         <v>161</v>
       </c>
       <c r="V144">
-        <v>2.799512334151499</v>
+        <v>2.828122122679191</v>
       </c>
       <c r="W144">
         <v>23.32788826273601</v>
@@ -13070,16 +13070,16 @@
         <v>78.70029260136461</v>
       </c>
       <c r="Y144">
-        <v>-1.33867523312119</v>
+        <v>-1.113955117766409</v>
       </c>
       <c r="Z144">
-        <v>-3.900402799093087</v>
+        <v>-3.134358165555412</v>
       </c>
       <c r="AA144">
-        <v>-0.05738518712212761</v>
+        <v>-0.04775207705130523</v>
       </c>
       <c r="AB144">
-        <v>-0.04956020708651668</v>
+        <v>-0.03982651222698331</v>
       </c>
     </row>
     <row r="145" spans="1:28">
@@ -13108,13 +13108,13 @@
         <v>83</v>
       </c>
       <c r="I145">
-        <v>118.0554561326494</v>
+        <v>119.2619311294881</v>
       </c>
       <c r="J145">
-        <v>118.0554561326494</v>
+        <v>119.2619311294881</v>
       </c>
       <c r="K145">
-        <v>401.5848633321355</v>
+        <v>405.6975957208963</v>
       </c>
       <c r="L145">
         <v>0.002974183712568552</v>
@@ -13147,7 +13147,7 @@
         <v>351.3</v>
       </c>
       <c r="V145">
-        <v>16.77977089310558</v>
+        <v>16.95125279405615</v>
       </c>
       <c r="W145">
         <v>122.4714133793645</v>
@@ -13156,16 +13156,16 @@
         <v>413.176536157166</v>
       </c>
       <c r="Y145">
-        <v>-4.415957246715109</v>
+        <v>-3.209482249876402</v>
       </c>
       <c r="Z145">
-        <v>-11.59167282503051</v>
+        <v>-7.478940436269681</v>
       </c>
       <c r="AA145">
-        <v>-0.03605704486349271</v>
+        <v>-0.02620597053072937</v>
       </c>
       <c r="AB145">
-        <v>-0.02805501235099473</v>
+        <v>-0.0181010773405216</v>
       </c>
     </row>
     <row r="146" spans="1:28">
@@ -13194,16 +13194,16 @@
         <v>84</v>
       </c>
       <c r="I146">
-        <v>395.8283871385714</v>
+        <v>399.8735796926969</v>
       </c>
       <c r="J146">
-        <v>395.8283871385714</v>
+        <v>399.8735796926969</v>
       </c>
       <c r="K146">
-        <v>1346.474732801961</v>
+        <v>1360.264321877341</v>
       </c>
       <c r="L146">
-        <v>0.00997214682459927</v>
+        <v>0.009972146824599269</v>
       </c>
       <c r="M146">
         <v>0.01003204681621842</v>
@@ -13233,7 +13233,7 @@
         <v>825.8</v>
       </c>
       <c r="V146">
-        <v>35.33582483774097</v>
+        <v>35.69694147356596</v>
       </c>
       <c r="W146">
         <v>419.9019887292501</v>
@@ -13242,16 +13242,16 @@
         <v>1416.60526682457</v>
       </c>
       <c r="Y146">
-        <v>-24.07360159067866</v>
+        <v>-20.02840903655323</v>
       </c>
       <c r="Z146">
-        <v>-70.13053402260903</v>
+        <v>-56.34094494722922</v>
       </c>
       <c r="AA146">
-        <v>-0.05733147790876779</v>
+        <v>-0.04769781895333534</v>
       </c>
       <c r="AB146">
-        <v>-0.04950605201391918</v>
+        <v>-0.03977180253855881</v>
       </c>
     </row>
     <row r="147" spans="1:28">
@@ -13280,13 +13280,13 @@
         <v>85</v>
       </c>
       <c r="I147">
-        <v>1483.764583931551</v>
+        <v>1498.928007379737</v>
       </c>
       <c r="J147">
-        <v>1483.764583931551</v>
+        <v>1498.928007379737</v>
       </c>
       <c r="K147">
-        <v>5047.266913150523</v>
+        <v>5098.95725311054</v>
       </c>
       <c r="L147">
         <v>0.03738063960260126</v>
@@ -13319,7 +13319,7 @@
         <v>1450.2</v>
       </c>
       <c r="V147">
-        <v>144.0803341228122</v>
+        <v>145.5527719613482</v>
       </c>
       <c r="W147">
         <v>1632.952178391533</v>
@@ -13328,16 +13328,16 @@
         <v>5509.020482095565</v>
       </c>
       <c r="Y147">
-        <v>-149.1875944599824</v>
+        <v>-134.0241710117957</v>
       </c>
       <c r="Z147">
-        <v>-461.7535689450424</v>
+        <v>-410.0632289850255</v>
       </c>
       <c r="AA147">
-        <v>-0.0913606634867489</v>
+        <v>-0.08207476788684055</v>
       </c>
       <c r="AB147">
-        <v>-0.08381772593617166</v>
+        <v>-0.07443487101159631</v>
       </c>
     </row>
     <row r="148" spans="1:28">
@@ -13366,13 +13366,13 @@
         <v>86</v>
       </c>
       <c r="I148">
-        <v>84.24068609126385</v>
+        <v>85.10158896534575</v>
       </c>
       <c r="J148">
-        <v>84.24068609126385</v>
+        <v>85.10158896534575</v>
       </c>
       <c r="K148">
-        <v>286.5584151651043</v>
+        <v>289.4931325385198</v>
       </c>
       <c r="L148">
         <v>0.002122284600101136</v>
@@ -13405,7 +13405,7 @@
         <v>81</v>
       </c>
       <c r="V148">
-        <v>7.958357328425905</v>
+        <v>8.039688250749947</v>
       </c>
       <c r="W148">
         <v>87.4795809852595</v>
@@ -13414,16 +13414,16 @@
         <v>295.1260972551156</v>
       </c>
       <c r="Y148">
-        <v>-3.238894893995649</v>
+        <v>-2.377992019913748</v>
       </c>
       <c r="Z148">
-        <v>-8.56768209001126</v>
+        <v>-5.632964716595779</v>
       </c>
       <c r="AA148">
-        <v>-0.03702458170828928</v>
+        <v>-0.02718339517783521</v>
       </c>
       <c r="AB148">
-        <v>-0.0290305810624572</v>
+        <v>-0.01908663709846873</v>
       </c>
     </row>
     <row r="149" spans="1:28">
@@ -13452,16 +13452,16 @@
         <v>87</v>
       </c>
       <c r="I149">
-        <v>1115.643432110659</v>
+        <v>1127.044818800627</v>
       </c>
       <c r="J149">
-        <v>1115.643432110659</v>
+        <v>1127.044818800627</v>
       </c>
       <c r="K149">
-        <v>3795.042854335705</v>
+        <v>3833.908850265569</v>
       </c>
       <c r="L149">
-        <v>0.02810652411599923</v>
+        <v>0.02810652411599924</v>
       </c>
       <c r="M149">
         <v>0.02654312386791133</v>
@@ -13482,7 +13482,7 @@
         <v>105</v>
       </c>
       <c r="S149">
-        <v>60605.82209629644</v>
+        <v>60605.82209629643</v>
       </c>
       <c r="T149">
         <v>4070</v>
@@ -13491,7 +13491,7 @@
         <v>286.3</v>
       </c>
       <c r="V149">
-        <v>105.6112283210469</v>
+        <v>106.6905287661835</v>
       </c>
       <c r="W149">
         <v>1110.990678512812</v>
@@ -13500,16 +13500,16 @@
         <v>3748.101435140022</v>
       </c>
       <c r="Y149">
-        <v>4.652753597847095</v>
+        <v>16.05414028781479</v>
       </c>
       <c r="Z149">
-        <v>46.94141919568347</v>
+        <v>85.80741512554732</v>
       </c>
       <c r="AA149">
-        <v>0.004187932165259332</v>
+        <v>0.01445029251667988</v>
       </c>
       <c r="AB149">
-        <v>0.01252405251245017</v>
+        <v>0.02289356801314576</v>
       </c>
     </row>
     <row r="150" spans="1:28">
@@ -13538,13 +13538,13 @@
         <v>88</v>
       </c>
       <c r="I150">
-        <v>11242.30280668116</v>
+        <v>11357.19421185188</v>
       </c>
       <c r="J150">
-        <v>11242.30280668116</v>
+        <v>11357.19421185188</v>
       </c>
       <c r="K150">
-        <v>38242.52418360645</v>
+        <v>38634.17556840429</v>
       </c>
       <c r="L150">
         <v>0.2832285350862964</v>
@@ -13577,7 +13577,7 @@
         <v>668.1999999999999</v>
       </c>
       <c r="V150">
-        <v>1140.150618176461</v>
+        <v>1151.802457562135</v>
       </c>
       <c r="W150">
         <v>11978.8706229151</v>
@@ -13586,16 +13586,16 @@
         <v>40412.60025080129</v>
       </c>
       <c r="Y150">
-        <v>-736.5678162339464</v>
+        <v>-621.676411063223</v>
       </c>
       <c r="Z150">
-        <v>-2170.076067194845</v>
+        <v>-1778.424682396995</v>
       </c>
       <c r="AA150">
-        <v>-0.06148891990075603</v>
+        <v>-0.05189774817953043</v>
       </c>
       <c r="AB150">
-        <v>-0.05369800640709371</v>
+        <v>-0.04400668779935122</v>
       </c>
     </row>
     <row r="151" spans="1:28">
@@ -13624,13 +13624,13 @@
         <v>89</v>
       </c>
       <c r="I151">
-        <v>1669.166935577262</v>
+        <v>1686.225089764232</v>
       </c>
       <c r="J151">
-        <v>1669.166935577262</v>
+        <v>1686.225089764232</v>
       </c>
       <c r="K151">
-        <v>5677.94321127469</v>
+        <v>5736.092467082772</v>
       </c>
       <c r="L151">
         <v>0.04205150084527855</v>
@@ -13654,7 +13654,7 @@
         <v>105</v>
       </c>
       <c r="S151">
-        <v>43887.23851694327</v>
+        <v>43887.23851694328</v>
       </c>
       <c r="T151">
         <v>6080</v>
@@ -13663,7 +13663,7 @@
         <v>1434.9</v>
       </c>
       <c r="V151">
-        <v>194.8229165742195</v>
+        <v>196.8139213558526</v>
       </c>
       <c r="W151">
         <v>1746.675633672379</v>
@@ -13672,16 +13672,16 @@
         <v>5892.684408527245</v>
       </c>
       <c r="Y151">
-        <v>-77.50869809511755</v>
+        <v>-60.45054390814744</v>
       </c>
       <c r="Z151">
-        <v>-214.7411972525551</v>
+        <v>-156.5919414444734</v>
       </c>
       <c r="AA151">
-        <v>-0.04437498102160834</v>
+        <v>-0.03460891234914085</v>
       </c>
       <c r="AB151">
-        <v>-0.03644199864866431</v>
+        <v>-0.02657395689100043</v>
       </c>
     </row>
     <row r="152" spans="1:28">
@@ -18612,16 +18612,16 @@
         <v>72</v>
       </c>
       <c r="I209">
-        <v>6106.302442746533</v>
+        <v>6122.505029926248</v>
       </c>
       <c r="J209">
-        <v>6106.302442746533</v>
+        <v>6122.505029926248</v>
       </c>
       <c r="K209">
-        <v>45032.41650438225</v>
+        <v>45148.52309007628</v>
       </c>
       <c r="L209">
-        <v>0.5000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M209">
         <v>0.5</v>
@@ -18651,7 +18651,7 @@
         <v>6175</v>
       </c>
       <c r="V209">
-        <v>554.8631634419057</v>
+        <v>556.3354486525998</v>
       </c>
       <c r="W209">
         <v>6089.070013066867</v>
@@ -18660,16 +18660,16 @@
         <v>45958.00000000001</v>
       </c>
       <c r="Y209">
-        <v>17.23242967966598</v>
+        <v>33.43501685938099</v>
       </c>
       <c r="Z209">
-        <v>-925.5834956177569</v>
+        <v>-809.476909923731</v>
       </c>
       <c r="AA209">
-        <v>0.002830059375682325</v>
+        <v>0.005490989065264641</v>
       </c>
       <c r="AB209">
-        <v>-0.02013976882409497</v>
+        <v>-0.01761340593419494</v>
       </c>
     </row>
     <row r="210" spans="1:28">
@@ -18698,13 +18698,13 @@
         <v>73</v>
       </c>
       <c r="I210">
-        <v>501.3891583741135</v>
+        <v>502.7195545714343</v>
       </c>
       <c r="J210">
-        <v>501.3891583741135</v>
+        <v>502.7195545714343</v>
       </c>
       <c r="K210">
-        <v>3697.616621905994</v>
+        <v>3707.150146297989</v>
       </c>
       <c r="L210">
         <v>0.04105505443557717</v>
@@ -18737,7 +18737,7 @@
         <v>739.7</v>
       </c>
       <c r="V210">
-        <v>37.90593475167693</v>
+        <v>38.00651513042516</v>
       </c>
       <c r="W210">
         <v>493.2198356640241</v>
@@ -18746,16 +18746,16 @@
         <v>3722.636980491933</v>
       </c>
       <c r="Y210">
-        <v>8.169322710089432</v>
+        <v>9.499718907410227</v>
       </c>
       <c r="Z210">
-        <v>-25.02035858593899</v>
+        <v>-15.48683419394456</v>
       </c>
       <c r="AA210">
-        <v>0.0165632485139026</v>
+        <v>0.01926061812704818</v>
       </c>
       <c r="AB210">
-        <v>-0.006721138461003695</v>
+        <v>-0.004160178463573429</v>
       </c>
     </row>
     <row r="211" spans="1:28">
@@ -18784,13 +18784,13 @@
         <v>74</v>
       </c>
       <c r="I211">
-        <v>399.3113077798976</v>
+        <v>400.3708485309188</v>
       </c>
       <c r="J211">
-        <v>399.3113077798976</v>
+        <v>400.3708485309188</v>
       </c>
       <c r="K211">
-        <v>2944.818619034186</v>
+        <v>2952.411212589786</v>
       </c>
       <c r="L211">
         <v>0.03269665329582765</v>
@@ -18814,7 +18814,7 @@
         <v>106</v>
       </c>
       <c r="S211">
-        <v>84287.97396802202</v>
+        <v>84287.97396802201</v>
       </c>
       <c r="T211">
         <v>2750</v>
@@ -18823,7 +18823,7 @@
         <v>742.2</v>
       </c>
       <c r="V211">
-        <v>33.35808028142133</v>
+        <v>33.44659329055827</v>
       </c>
       <c r="W211">
         <v>389.9277234830764</v>
@@ -18832,16 +18832,16 @@
         <v>2943.027141645453</v>
       </c>
       <c r="Y211">
-        <v>9.383584296821198</v>
+        <v>10.44312504784239</v>
       </c>
       <c r="Z211">
-        <v>1.791477388732346</v>
+        <v>9.384070944332507</v>
       </c>
       <c r="AA211">
-        <v>0.02406493237516225</v>
+        <v>0.02678220710894294</v>
       </c>
       <c r="AB211">
-        <v>0.0006087192888512496</v>
+        <v>0.003188577778146433</v>
       </c>
     </row>
     <row r="212" spans="1:28">
@@ -18870,16 +18870,16 @@
         <v>75</v>
       </c>
       <c r="I212">
-        <v>78.64211000729907</v>
+        <v>78.85078058255098</v>
       </c>
       <c r="J212">
-        <v>78.64211000729907</v>
+        <v>78.85078058255098</v>
       </c>
       <c r="K212">
-        <v>579.9654186534601</v>
+        <v>581.4607371330693</v>
       </c>
       <c r="L212">
-        <v>0.00643942146205969</v>
+        <v>0.006439421462059691</v>
       </c>
       <c r="M212">
         <v>0.00657336726039008</v>
@@ -18909,7 +18909,7 @@
         <v>210</v>
       </c>
       <c r="V212">
-        <v>4.429850979097971</v>
+        <v>4.44160523584417</v>
       </c>
       <c r="W212">
         <v>80.05138694023348</v>
@@ -18918,16 +18918,16 @@
         <v>604.1976251060147</v>
       </c>
       <c r="Y212">
-        <v>-1.409276932934418</v>
+        <v>-1.200606357682503</v>
       </c>
       <c r="Z212">
-        <v>-24.23220645255458</v>
+        <v>-22.7368879729454</v>
       </c>
       <c r="AA212">
-        <v>-0.01760465354568543</v>
+        <v>-0.01499794573926468</v>
       </c>
       <c r="AB212">
-        <v>-0.04010642453005787</v>
+        <v>-0.03763154144963066</v>
       </c>
     </row>
     <row r="213" spans="1:28">
@@ -18956,13 +18956,13 @@
         <v>76</v>
       </c>
       <c r="I213">
-        <v>764.9121740903787</v>
+        <v>766.9418076209365</v>
       </c>
       <c r="J213">
-        <v>764.9121740903787</v>
+        <v>766.9418076209365</v>
       </c>
       <c r="K213">
-        <v>5641.031366506834</v>
+        <v>5655.575575825342</v>
       </c>
       <c r="L213">
         <v>0.0626330075575434</v>
@@ -18995,7 +18995,7 @@
         <v>94.2</v>
       </c>
       <c r="V213">
-        <v>49.04799210558185</v>
+        <v>49.17813704608094</v>
       </c>
       <c r="W213">
         <v>733.3739964847293</v>
@@ -19004,16 +19004,16 @@
         <v>5535.229855810014</v>
       </c>
       <c r="Y213">
-        <v>31.53817760564937</v>
+        <v>33.56781113620718</v>
       </c>
       <c r="Z213">
-        <v>105.8015106968205</v>
+        <v>120.345720015328</v>
       </c>
       <c r="AA213">
-        <v>0.04300422125248624</v>
+        <v>0.0457717498808347</v>
       </c>
       <c r="AB213">
-        <v>0.01911420364698437</v>
+        <v>0.02174177462368757</v>
       </c>
     </row>
     <row r="214" spans="1:28">
@@ -19042,13 +19042,13 @@
         <v>77</v>
       </c>
       <c r="I214">
-        <v>4.278769876862007</v>
+        <v>4.290123251936666</v>
       </c>
       <c r="J214">
-        <v>4.278769876862007</v>
+        <v>4.290123251936666</v>
       </c>
       <c r="K214">
-        <v>31.55483191798602</v>
+        <v>31.63618939512229</v>
       </c>
       <c r="L214">
         <v>0.0003503568580970479</v>
@@ -19081,7 +19081,7 @@
         <v>14.9</v>
       </c>
       <c r="V214">
-        <v>0.4548959769193286</v>
+        <v>0.4561030071627279</v>
       </c>
       <c r="W214">
         <v>3.873454206785384</v>
@@ -19090,16 +19090,16 @@
         <v>29.23536895674183</v>
       </c>
       <c r="Y214">
-        <v>0.4053156700766238</v>
+        <v>0.416669045151282</v>
       </c>
       <c r="Z214">
-        <v>2.319462961244188</v>
+        <v>2.400820438380457</v>
       </c>
       <c r="AA214">
-        <v>0.1046393344128364</v>
+        <v>0.1075704069048694</v>
       </c>
       <c r="AB214">
-        <v>0.07933756419069606</v>
+        <v>0.08212040839754187</v>
       </c>
     </row>
     <row r="215" spans="1:28">
@@ -19128,16 +19128,16 @@
         <v>79</v>
       </c>
       <c r="I215">
-        <v>22.25634964386602</v>
+        <v>22.31540509498199</v>
       </c>
       <c r="J215">
-        <v>22.25634964386602</v>
+        <v>22.31540509498199</v>
       </c>
       <c r="K215">
-        <v>164.1348780914514</v>
+        <v>164.5580652479001</v>
       </c>
       <c r="L215">
-        <v>0.001822408065481884</v>
+        <v>0.001822408065481883</v>
       </c>
       <c r="M215">
         <v>0.001802374893977908</v>
@@ -19158,7 +19158,7 @@
         <v>106</v>
       </c>
       <c r="S215">
-        <v>83044.11764705864</v>
+        <v>83044.11764705865</v>
       </c>
       <c r="T215">
         <v>160</v>
@@ -19167,7 +19167,7 @@
         <v>7</v>
       </c>
       <c r="V215">
-        <v>1.782872204584662</v>
+        <v>1.7876029139781</v>
       </c>
       <c r="W215">
         <v>21.94957383845091</v>
@@ -19176,16 +19176,16 @@
         <v>165.6670907548734</v>
       </c>
       <c r="Y215">
-        <v>0.3067758054151071</v>
+        <v>0.3658312565310808</v>
       </c>
       <c r="Z215">
-        <v>-1.53221266342203</v>
+        <v>-1.109025506973325</v>
       </c>
       <c r="AA215">
-        <v>0.01397639005080373</v>
+        <v>0.01666689564105448</v>
       </c>
       <c r="AB215">
-        <v>-0.009248744916328268</v>
+        <v>-0.006694301818906664</v>
       </c>
     </row>
     <row r="216" spans="1:28">
@@ -19214,13 +19214,13 @@
         <v>83</v>
       </c>
       <c r="I216">
-        <v>40.58510817410864</v>
+        <v>40.69279752614366</v>
       </c>
       <c r="J216">
-        <v>40.58510817410864</v>
+        <v>40.69279752614366</v>
       </c>
       <c r="K216">
-        <v>299.3047776961762</v>
+        <v>300.0764719226415</v>
       </c>
       <c r="L216">
         <v>0.003323214707643437</v>
@@ -19253,7 +19253,7 @@
         <v>351.3</v>
       </c>
       <c r="V216">
-        <v>5.768550130103725</v>
+        <v>5.783856518422992</v>
       </c>
       <c r="W216">
         <v>40.02569347011705</v>
@@ -19262,16 +19262,16 @@
         <v>302.0988125530097</v>
       </c>
       <c r="Y216">
-        <v>0.5594147039915924</v>
+        <v>0.6671040560266093</v>
       </c>
       <c r="Z216">
-        <v>-2.794034856833434</v>
+        <v>-2.022340630368149</v>
       </c>
       <c r="AA216">
-        <v>0.01397639005078696</v>
+        <v>0.01666689564103781</v>
       </c>
       <c r="AB216">
-        <v>-0.009248744916344752</v>
+        <v>-0.00669430181892319</v>
       </c>
     </row>
     <row r="217" spans="1:28">
@@ -19300,13 +19300,13 @@
         <v>84</v>
       </c>
       <c r="I217">
-        <v>240.2892882150108</v>
+        <v>240.926876702833</v>
       </c>
       <c r="J217">
-        <v>240.2892882150108</v>
+        <v>240.926876702833</v>
       </c>
       <c r="K217">
-        <v>1772.071955147518</v>
+        <v>1776.640868838755</v>
       </c>
       <c r="L217">
         <v>0.0196755148035979</v>
@@ -19339,7 +19339,7 @@
         <v>300.2</v>
       </c>
       <c r="V217">
-        <v>21.22294777338118</v>
+        <v>21.27926117494177</v>
       </c>
       <c r="W217">
         <v>241.4453122229649</v>
@@ -19348,16 +19348,16 @@
         <v>1822.337998303645</v>
       </c>
       <c r="Y217">
-        <v>-1.156024007954102</v>
+        <v>-0.5184355201319022</v>
       </c>
       <c r="Z217">
-        <v>-50.26604315612644</v>
+        <v>-45.69712946489017</v>
       </c>
       <c r="AA217">
-        <v>-0.004787933123698673</v>
+        <v>-0.002147217170458659</v>
       </c>
       <c r="AB217">
-        <v>-0.02758327116205526</v>
+        <v>-0.02507609977261526</v>
       </c>
     </row>
     <row r="218" spans="1:28">
@@ -19386,13 +19386,13 @@
         <v>85</v>
       </c>
       <c r="I218">
-        <v>503.2117150449728</v>
+        <v>504.5469472512576</v>
       </c>
       <c r="J218">
-        <v>503.2117150449728</v>
+        <v>504.5469472512576</v>
       </c>
       <c r="K218">
-        <v>3711.057510541058</v>
+        <v>3720.625689428842</v>
       </c>
       <c r="L218">
         <v>0.04120429013819327</v>
@@ -19425,7 +19425,7 @@
         <v>1431.3</v>
       </c>
       <c r="V218">
-        <v>50.9426016969932</v>
+        <v>51.07777383314206</v>
       </c>
       <c r="W218">
         <v>522.9163179160481</v>
@@ -19434,16 +19434,16 @@
         <v>3946.774809160308</v>
       </c>
       <c r="Y218">
-        <v>-19.70460287107534</v>
+        <v>-18.36937066479055</v>
       </c>
       <c r="Z218">
-        <v>-235.71729861925</v>
+        <v>-226.1491197314663</v>
       </c>
       <c r="AA218">
-        <v>-0.03768213420763592</v>
+        <v>-0.03512870039702925</v>
       </c>
       <c r="AB218">
-        <v>-0.05972403038353226</v>
+        <v>-0.05729972716117046</v>
       </c>
     </row>
     <row r="219" spans="1:28">
@@ -19472,16 +19472,16 @@
         <v>86</v>
       </c>
       <c r="I219">
-        <v>53.67707855285407</v>
+        <v>53.81950640554555</v>
       </c>
       <c r="J219">
-        <v>53.67707855285407</v>
+        <v>53.81950640554555</v>
       </c>
       <c r="K219">
-        <v>395.8547059852706</v>
+        <v>396.8753338331763</v>
       </c>
       <c r="L219">
-        <v>0.004395219452044603</v>
+        <v>0.004395219452044604</v>
       </c>
       <c r="M219">
         <v>0.00434690415606447</v>
@@ -19511,7 +19511,7 @@
         <v>81</v>
       </c>
       <c r="V219">
-        <v>5.070962634454372</v>
+        <v>5.084418029915079</v>
       </c>
       <c r="W219">
         <v>52.93720749273581</v>
@@ -19520,16 +19520,16 @@
         <v>399.5500424088219</v>
       </c>
       <c r="Y219">
-        <v>0.7398710601182614</v>
+        <v>0.8822989128097376</v>
       </c>
       <c r="Z219">
-        <v>-3.695336423551339</v>
+        <v>-2.674708575645582</v>
       </c>
       <c r="AA219">
-        <v>0.01397639005079345</v>
+        <v>0.01666689564104433</v>
       </c>
       <c r="AB219">
-        <v>-0.009248744916338288</v>
+        <v>-0.006694301818916601</v>
       </c>
     </row>
     <row r="220" spans="1:28">
@@ -19558,13 +19558,13 @@
         <v>87</v>
       </c>
       <c r="I220">
-        <v>233.2641819118615</v>
+        <v>233.8831298396409</v>
       </c>
       <c r="J220">
-        <v>233.2641819118615</v>
+        <v>233.8831298396409</v>
       </c>
       <c r="K220">
-        <v>1720.263595506445</v>
+        <v>1724.698932272095</v>
       </c>
       <c r="L220">
         <v>0.01910028074264059</v>
@@ -19588,7 +19588,7 @@
         <v>105</v>
       </c>
       <c r="S220">
-        <v>62074.30408779224</v>
+        <v>62074.30408779222</v>
       </c>
       <c r="T220">
         <v>1400</v>
@@ -19597,7 +19597,7 @@
         <v>287.8</v>
       </c>
       <c r="V220">
-        <v>21.79983277411826</v>
+        <v>21.85767689408082</v>
       </c>
       <c r="W220">
         <v>218.2045869822508</v>
@@ -19606,16 +19606,16 @@
         <v>1646.92578456318</v>
       </c>
       <c r="Y220">
-        <v>15.05959492961077</v>
+        <v>15.67854285739014</v>
       </c>
       <c r="Z220">
-        <v>73.33781094326514</v>
+        <v>77.7731477089153</v>
       </c>
       <c r="AA220">
-        <v>0.06901594113067727</v>
+        <v>0.07185248978595243</v>
       </c>
       <c r="AB220">
-        <v>0.04453012493378188</v>
+        <v>0.04722322550165389</v>
       </c>
     </row>
     <row r="221" spans="1:28">
@@ -19644,13 +19644,13 @@
         <v>88</v>
       </c>
       <c r="I221">
-        <v>3099.300439883713</v>
+        <v>3107.524186749217</v>
       </c>
       <c r="J221">
-        <v>3099.300439883713</v>
+        <v>3107.524186749217</v>
       </c>
       <c r="K221">
-        <v>22856.54691847891</v>
+        <v>22915.47770277741</v>
       </c>
       <c r="L221">
         <v>0.2537788186012033</v>
@@ -19674,7 +19674,7 @@
         <v>105</v>
       </c>
       <c r="S221">
-        <v>52700.4810891475</v>
+        <v>52700.48108914749</v>
       </c>
       <c r="T221">
         <v>25060</v>
@@ -19683,7 +19683,7 @@
         <v>563.3000000000001</v>
       </c>
       <c r="V221">
-        <v>302.8940844018373</v>
+        <v>303.6977897300218</v>
       </c>
       <c r="W221">
         <v>3128.459847680459</v>
@@ -19692,16 +19692,16 @@
         <v>23612.43299406281</v>
       </c>
       <c r="Y221">
-        <v>-29.15940779674565</v>
+        <v>-20.93566093124218</v>
       </c>
       <c r="Z221">
-        <v>-755.8860755838978</v>
+        <v>-696.9552912853978</v>
       </c>
       <c r="AA221">
-        <v>-0.0093206910801062</v>
+        <v>-0.006692002439080225</v>
       </c>
       <c r="AB221">
-        <v>-0.03201220627175354</v>
+        <v>-0.02951645395714379</v>
       </c>
     </row>
     <row r="222" spans="1:28">
@@ -19730,16 +19730,16 @@
         <v>89</v>
       </c>
       <c r="I222">
-        <v>165.1847611915935</v>
+        <v>165.6230657988516</v>
       </c>
       <c r="J222">
-        <v>165.1847611915935</v>
+        <v>165.6230657988516</v>
       </c>
       <c r="K222">
-        <v>1218.195304916955</v>
+        <v>1221.336164514144</v>
       </c>
       <c r="L222">
-        <v>0.01352575988009003</v>
+        <v>0.01352575988009002</v>
       </c>
       <c r="M222">
         <v>0.01335877862595411</v>
@@ -19760,7 +19760,7 @@
         <v>105</v>
       </c>
       <c r="S222">
-        <v>43022.10738988892</v>
+        <v>43022.10738988893</v>
       </c>
       <c r="T222">
         <v>1220</v>
@@ -19769,7 +19769,7 @@
         <v>1352.1</v>
       </c>
       <c r="V222">
-        <v>20.18455773173556</v>
+        <v>20.23811584802588</v>
       </c>
       <c r="W222">
         <v>162.6850766849916</v>
@@ -19778,16 +19778,16 @@
         <v>1227.885496183198</v>
       </c>
       <c r="Y222">
-        <v>2.499684506601938</v>
+        <v>2.937989113860027</v>
       </c>
       <c r="Z222">
-        <v>-9.690191266243801</v>
+        <v>-6.549331669054936</v>
       </c>
       <c r="AA222">
-        <v>0.01536517397623444</v>
+        <v>0.01805936459401792</v>
       </c>
       <c r="AB222">
-        <v>-0.007891771094589132</v>
+        <v>-0.005333829326442168</v>
       </c>
     </row>
     <row r="223" spans="1:28">
@@ -24374,16 +24374,16 @@
         <v>72</v>
       </c>
       <c r="I276">
-        <v>7627.794099891538</v>
+        <v>7692.791672386667</v>
       </c>
       <c r="J276">
-        <v>7627.794099891538</v>
+        <v>7692.791672386667</v>
       </c>
       <c r="K276">
-        <v>14010.17594989923</v>
+        <v>14119.27314513533</v>
       </c>
       <c r="L276">
-        <v>0.5000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M276">
         <v>0.4999999999999999</v>
@@ -24404,7 +24404,7 @@
         <v>105</v>
       </c>
       <c r="S276">
-        <v>58229.86391943943</v>
+        <v>58229.86391943944</v>
       </c>
       <c r="T276">
         <v>14030</v>
@@ -24413,7 +24413,7 @@
         <v>4992.900000000001</v>
       </c>
       <c r="V276">
-        <v>721.2867600920292</v>
+        <v>727.4329522761529</v>
       </c>
       <c r="W276">
         <v>8874.553681709272</v>
@@ -24422,16 +24422,16 @@
         <v>15947</v>
       </c>
       <c r="Y276">
-        <v>-1246.759581817734</v>
+        <v>-1181.762009322605</v>
       </c>
       <c r="Z276">
-        <v>-1936.824050100775</v>
+        <v>-1827.726854864668</v>
       </c>
       <c r="AA276">
-        <v>-0.1404870178865833</v>
+        <v>-0.133162979424898</v>
       </c>
       <c r="AB276">
-        <v>-0.121453818906426</v>
+        <v>-0.1146125826089338</v>
       </c>
     </row>
     <row r="277" spans="1:28">
@@ -24460,13 +24460,13 @@
         <v>73</v>
       </c>
       <c r="I277">
-        <v>474.9824366934012</v>
+        <v>479.0298329600797</v>
       </c>
       <c r="J277">
-        <v>474.9824366934012</v>
+        <v>479.0298329600797</v>
       </c>
       <c r="K277">
-        <v>872.4131018797484</v>
+        <v>879.2065799090517</v>
       </c>
       <c r="L277">
         <v>0.03113498021008165</v>
@@ -24499,7 +24499,7 @@
         <v>600.3</v>
       </c>
       <c r="V277">
-        <v>35.69116618211661</v>
+        <v>35.99529593850199</v>
       </c>
       <c r="W277">
         <v>535.1489657312111</v>
@@ -24508,16 +24508,16 @@
         <v>961.6281407035149</v>
       </c>
       <c r="Y277">
-        <v>-60.16652903780994</v>
+        <v>-56.11913277113143</v>
       </c>
       <c r="Z277">
-        <v>-89.21503882376646</v>
+        <v>-82.42156079446318</v>
       </c>
       <c r="AA277">
-        <v>-0.1124294970010831</v>
+        <v>-0.1048663762144284</v>
       </c>
       <c r="AB277">
-        <v>-0.09277498759395485</v>
+        <v>-0.08571042932891358</v>
       </c>
     </row>
     <row r="278" spans="1:28">
@@ -24546,13 +24546,13 @@
         <v>74</v>
       </c>
       <c r="I278">
-        <v>227.8027926312167</v>
+        <v>229.7439342423741</v>
       </c>
       <c r="J278">
-        <v>227.8027926312167</v>
+        <v>229.7439342423741</v>
       </c>
       <c r="K278">
-        <v>418.4115571089069</v>
+        <v>421.6697265636085</v>
       </c>
       <c r="L278">
         <v>0.01493241621679693</v>
@@ -24585,7 +24585,7 @@
         <v>456.9</v>
       </c>
       <c r="V278">
-        <v>19.21903604393857</v>
+        <v>19.38280431982454</v>
       </c>
       <c r="W278">
         <v>256.425546079537</v>
@@ -24594,16 +24594,16 @@
         <v>460.7801507537647</v>
       </c>
       <c r="Y278">
-        <v>-28.62275344832034</v>
+        <v>-26.6816118371629</v>
       </c>
       <c r="Z278">
-        <v>-42.36859364485775</v>
+        <v>-39.11042419015621</v>
       </c>
       <c r="AA278">
-        <v>-0.1116220824560212</v>
+        <v>-0.1040520815694662</v>
       </c>
       <c r="AB278">
-        <v>-0.09194969352640152</v>
+        <v>-0.08487870869910007</v>
       </c>
     </row>
     <row r="279" spans="1:28">
@@ -24632,16 +24632,16 @@
         <v>75</v>
       </c>
       <c r="I279">
-        <v>40.11281598686918</v>
+        <v>40.4546232814745</v>
       </c>
       <c r="J279">
-        <v>40.11281598686918</v>
+        <v>40.4546232814745</v>
       </c>
       <c r="K279">
-        <v>73.67629519915316</v>
+        <v>74.25001227382509</v>
       </c>
       <c r="L279">
-        <v>0.002629385079196065</v>
+        <v>0.002629385079196066</v>
       </c>
       <c r="M279">
         <v>0.002826633165829108</v>
@@ -24671,7 +24671,7 @@
         <v>55.09999999999999</v>
       </c>
       <c r="V279">
-        <v>2.10607467872771</v>
+        <v>2.124020855540835</v>
       </c>
       <c r="W279">
         <v>50.17021553730051</v>
@@ -24680,16 +24680,16 @@
         <v>90.15263819095358</v>
       </c>
       <c r="Y279">
-        <v>-10.05739955043133</v>
+        <v>-9.715592255826003</v>
       </c>
       <c r="Z279">
-        <v>-16.47634299180042</v>
+        <v>-15.90262591712849</v>
       </c>
       <c r="AA279">
-        <v>-0.2004655440029725</v>
+        <v>-0.1936525915182219</v>
       </c>
       <c r="AB279">
-        <v>-0.1827605195191476</v>
+        <v>-0.1763966783029124</v>
       </c>
     </row>
     <row r="280" spans="1:28">
@@ -24718,16 +24718,16 @@
         <v>76</v>
       </c>
       <c r="I280">
-        <v>324.5330194442205</v>
+        <v>327.2984137616535</v>
       </c>
       <c r="J280">
-        <v>324.5330194442205</v>
+        <v>327.2984137616535</v>
       </c>
       <c r="K280">
-        <v>596.0785837192757</v>
+        <v>600.720245740983</v>
       </c>
       <c r="L280">
-        <v>0.02127305844876143</v>
+        <v>0.02127305844876142</v>
       </c>
       <c r="M280">
         <v>0.02010050251256281</v>
@@ -24748,7 +24748,7 @@
         <v>106</v>
       </c>
       <c r="S280">
-        <v>95119.05979192947</v>
+        <v>95119.05979192948</v>
       </c>
       <c r="T280">
         <v>740</v>
@@ -24757,7 +24757,7 @@
         <v>52.89999999999999</v>
       </c>
       <c r="V280">
-        <v>22.52997888309799</v>
+        <v>22.72196019730109</v>
       </c>
       <c r="W280">
         <v>356.7659771541416</v>
@@ -24766,16 +24766,16 @@
         <v>641.0854271356783</v>
       </c>
       <c r="Y280">
-        <v>-32.23295770992115</v>
+        <v>-29.46756339248816</v>
       </c>
       <c r="Z280">
-        <v>-45.0068434164026</v>
+        <v>-40.36518139469524</v>
       </c>
       <c r="AA280">
-        <v>-0.09034762217809469</v>
+        <v>-0.08259633843884341</v>
       </c>
       <c r="AB280">
-        <v>-0.07020412804809775</v>
+        <v>-0.0629638105720853</v>
       </c>
     </row>
     <row r="281" spans="1:28">
@@ -24804,13 +24804,13 @@
         <v>77</v>
       </c>
       <c r="I281">
-        <v>25.63191513198404</v>
+        <v>25.85032850814004</v>
       </c>
       <c r="J281">
-        <v>25.63191513198404</v>
+        <v>25.85032850814004</v>
       </c>
       <c r="K281">
-        <v>47.07883252080534</v>
+        <v>47.44543523881384</v>
       </c>
       <c r="L281">
         <v>0.001680165641358129</v>
@@ -24834,7 +24834,7 @@
         <v>106</v>
       </c>
       <c r="S281">
-        <v>83910</v>
+        <v>83909.99999999999</v>
       </c>
       <c r="T281">
         <v>0</v>
@@ -24843,7 +24843,7 @@
         <v>14.9</v>
       </c>
       <c r="V281">
-        <v>2.725048415744289</v>
+        <v>2.748268960194696</v>
       </c>
       <c r="W281">
         <v>27.87234196516705</v>
@@ -24852,16 +24852,16 @@
         <v>50.08479899497438</v>
       </c>
       <c r="Y281">
-        <v>-2.240426833183005</v>
+        <v>-2.022013457027004</v>
       </c>
       <c r="Z281">
-        <v>-3.00596647416905</v>
+        <v>-2.639363756160549</v>
       </c>
       <c r="AA281">
-        <v>-0.0803817216358402</v>
+        <v>-0.07254551696997615</v>
       </c>
       <c r="AB281">
-        <v>-0.06001754094032952</v>
+        <v>-0.0526979005431446</v>
       </c>
     </row>
     <row r="282" spans="1:28">
@@ -24890,13 +24890,13 @@
         <v>83</v>
       </c>
       <c r="I282">
-        <v>38.89601445543148</v>
+        <v>39.22745320249657</v>
       </c>
       <c r="J282">
-        <v>38.89601445543148</v>
+        <v>39.22745320249657</v>
       </c>
       <c r="K282">
-        <v>71.44136288080551</v>
+        <v>71.99767654467475</v>
       </c>
       <c r="L282">
         <v>0.002549624042420374</v>
@@ -24929,7 +24929,7 @@
         <v>351.3</v>
       </c>
       <c r="V282">
-        <v>5.528471386224744</v>
+        <v>5.575580316409226</v>
       </c>
       <c r="W282">
         <v>44.59574714426781</v>
@@ -24938,16 +24938,16 @@
         <v>80.13567839195998</v>
       </c>
       <c r="Y282">
-        <v>-5.699732688836335</v>
+        <v>-5.368293941771242</v>
       </c>
       <c r="Z282">
-        <v>-8.694315511154471</v>
+        <v>-8.138001847285238</v>
       </c>
       <c r="AA282">
-        <v>-0.1278088843404199</v>
+        <v>-0.1203768136097091</v>
       </c>
       <c r="AB282">
-        <v>-0.1084949386542758</v>
+        <v>-0.1015527915977776</v>
       </c>
     </row>
     <row r="283" spans="1:28">
@@ -24976,13 +24976,13 @@
         <v>84</v>
       </c>
       <c r="I283">
-        <v>91.76752495677326</v>
+        <v>92.54948973950924</v>
       </c>
       <c r="J283">
-        <v>91.76752495677326</v>
+        <v>92.54948973950924</v>
       </c>
       <c r="K283">
-        <v>168.5518977432077</v>
+        <v>169.864410830928</v>
       </c>
       <c r="L283">
         <v>0.006015338363556388</v>
@@ -25015,7 +25015,7 @@
         <v>114.8</v>
       </c>
       <c r="V283">
-        <v>8.025376601689318</v>
+        <v>8.093762034048648</v>
       </c>
       <c r="W283">
         <v>105.9148994676355</v>
@@ -25024,16 +25024,16 @@
         <v>190.3222361809039</v>
       </c>
       <c r="Y283">
-        <v>-14.14737451086222</v>
+        <v>-13.36540972812624</v>
       </c>
       <c r="Z283">
-        <v>-21.77033843769624</v>
+        <v>-20.45782534997591</v>
       </c>
       <c r="AA283">
-        <v>-0.1335730344075457</v>
+        <v>-0.1261900808602506</v>
       </c>
       <c r="AB283">
-        <v>-0.1143867310228702</v>
+        <v>-0.1074904633346703</v>
       </c>
     </row>
     <row r="284" spans="1:28">
@@ -25062,13 +25062,13 @@
         <v>85</v>
       </c>
       <c r="I284">
-        <v>451.4304188373958</v>
+        <v>455.2771248431738</v>
       </c>
       <c r="J284">
-        <v>451.4304188373958</v>
+        <v>455.2771248431738</v>
       </c>
       <c r="K284">
-        <v>829.1544730000708</v>
+        <v>835.6110962248799</v>
       </c>
       <c r="L284">
         <v>0.02959115131619867</v>
@@ -25101,7 +25101,7 @@
         <v>1244.8</v>
       </c>
       <c r="V284">
-        <v>43.9970537503566</v>
+        <v>44.37195921493274</v>
       </c>
       <c r="W284">
         <v>540.7234341242455</v>
@@ -25110,16 +25110,16 @@
         <v>971.6451005025117</v>
       </c>
       <c r="Y284">
-        <v>-89.29301528684971</v>
+        <v>-85.44630928107171</v>
       </c>
       <c r="Z284">
-        <v>-142.4906275024409</v>
+        <v>-136.0340042776318</v>
       </c>
       <c r="AA284">
-        <v>-0.1651362039292203</v>
+        <v>-0.158022204862381</v>
       </c>
       <c r="AB284">
-        <v>-0.1466488406402175</v>
+        <v>-0.1400037978962465</v>
       </c>
     </row>
     <row r="285" spans="1:28">
@@ -25148,13 +25148,13 @@
         <v>86</v>
       </c>
       <c r="I285">
-        <v>39.56667229286086</v>
+        <v>39.90382581550023</v>
       </c>
       <c r="J285">
-        <v>39.56667229286086</v>
+        <v>39.90382581550023</v>
       </c>
       <c r="K285">
-        <v>72.67317828923377</v>
+        <v>73.23908409574194</v>
       </c>
       <c r="L285">
         <v>0.002593585496324781</v>
@@ -25178,7 +25178,7 @@
         <v>105</v>
       </c>
       <c r="S285">
-        <v>62350</v>
+        <v>62350.00000000001</v>
       </c>
       <c r="T285">
         <v>130</v>
@@ -25187,7 +25187,7 @@
         <v>81</v>
       </c>
       <c r="V285">
-        <v>3.737929152929472</v>
+        <v>3.769780605383156</v>
       </c>
       <c r="W285">
         <v>44.59574714426781</v>
@@ -25196,16 +25196,16 @@
         <v>80.13567839195998</v>
       </c>
       <c r="Y285">
-        <v>-5.029074851406953</v>
+        <v>-4.691921328767577</v>
       </c>
       <c r="Z285">
-        <v>-7.46250010272621</v>
+        <v>-6.896594296218041</v>
       </c>
       <c r="AA285">
-        <v>-0.1127702790837393</v>
+        <v>-0.1052100621520961</v>
       </c>
       <c r="AB285">
-        <v>-0.09312331601194659</v>
+        <v>-0.08606147017918021</v>
       </c>
     </row>
     <row r="286" spans="1:28">
@@ -25234,13 +25234,13 @@
         <v>87</v>
       </c>
       <c r="I286">
-        <v>517.8670935759575</v>
+        <v>522.2799164074003</v>
       </c>
       <c r="J286">
-        <v>517.8670935759575</v>
+        <v>522.2799164074003</v>
       </c>
       <c r="K286">
-        <v>951.1805123010934</v>
+        <v>958.5873519029931</v>
       </c>
       <c r="L286">
         <v>0.03394605876837455</v>
@@ -25264,7 +25264,7 @@
         <v>105</v>
       </c>
       <c r="S286">
-        <v>61945.38130196332</v>
+        <v>61945.38130196331</v>
       </c>
       <c r="T286">
         <v>760</v>
@@ -25273,7 +25273,7 @@
         <v>257.9</v>
       </c>
       <c r="V286">
-        <v>49.2229760066168</v>
+        <v>49.64241233506484</v>
       </c>
       <c r="W286">
         <v>563.0213076963798</v>
@@ -25282,16 +25282,16 @@
         <v>1011.712939698492</v>
       </c>
       <c r="Y286">
-        <v>-45.15421412042235</v>
+        <v>-40.74139128897957</v>
       </c>
       <c r="Z286">
-        <v>-60.53242739739903</v>
+        <v>-53.12558779549931</v>
       </c>
       <c r="AA286">
-        <v>-0.08019983169939394</v>
+        <v>-0.07236207712222173</v>
       </c>
       <c r="AB286">
-        <v>-0.05983162320276216</v>
+        <v>-0.05251053506475032</v>
       </c>
     </row>
     <row r="287" spans="1:28">
@@ -25320,16 +25320,16 @@
         <v>88</v>
       </c>
       <c r="I287">
-        <v>4904.362671585235</v>
+        <v>4946.153478221366</v>
       </c>
       <c r="J287">
-        <v>4904.362671585235</v>
+        <v>4946.153478221366</v>
       </c>
       <c r="K287">
-        <v>9007.975707158117</v>
+        <v>9078.120785130035</v>
       </c>
       <c r="L287">
-        <v>0.3214797494111025</v>
+        <v>0.3214797494111026</v>
       </c>
       <c r="M287">
         <v>0.3263190954773874</v>
@@ -25350,7 +25350,7 @@
         <v>105</v>
       </c>
       <c r="S287">
-        <v>49356.13398353081</v>
+        <v>49356.1339835308</v>
       </c>
       <c r="T287">
         <v>9330</v>
@@ -25359,7 +25359,7 @@
         <v>531.1</v>
       </c>
       <c r="V287">
-        <v>470.1239267685874</v>
+        <v>474.1299229467315</v>
       </c>
       <c r="W287">
         <v>5791.872660361776</v>
@@ -25368,16 +25368,16 @@
         <v>10407.62123115579</v>
       </c>
       <c r="Y287">
-        <v>-887.5099887765409</v>
+        <v>-845.7191821404103</v>
       </c>
       <c r="Z287">
-        <v>-1399.645523997671</v>
+        <v>-1329.500446025753</v>
       </c>
       <c r="AA287">
-        <v>-0.1532336846509855</v>
+        <v>-0.1460182624401111</v>
       </c>
       <c r="AB287">
-        <v>-0.1344827499878411</v>
+        <v>-0.1277429699349377</v>
       </c>
     </row>
     <row r="288" spans="1:28">
@@ -25406,13 +25406,13 @@
         <v>89</v>
       </c>
       <c r="I288">
-        <v>490.8407243001908</v>
+        <v>495.0232514035008</v>
       </c>
       <c r="J288">
-        <v>490.8407243001908</v>
+        <v>495.0232514035008</v>
       </c>
       <c r="K288">
-        <v>901.5404480988065</v>
+        <v>908.5607406797994</v>
       </c>
       <c r="L288">
         <v>0.03217448700582848</v>
@@ -25445,7 +25445,7 @@
         <v>1231.9</v>
       </c>
       <c r="V288">
-        <v>58.37972222199978</v>
+        <v>58.87718455221974</v>
       </c>
       <c r="W288">
         <v>557.4468393033463</v>
@@ -25454,16 +25454,16 @@
         <v>1001.695979899497</v>
       </c>
       <c r="Y288">
-        <v>-66.60611500315554</v>
+        <v>-62.42358789984559</v>
       </c>
       <c r="Z288">
-        <v>-100.1555318006909</v>
+        <v>-93.13523921969795</v>
       </c>
       <c r="AA288">
-        <v>-0.1194842455047277</v>
+        <v>-0.1119812392834763</v>
       </c>
       <c r="AB288">
-        <v>-0.09998595762632469</v>
+        <v>-0.092977551161823</v>
       </c>
     </row>
     <row r="289" spans="1:28">
@@ -29964,16 +29964,16 @@
         <v>72</v>
       </c>
       <c r="I341">
-        <v>14141.45016947364</v>
+        <v>14200.3378131718</v>
       </c>
       <c r="J341">
-        <v>14141.45016947364</v>
+        <v>14200.3378131718</v>
       </c>
       <c r="K341">
-        <v>48045.64526115706</v>
+        <v>48239.14076759229</v>
       </c>
       <c r="L341">
-        <v>0.5000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M341">
         <v>0.5</v>
@@ -29994,7 +29994,7 @@
         <v>105</v>
       </c>
       <c r="S341">
-        <v>60557.44929794789</v>
+        <v>60557.4492979479</v>
       </c>
       <c r="T341">
         <v>45610</v>
@@ -30003,7 +30003,7 @@
         <v>5975.7</v>
       </c>
       <c r="V341">
-        <v>1357.479609714771</v>
+        <v>1363.132408729469</v>
       </c>
       <c r="W341">
         <v>14602.46596485234</v>
@@ -30012,16 +30012,16 @@
         <v>49288.99999999999</v>
       </c>
       <c r="Y341">
-        <v>-461.0157953786966</v>
+        <v>-402.1281516805375</v>
       </c>
       <c r="Z341">
-        <v>-1243.354738842929</v>
+        <v>-1049.859232407704</v>
       </c>
       <c r="AA341">
-        <v>-0.03157109192983888</v>
+        <v>-0.02753837280966426</v>
       </c>
       <c r="AB341">
-        <v>-0.02522580573440177</v>
+        <v>-0.02130007166726255</v>
       </c>
     </row>
     <row r="342" spans="1:28">
@@ -30050,16 +30050,16 @@
         <v>73</v>
       </c>
       <c r="I342">
-        <v>984.2027635676066</v>
+        <v>988.3011679726103</v>
       </c>
       <c r="J342">
-        <v>984.2027635676066</v>
+        <v>988.3011679726103</v>
       </c>
       <c r="K342">
-        <v>3343.833643419028</v>
+        <v>3357.300353684892</v>
       </c>
       <c r="L342">
-        <v>0.03479850905574558</v>
+        <v>0.03479850905574557</v>
       </c>
       <c r="M342">
         <v>0.0340887081154367</v>
@@ -30080,7 +30080,7 @@
         <v>106</v>
       </c>
       <c r="S342">
-        <v>125384.7818500341</v>
+        <v>125384.7818500342</v>
       </c>
       <c r="T342">
         <v>3400</v>
@@ -30089,7 +30089,7 @@
         <v>620.8999999999999</v>
       </c>
       <c r="V342">
-        <v>74.11206022560107</v>
+        <v>74.42067670722066</v>
       </c>
       <c r="W342">
         <v>995.5584000829002</v>
@@ -30098,16 +30098,16 @@
         <v>3360.39666860352</v>
       </c>
       <c r="Y342">
-        <v>-11.35563651529367</v>
+        <v>-7.25723211028992</v>
       </c>
       <c r="Z342">
-        <v>-16.56302518449229</v>
+        <v>-3.096314918628195</v>
       </c>
       <c r="AA342">
-        <v>-0.01140629873079076</v>
+        <v>-0.007289609639862021</v>
       </c>
       <c r="AB342">
-        <v>-0.004928889895422788</v>
+        <v>-0.0009214135186947828</v>
       </c>
     </row>
     <row r="343" spans="1:28">
@@ -30136,13 +30136,13 @@
         <v>74</v>
       </c>
       <c r="I343">
-        <v>661.940635124747</v>
+        <v>664.697079747004</v>
       </c>
       <c r="J343">
-        <v>661.940635124747</v>
+        <v>664.697079747004</v>
       </c>
       <c r="K343">
-        <v>2248.946505345029</v>
+        <v>2258.003747486998</v>
       </c>
       <c r="L343">
         <v>0.02340426997203022</v>
@@ -30175,7 +30175,7 @@
         <v>634</v>
       </c>
       <c r="V343">
-        <v>58.04348406668758</v>
+        <v>58.28518799151541</v>
       </c>
       <c r="W343">
         <v>656.1634909637276</v>
@@ -30184,16 +30184,16 @@
         <v>2214.806895215949</v>
       </c>
       <c r="Y343">
-        <v>5.777144161019464</v>
+        <v>8.5335887832764</v>
       </c>
       <c r="Z343">
-        <v>34.13961012908021</v>
+        <v>43.19685227104947</v>
       </c>
       <c r="AA343">
-        <v>0.008804427921666892</v>
+        <v>0.01300527825884195</v>
       </c>
       <c r="AB343">
-        <v>0.01541426035959289</v>
+        <v>0.0195036652470046</v>
       </c>
     </row>
     <row r="344" spans="1:28">
@@ -30222,13 +30222,13 @@
         <v>75</v>
       </c>
       <c r="I344">
-        <v>117.9511964108474</v>
+        <v>118.4423672557588</v>
       </c>
       <c r="J344">
-        <v>117.9511964108474</v>
+        <v>118.4423672557588</v>
       </c>
       <c r="K344">
-        <v>400.7397595699034</v>
+        <v>402.353669473813</v>
       </c>
       <c r="L344">
         <v>0.004170406676730441</v>
@@ -30261,7 +30261,7 @@
         <v>235.8</v>
       </c>
       <c r="V344">
-        <v>6.849207701113514</v>
+        <v>6.877729083141825</v>
       </c>
       <c r="W344">
         <v>118.7882181917071</v>
@@ -30270,16 +30270,16 @@
         <v>400.9564206856386</v>
       </c>
       <c r="Y344">
-        <v>-0.8370217808597573</v>
+        <v>-0.3458509359482775</v>
       </c>
       <c r="Z344">
-        <v>-0.2166611157352349</v>
+        <v>1.397248788174409</v>
       </c>
       <c r="AA344">
-        <v>-0.007046336695689167</v>
+        <v>-0.002911491907304509</v>
       </c>
       <c r="AB344">
-        <v>-0.0005403607588194816</v>
+        <v>0.003484789658150635</v>
       </c>
     </row>
     <row r="345" spans="1:28">
@@ -30308,16 +30308,16 @@
         <v>76</v>
       </c>
       <c r="I345">
-        <v>969.2825966671958</v>
+        <v>973.3188707063733</v>
       </c>
       <c r="J345">
-        <v>969.2825966671958</v>
+        <v>973.3188707063733</v>
       </c>
       <c r="K345">
-        <v>3293.142304302916</v>
+        <v>3306.404863989037</v>
       </c>
       <c r="L345">
-        <v>0.03427097592719069</v>
+        <v>0.03427097592719071</v>
       </c>
       <c r="M345">
         <v>0.03215184969978684</v>
@@ -30338,7 +30338,7 @@
         <v>106</v>
       </c>
       <c r="S345">
-        <v>94721.4437781655</v>
+        <v>94721.44377816549</v>
       </c>
       <c r="T345">
         <v>3200</v>
@@ -30347,7 +30347,7 @@
         <v>114.8</v>
       </c>
       <c r="V345">
-        <v>67.20951417941842</v>
+        <v>67.48938716816379</v>
       </c>
       <c r="W345">
         <v>938.9925818963704</v>
@@ -30356,16 +30356,16 @@
         <v>3169.465039705588</v>
       </c>
       <c r="Y345">
-        <v>30.29001477082534</v>
+        <v>34.32628881000289</v>
       </c>
       <c r="Z345">
-        <v>123.6772645973278</v>
+        <v>136.9398242834495</v>
       </c>
       <c r="AA345">
-        <v>0.03225799154840205</v>
+        <v>0.03655650691156496</v>
       </c>
       <c r="AB345">
-        <v>0.03902149512550428</v>
+        <v>0.04320597405806056</v>
       </c>
     </row>
     <row r="346" spans="1:28">
@@ -30394,13 +30394,13 @@
         <v>77</v>
       </c>
       <c r="I346">
-        <v>37.7073792109716</v>
+        <v>37.86439979126261</v>
       </c>
       <c r="J346">
-        <v>37.7073792109716</v>
+        <v>37.86439979126261</v>
       </c>
       <c r="K346">
-        <v>128.1110030150255</v>
+        <v>128.6269478685824</v>
       </c>
       <c r="L346">
         <v>0.001333221796883619</v>
@@ -30433,7 +30433,7 @@
         <v>25.5</v>
       </c>
       <c r="V346">
-        <v>4.322623713985214</v>
+        <v>4.340623927687474</v>
       </c>
       <c r="W346">
         <v>36.76778182124136</v>
@@ -30442,16 +30442,16 @@
         <v>124.1055587836456</v>
       </c>
       <c r="Y346">
-        <v>0.9395973897302383</v>
+        <v>1.096617970021256</v>
       </c>
       <c r="Z346">
-        <v>4.005444231379926</v>
+        <v>4.521389084936885</v>
       </c>
       <c r="AA346">
-        <v>0.02555491093529655</v>
+        <v>0.02982551341695903</v>
       </c>
       <c r="AB346">
-        <v>0.03227449495926815</v>
+        <v>0.03643180151840795</v>
       </c>
     </row>
     <row r="347" spans="1:28">
@@ -30480,13 +30480,13 @@
         <v>83</v>
       </c>
       <c r="I347">
-        <v>49.98318772276857</v>
+        <v>50.19132706592239</v>
       </c>
       <c r="J347">
-        <v>49.98318772276857</v>
+        <v>50.19132706592239</v>
       </c>
       <c r="K347">
-        <v>169.8181217322315</v>
+        <v>170.5020347755021</v>
       </c>
       <c r="L347">
         <v>0.001767258206328248</v>
@@ -30519,7 +30519,7 @@
         <v>351.3</v>
       </c>
       <c r="V347">
-        <v>7.10434287385038</v>
+        <v>7.133926686461619</v>
       </c>
       <c r="W347">
         <v>50.90923636787489</v>
@@ -30528,16 +30528,16 @@
         <v>171.8384660081322</v>
       </c>
       <c r="Y347">
-        <v>-0.9260486451063201</v>
+        <v>-0.7179093019524956</v>
       </c>
       <c r="Z347">
-        <v>-2.020344275900726</v>
+        <v>-1.336431232630133</v>
       </c>
       <c r="AA347">
-        <v>-0.01819018926967606</v>
+        <v>-0.01410174956789405</v>
       </c>
       <c r="AB347">
-        <v>-0.01175722946575369</v>
+        <v>-0.007777253042790122</v>
       </c>
     </row>
     <row r="348" spans="1:28">
@@ -30566,13 +30566,13 @@
         <v>84</v>
       </c>
       <c r="I348">
-        <v>310.2929249797538</v>
+        <v>311.585042760412</v>
       </c>
       <c r="J348">
-        <v>310.2929249797538</v>
+        <v>311.585042760412</v>
       </c>
       <c r="K348">
-        <v>1054.22171149078</v>
+        <v>1058.467406659428</v>
       </c>
       <c r="L348">
         <v>0.01097104332515932</v>
@@ -30596,7 +30596,7 @@
         <v>105</v>
       </c>
       <c r="S348">
-        <v>76949.98845922104</v>
+        <v>76949.98845922107</v>
       </c>
       <c r="T348">
         <v>930</v>
@@ -30605,7 +30605,7 @@
         <v>147</v>
       </c>
       <c r="V348">
-        <v>27.16838671853815</v>
+        <v>27.28152096274662</v>
       </c>
       <c r="W348">
         <v>322.4251636632125</v>
@@ -30614,16 +30614,16 @@
         <v>1088.310284718187</v>
       </c>
       <c r="Y348">
-        <v>-12.1322386834587</v>
+        <v>-10.84012090280055</v>
       </c>
       <c r="Z348">
-        <v>-34.08857322740732</v>
+        <v>-29.84287805875852</v>
       </c>
       <c r="AA348">
-        <v>-0.037628076374744</v>
+        <v>-0.03362057967077142</v>
       </c>
       <c r="AB348">
-        <v>-0.03132247641694795</v>
+        <v>-0.02742129563398015</v>
       </c>
     </row>
     <row r="349" spans="1:28">
@@ -30652,13 +30652,13 @@
         <v>85</v>
       </c>
       <c r="I349">
-        <v>1049.530142983643</v>
+        <v>1053.90058281618</v>
       </c>
       <c r="J349">
-        <v>1049.530142983643</v>
+        <v>1053.90058281618</v>
       </c>
       <c r="K349">
-        <v>3565.783730549359</v>
+        <v>3580.14430631082</v>
       </c>
       <c r="L349">
         <v>0.03710829265760895</v>
@@ -30682,7 +30682,7 @@
         <v>105</v>
       </c>
       <c r="S349">
-        <v>47330.03959590689</v>
+        <v>47330.0395959069</v>
       </c>
       <c r="T349">
         <v>4100</v>
@@ -30691,7 +30691,7 @@
         <v>1435.9</v>
       </c>
       <c r="V349">
-        <v>103.4222061859705</v>
+        <v>103.8528755979028</v>
       </c>
       <c r="W349">
         <v>1134.144654639896</v>
@@ -30700,16 +30700,16 @@
         <v>3828.179159403444</v>
       </c>
       <c r="Y349">
-        <v>-84.61451165625249</v>
+        <v>-80.24407182371579</v>
       </c>
       <c r="Z349">
-        <v>-262.3954288540849</v>
+        <v>-248.0348530926244</v>
       </c>
       <c r="AA349">
-        <v>-0.07460645457357341</v>
+        <v>-0.07075294275331591</v>
       </c>
       <c r="AB349">
-        <v>-0.06854314229508911</v>
+        <v>-0.0647918612908588</v>
       </c>
     </row>
     <row r="350" spans="1:28">
@@ -30738,13 +30738,13 @@
         <v>86</v>
       </c>
       <c r="I350">
-        <v>32.14853433365838</v>
+        <v>32.28240684408487</v>
       </c>
       <c r="J350">
-        <v>32.14853433365838</v>
+        <v>32.28240684408487</v>
       </c>
       <c r="K350">
-        <v>109.2248006923162</v>
+        <v>109.6646846403903</v>
       </c>
       <c r="L350">
         <v>0.001136677425171558</v>
@@ -30777,7 +30777,7 @@
         <v>81</v>
       </c>
       <c r="V350">
-        <v>3.037125356923639</v>
+        <v>3.049772515011516</v>
       </c>
       <c r="W350">
         <v>33.93949091191611</v>
@@ -30786,16 +30786,16 @@
         <v>114.5589773387532</v>
       </c>
       <c r="Y350">
-        <v>-1.790956578257735</v>
+        <v>-1.657084067831242</v>
       </c>
       <c r="Z350">
-        <v>-5.334176646437015</v>
+        <v>-4.894292698362904</v>
       </c>
       <c r="AA350">
-        <v>-0.05276910555039976</v>
+        <v>-0.04882465892408074</v>
       </c>
       <c r="AB350">
-        <v>-0.04656271180445116</v>
+        <v>-0.04272290842724951</v>
       </c>
     </row>
     <row r="351" spans="1:28">
@@ -30824,13 +30824,13 @@
         <v>87</v>
       </c>
       <c r="I351">
-        <v>498.1795344562497</v>
+        <v>500.2540472234131</v>
       </c>
       <c r="J351">
-        <v>498.1795344562497</v>
+        <v>500.2540472234131</v>
       </c>
       <c r="K351">
-        <v>1692.567374774708</v>
+        <v>1699.383896429847</v>
       </c>
       <c r="L351">
         <v>0.01761416009270542</v>
@@ -30863,7 +30863,7 @@
         <v>262.7</v>
       </c>
       <c r="V351">
-        <v>47.31884993257182</v>
+        <v>47.51589447479644</v>
       </c>
       <c r="W351">
         <v>483.6377454948188</v>
@@ -30872,16 +30872,16 @@
         <v>1632.465427077281</v>
       </c>
       <c r="Y351">
-        <v>14.54178896143094</v>
+        <v>16.61630172859429</v>
       </c>
       <c r="Z351">
-        <v>60.10194769742748</v>
+        <v>66.91846935256604</v>
       </c>
       <c r="AA351">
-        <v>0.0300675228451265</v>
+        <v>0.03435691668687655</v>
       </c>
       <c r="AB351">
-        <v>0.0368166741546449</v>
+        <v>0.04099227355299949</v>
       </c>
     </row>
     <row r="352" spans="1:28">
@@ -30910,16 +30910,16 @@
         <v>88</v>
       </c>
       <c r="I352">
-        <v>8739.84219353862</v>
+        <v>8776.236531241146</v>
       </c>
       <c r="J352">
-        <v>8739.84219353862</v>
+        <v>8776.236531241146</v>
       </c>
       <c r="K352">
-        <v>29693.6560704141</v>
+        <v>29813.24212213694</v>
       </c>
       <c r="L352">
-        <v>0.3090150617086227</v>
+        <v>0.3090150617086228</v>
       </c>
       <c r="M352">
         <v>0.3121247336819685</v>
@@ -30940,7 +30940,7 @@
         <v>105</v>
       </c>
       <c r="S352">
-        <v>50163.8090048156</v>
+        <v>50163.80900481559</v>
       </c>
       <c r="T352">
         <v>28380</v>
@@ -30949,7 +30949,7 @@
         <v>640.7</v>
       </c>
       <c r="V352">
-        <v>871.3282417886041</v>
+        <v>874.956615571468</v>
       </c>
       <c r="W352">
         <v>9115.581600759089</v>
@@ -30958,16 +30958,16 @@
         <v>30768.63199690108</v>
       </c>
       <c r="Y352">
-        <v>-375.7394072204697</v>
+        <v>-339.3450695179436</v>
       </c>
       <c r="Z352">
-        <v>-1074.975926486986</v>
+        <v>-955.3898747641433</v>
       </c>
       <c r="AA352">
-        <v>-0.04121946614894879</v>
+        <v>-0.03722692466377406</v>
       </c>
       <c r="AB352">
-        <v>-0.03493739749610104</v>
+        <v>-0.03105077518104695</v>
       </c>
     </row>
     <row r="353" spans="1:28">
@@ -30996,16 +30996,16 @@
         <v>89</v>
       </c>
       <c r="I353">
-        <v>690.3890804775768</v>
+        <v>693.2639897476337</v>
       </c>
       <c r="J353">
-        <v>690.3890804775768</v>
+        <v>693.2639897476337</v>
       </c>
       <c r="K353">
-        <v>2345.600235851675</v>
+        <v>2355.04673413604</v>
       </c>
       <c r="L353">
-        <v>0.0244101231558232</v>
+        <v>0.02441012315582321</v>
       </c>
       <c r="M353">
         <v>0.02450125895797011</v>
@@ -31035,7 +31035,7 @@
         <v>1426.1</v>
       </c>
       <c r="V353">
-        <v>87.56356697150657</v>
+        <v>87.92819804335302</v>
       </c>
       <c r="W353">
         <v>715.5576000595839</v>
@@ -31044,16 +31044,16 @@
         <v>2415.285105558778</v>
       </c>
       <c r="Y353">
-        <v>-25.16851958200709</v>
+        <v>-22.29361031195026</v>
       </c>
       <c r="Z353">
-        <v>-69.68486970710273</v>
+        <v>-60.23837142273851</v>
       </c>
       <c r="AA353">
-        <v>-0.03517329643331484</v>
+        <v>-0.03115557756649344</v>
       </c>
       <c r="AB353">
-        <v>-0.02885161240249568</v>
+        <v>-0.02494048064309258</v>
       </c>
     </row>
     <row r="354" spans="1:28">
@@ -35812,16 +35812,16 @@
         <v>72</v>
       </c>
       <c r="I409">
-        <v>5862.459434922803</v>
+        <v>5873.978465519293</v>
       </c>
       <c r="J409">
-        <v>5862.459434922803</v>
+        <v>5873.978465519293</v>
       </c>
       <c r="K409">
-        <v>17645.52526386701</v>
+        <v>17680.01028856961</v>
       </c>
       <c r="L409">
-        <v>0.5</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="M409">
         <v>0.4999999999999999</v>
@@ -35842,7 +35842,7 @@
         <v>105</v>
       </c>
       <c r="S409">
-        <v>75482.2747737289</v>
+        <v>75482.27477372887</v>
       </c>
       <c r="T409">
         <v>14730</v>
@@ -35851,7 +35851,7 @@
         <v>5486.5</v>
       </c>
       <c r="V409">
-        <v>524.650456552362</v>
+        <v>525.6813318579525</v>
       </c>
       <c r="W409">
         <v>5948.051175681667</v>
@@ -35860,16 +35860,16 @@
         <v>17831</v>
       </c>
       <c r="Y409">
-        <v>-85.59174075886403</v>
+        <v>-74.07271016237337</v>
       </c>
       <c r="Z409">
-        <v>-185.4747361329937</v>
+        <v>-150.9897114303967</v>
       </c>
       <c r="AA409">
-        <v>-0.01438987968173541</v>
+        <v>-0.01245327384962931</v>
       </c>
       <c r="AB409">
-        <v>-0.01040181347837999</v>
+        <v>-0.008467820729650423</v>
       </c>
     </row>
     <row r="410" spans="1:28">
@@ -35898,13 +35898,13 @@
         <v>73</v>
       </c>
       <c r="I410">
-        <v>652.9371547242126</v>
+        <v>654.2200980257985</v>
       </c>
       <c r="J410">
-        <v>652.9371547242126</v>
+        <v>654.2200980257985</v>
       </c>
       <c r="K410">
-        <v>1965.287638626577</v>
+        <v>1969.128441989033</v>
       </c>
       <c r="L410">
         <v>0.05568798914280339</v>
@@ -35928,7 +35928,7 @@
         <v>106</v>
       </c>
       <c r="S410">
-        <v>137457.6629278278</v>
+        <v>137457.6629278277</v>
       </c>
       <c r="T410">
         <v>1510</v>
@@ -35937,7 +35937,7 @@
         <v>748.7</v>
       </c>
       <c r="V410">
-        <v>49.04566610508348</v>
+        <v>49.14203496439263</v>
       </c>
       <c r="W410">
         <v>662.5396144660967</v>
@@ -35946,16 +35946,16 @@
         <v>1986.153702551336</v>
       </c>
       <c r="Y410">
-        <v>-9.602459741884104</v>
+        <v>-8.31951644029823</v>
       </c>
       <c r="Z410">
-        <v>-20.86606392475846</v>
+        <v>-17.02526056230317</v>
       </c>
       <c r="AA410">
-        <v>-0.01449341221599585</v>
+        <v>-0.01255700981291882</v>
       </c>
       <c r="AB410">
-        <v>-0.01050576493549051</v>
+        <v>-0.008571975341300719</v>
       </c>
     </row>
     <row r="411" spans="1:28">
@@ -35984,13 +35984,13 @@
         <v>74</v>
       </c>
       <c r="I411">
-        <v>539.6260298044415</v>
+        <v>540.6863303177296</v>
       </c>
       <c r="J411">
-        <v>539.6260298044415</v>
+        <v>540.6863303177296</v>
       </c>
       <c r="K411">
-        <v>1624.230384475131</v>
+        <v>1627.404652403898</v>
       </c>
       <c r="L411">
         <v>0.04602386044582902</v>
@@ -36023,7 +36023,7 @@
         <v>742.2</v>
       </c>
       <c r="V411">
-        <v>46.77537333909487</v>
+        <v>46.86728134504978</v>
       </c>
       <c r="W411">
         <v>544.096778360425</v>
@@ -36032,16 +36032,16 @@
         <v>1631.087118855005</v>
       </c>
       <c r="Y411">
-        <v>-4.470748555983505</v>
+        <v>-3.410448042695407</v>
       </c>
       <c r="Z411">
-        <v>-6.856734379874297</v>
+        <v>-3.682466451107302</v>
       </c>
       <c r="AA411">
-        <v>-0.008216826001902837</v>
+        <v>-0.006268090858711592</v>
       </c>
       <c r="AB411">
-        <v>-0.004203781821713855</v>
+        <v>-0.002257676128110392</v>
       </c>
     </row>
     <row r="412" spans="1:28">
@@ -36070,13 +36070,13 @@
         <v>75</v>
       </c>
       <c r="I412">
-        <v>289.1025022312552</v>
+        <v>289.6705540200463</v>
       </c>
       <c r="J412">
-        <v>289.1025022312552</v>
+        <v>289.6705540200463</v>
       </c>
       <c r="K412">
-        <v>870.1749775153806</v>
+        <v>871.8755789509555</v>
       </c>
       <c r="L412">
         <v>0.02465710044056468</v>
@@ -36109,7 +36109,7 @@
         <v>193.7</v>
       </c>
       <c r="V412">
-        <v>18.00958060639453</v>
+        <v>18.04496727513618</v>
       </c>
       <c r="W412">
         <v>296.1070902641772</v>
@@ -36118,16 +36118,16 @@
         <v>887.6664592408199</v>
       </c>
       <c r="Y412">
-        <v>-7.004588032922015</v>
+        <v>-6.436536244130878</v>
       </c>
       <c r="Z412">
-        <v>-17.49148172543926</v>
+        <v>-15.79088028986439</v>
       </c>
       <c r="AA412">
-        <v>-0.02365559036993254</v>
+        <v>-0.02173719054950156</v>
       </c>
       <c r="AB412">
-        <v>-0.01970501593627736</v>
+        <v>-0.01778920463365215</v>
       </c>
     </row>
     <row r="413" spans="1:28">
@@ -36156,16 +36156,16 @@
         <v>76</v>
       </c>
       <c r="I413">
-        <v>1004.357599932052</v>
+        <v>1006.331042316065</v>
       </c>
       <c r="J413">
-        <v>1004.357599932052</v>
+        <v>1006.331042316065</v>
       </c>
       <c r="K413">
-        <v>3023.034547238829</v>
+        <v>3028.942527844644</v>
       </c>
       <c r="L413">
-        <v>0.08566008951371767</v>
+        <v>0.08566008951371765</v>
       </c>
       <c r="M413">
         <v>0.08494088363410093</v>
@@ -36186,7 +36186,7 @@
         <v>106</v>
       </c>
       <c r="S413">
-        <v>99424.13271945597</v>
+        <v>99424.13271945599</v>
       </c>
       <c r="T413">
         <v>1580</v>
@@ -36195,7 +36195,7 @@
         <v>97.30000000000001</v>
       </c>
       <c r="V413">
-        <v>66.94884740234562</v>
+        <v>67.08039386849826</v>
       </c>
       <c r="W413">
         <v>1010.465445526508</v>
@@ -36204,16 +36204,16 @@
         <v>3029.161792159307</v>
       </c>
       <c r="Y413">
-        <v>-6.107845594455512</v>
+        <v>-4.134403210442656</v>
       </c>
       <c r="Z413">
-        <v>-6.127244920478006</v>
+        <v>-0.2192643146627233</v>
       </c>
       <c r="AA413">
-        <v>-0.00604458630574249</v>
+        <v>-0.00409158297173478</v>
       </c>
       <c r="AB413">
-        <v>-0.002022752609760822</v>
+        <v>-7.238448445714187E-05</v>
       </c>
     </row>
     <row r="414" spans="1:28">
@@ -36242,13 +36242,13 @@
         <v>77</v>
       </c>
       <c r="I414">
-        <v>25.3907101071065</v>
+        <v>25.44059981122079</v>
       </c>
       <c r="J414">
-        <v>25.3907101071065</v>
+        <v>25.44059981122079</v>
       </c>
       <c r="K414">
-        <v>76.42396875166962</v>
+        <v>76.57332573656306</v>
       </c>
       <c r="L414">
         <v>0.002165533969911456</v>
@@ -36272,7 +36272,7 @@
         <v>106</v>
       </c>
       <c r="S414">
-        <v>84149.99999999999</v>
+        <v>84150</v>
       </c>
       <c r="T414">
         <v>90</v>
@@ -36281,7 +36281,7 @@
         <v>6.3</v>
       </c>
       <c r="V414">
-        <v>1.799341661133531</v>
+        <v>1.802877151976276</v>
       </c>
       <c r="W414">
         <v>25.90937039811559</v>
@@ -36290,16 +36290,16 @@
         <v>77.670815183572</v>
       </c>
       <c r="Y414">
-        <v>-0.5186602910090912</v>
+        <v>-0.4687705868947987</v>
       </c>
       <c r="Z414">
-        <v>-1.246846431902384</v>
+        <v>-1.09748944700894</v>
       </c>
       <c r="AA414">
-        <v>-0.02001825142948336</v>
+        <v>-0.01809270467370727</v>
       </c>
       <c r="AB414">
-        <v>-0.01605295926089497</v>
+        <v>-0.01413001066636246</v>
       </c>
     </row>
     <row r="415" spans="1:28">
@@ -36328,13 +36328,13 @@
         <v>79</v>
       </c>
       <c r="I415">
-        <v>13.9237564683572</v>
+        <v>13.95111498205908</v>
       </c>
       <c r="J415">
-        <v>13.9237564683572</v>
+        <v>13.95111498205908</v>
       </c>
       <c r="K415">
-        <v>41.90937255219812</v>
+        <v>41.99127692886707</v>
       </c>
       <c r="L415">
         <v>0.001187535421176057</v>
@@ -36367,7 +36367,7 @@
         <v>4.5</v>
       </c>
       <c r="V415">
-        <v>1.106035377009839</v>
+        <v>1.108208604047059</v>
       </c>
       <c r="W415">
         <v>14.80535451320874</v>
@@ -36376,16 +36376,16 @@
         <v>44.38332296204064</v>
       </c>
       <c r="Y415">
-        <v>-0.8815980448515361</v>
+        <v>-0.8542395311496538</v>
       </c>
       <c r="Z415">
-        <v>-2.473950409842516</v>
+        <v>-2.392046033173571</v>
       </c>
       <c r="AA415">
-        <v>-0.05954589226924692</v>
+        <v>-0.05769801259318282</v>
       </c>
       <c r="AB415">
-        <v>-0.05574054047188831</v>
+        <v>-0.05389515416002981</v>
       </c>
     </row>
     <row r="416" spans="1:28">
@@ -36414,16 +36414,16 @@
         <v>83</v>
       </c>
       <c r="I416">
-        <v>14.43204690952955</v>
+        <v>14.46040415306637</v>
       </c>
       <c r="J416">
-        <v>14.43204690952955</v>
+        <v>14.46040415306637</v>
       </c>
       <c r="K416">
-        <v>43.43928536791159</v>
+        <v>43.52417968568196</v>
       </c>
       <c r="L416">
-        <v>0.001230886718256635</v>
+        <v>0.001230886718256634</v>
       </c>
       <c r="M416">
         <v>0.001244555071561905</v>
@@ -36453,7 +36453,7 @@
         <v>351.3</v>
       </c>
       <c r="V416">
-        <v>2.051293930780761</v>
+        <v>2.055324477655047</v>
       </c>
       <c r="W416">
         <v>14.80535451320874</v>
@@ -36462,16 +36462,16 @@
         <v>44.38332296204064</v>
       </c>
       <c r="Y416">
-        <v>-0.3733076036791907</v>
+        <v>-0.3449503601423718</v>
       </c>
       <c r="Z416">
-        <v>-0.9440375941290498</v>
+        <v>-0.8591432763586795</v>
       </c>
       <c r="AA416">
-        <v>-0.02521436439405357</v>
+        <v>-0.0232990273778734</v>
       </c>
       <c r="AB416">
-        <v>-0.02127009721503838</v>
+        <v>-0.01935734458398872</v>
       </c>
     </row>
     <row r="417" spans="1:28">
@@ -36500,16 +36500,16 @@
         <v>84</v>
       </c>
       <c r="I417">
-        <v>290.533239035187</v>
+        <v>291.1041020504272</v>
       </c>
       <c r="J417">
-        <v>290.533239035187</v>
+        <v>291.1041020504272</v>
       </c>
       <c r="K417">
-        <v>874.481378728041</v>
+        <v>876.1903962549463</v>
       </c>
       <c r="L417">
-        <v>0.02477912574579826</v>
+        <v>0.02477912574579825</v>
       </c>
       <c r="M417">
         <v>0.02551337896701935</v>
@@ -36539,7 +36539,7 @@
         <v>147</v>
       </c>
       <c r="V417">
-        <v>25.46918500305643</v>
+        <v>25.5192289009417</v>
       </c>
       <c r="W417">
         <v>303.5097675207827</v>
@@ -36548,16 +36548,16 @@
         <v>909.8581207218439</v>
       </c>
       <c r="Y417">
-        <v>-12.97652848559568</v>
+        <v>-12.40566547035553</v>
       </c>
       <c r="Z417">
-        <v>-35.37674199380285</v>
+        <v>-33.66772446689754</v>
       </c>
       <c r="AA417">
-        <v>-0.04275489580317087</v>
+        <v>-0.0408740238302415</v>
       </c>
       <c r="AB417">
-        <v>-0.03888160273355191</v>
+        <v>-0.03700326864169433</v>
       </c>
     </row>
     <row r="418" spans="1:28">
@@ -36586,16 +36586,16 @@
         <v>85</v>
       </c>
       <c r="I418">
-        <v>442.3169344804796</v>
+        <v>443.1860342769361</v>
       </c>
       <c r="J418">
-        <v>442.3169344804796</v>
+        <v>443.1860342769361</v>
       </c>
       <c r="K418">
-        <v>1331.33793566527</v>
+        <v>1333.939797662144</v>
       </c>
       <c r="L418">
-        <v>0.03772451983595722</v>
+        <v>0.03772451983595721</v>
       </c>
       <c r="M418">
         <v>0.03982576228998121</v>
@@ -36625,7 +36625,7 @@
         <v>1302.8</v>
       </c>
       <c r="V418">
-        <v>45.93937318104811</v>
+        <v>46.0296385468268</v>
       </c>
       <c r="W418">
         <v>473.7713444226827</v>
@@ -36634,16 +36634,16 @@
         <v>1420.266334785309</v>
       </c>
       <c r="Y418">
-        <v>-31.45440994220303</v>
+        <v>-30.58531014574652</v>
       </c>
       <c r="Z418">
-        <v>-88.9283991200391</v>
+        <v>-86.32653712316574</v>
       </c>
       <c r="AA418">
-        <v>-0.06639154164237607</v>
+        <v>-0.06455711284737252</v>
       </c>
       <c r="AB418">
-        <v>-0.06261388934032694</v>
+        <v>-0.06078193576010871</v>
       </c>
     </row>
     <row r="419" spans="1:28">
@@ -36672,16 +36672,16 @@
         <v>86</v>
       </c>
       <c r="I419">
-        <v>54.25426966161145</v>
+        <v>54.36087280303352</v>
       </c>
       <c r="J419">
-        <v>54.25426966161145</v>
+        <v>54.36087280303352</v>
       </c>
       <c r="K419">
-        <v>163.3009313947133</v>
+        <v>163.6200738724176</v>
       </c>
       <c r="L419">
-        <v>0.004627261839836157</v>
+        <v>0.004627261839836156</v>
       </c>
       <c r="M419">
         <v>0.004667081518357168</v>
@@ -36711,7 +36711,7 @@
         <v>81</v>
       </c>
       <c r="V419">
-        <v>5.12549083577155</v>
+        <v>5.135561811343264</v>
       </c>
       <c r="W419">
         <v>55.52007942453307</v>
@@ -36720,16 +36720,16 @@
         <v>166.4374611076533</v>
       </c>
       <c r="Y419">
-        <v>-1.26580976292162</v>
+        <v>-1.15920662149955</v>
       </c>
       <c r="Z419">
-        <v>-3.136529712940018</v>
+        <v>-2.817387235235714</v>
       </c>
       <c r="AA419">
-        <v>-0.02279913458413187</v>
+        <v>-0.02087905193066641</v>
       </c>
       <c r="AB419">
-        <v>-0.0188450946804054</v>
+        <v>-0.01692760281541066</v>
       </c>
     </row>
     <row r="420" spans="1:28">
@@ -36758,16 +36758,16 @@
         <v>87</v>
       </c>
       <c r="I420">
-        <v>194.0940878808979</v>
+        <v>194.4754595153998</v>
       </c>
       <c r="J420">
-        <v>194.0940878808979</v>
+        <v>194.4754595153998</v>
       </c>
       <c r="K420">
-        <v>584.207390991475</v>
+        <v>585.3491199005621</v>
       </c>
       <c r="L420">
-        <v>0.01655398131411154</v>
+        <v>0.01655398131411153</v>
       </c>
       <c r="M420">
         <v>0.01524579962663351</v>
@@ -36788,7 +36788,7 @@
         <v>105</v>
       </c>
       <c r="S420">
-        <v>63058.31970479211</v>
+        <v>63058.31970479212</v>
       </c>
       <c r="T420">
         <v>500</v>
@@ -36797,7 +36797,7 @@
         <v>257.9</v>
       </c>
       <c r="V420">
-        <v>18.35279756420149</v>
+        <v>18.38885861315543</v>
       </c>
       <c r="W420">
         <v>181.3655927868091</v>
@@ -36806,16 +36806,16 @@
         <v>543.6957062850041</v>
       </c>
       <c r="Y420">
-        <v>12.72849509408877</v>
+        <v>13.10986672859067</v>
       </c>
       <c r="Z420">
-        <v>40.51168470647087</v>
+        <v>41.65341361555795</v>
       </c>
       <c r="AA420">
-        <v>0.07018142139590285</v>
+        <v>0.07228419970485253</v>
       </c>
       <c r="AB420">
-        <v>0.07451168776608792</v>
+        <v>0.07661162877332586</v>
       </c>
     </row>
     <row r="421" spans="1:28">
@@ -36844,13 +36844,13 @@
         <v>88</v>
       </c>
       <c r="I421">
-        <v>2173.379433183886</v>
+        <v>2177.649863447247</v>
       </c>
       <c r="J421">
-        <v>2173.379433183886</v>
+        <v>2177.649863447247</v>
       </c>
       <c r="K421">
-        <v>6541.695020994241</v>
+        <v>6554.479594478024</v>
       </c>
       <c r="L421">
         <v>0.185364134055838</v>
@@ -36883,7 +36883,7 @@
         <v>546.8000000000001</v>
       </c>
       <c r="V421">
-        <v>222.8510975153189</v>
+        <v>223.2889732292979</v>
       </c>
       <c r="W421">
         <v>2198.595145211522</v>
@@ -36892,16 +36892,16 @@
         <v>6590.923459863108</v>
       </c>
       <c r="Y421">
-        <v>-25.21571202763653</v>
+        <v>-20.94528176427502</v>
       </c>
       <c r="Z421">
-        <v>-49.22843886886767</v>
+        <v>-36.44386538508388</v>
       </c>
       <c r="AA421">
-        <v>-0.01146901105578971</v>
+        <v>-0.009526666066689563</v>
       </c>
       <c r="AB421">
-        <v>-0.007469126165499444</v>
+        <v>-0.00552940200368232</v>
       </c>
     </row>
     <row r="422" spans="1:28">
@@ -36930,13 +36930,13 @@
         <v>89</v>
       </c>
       <c r="I422">
-        <v>168.111670503787</v>
+        <v>168.4419898002625</v>
       </c>
       <c r="J422">
-        <v>168.111670503787</v>
+        <v>168.4419898002625</v>
       </c>
       <c r="K422">
-        <v>506.0024315655708</v>
+        <v>506.9913228618728</v>
       </c>
       <c r="L422">
         <v>0.01433798155619995</v>
@@ -36969,7 +36969,7 @@
         <v>1007</v>
       </c>
       <c r="V422">
-        <v>21.17637403112282</v>
+        <v>21.21798306963217</v>
       </c>
       <c r="W422">
         <v>166.5602382735992</v>
@@ -36978,16 +36978,16 @@
         <v>499.3123833229599</v>
       </c>
       <c r="Y422">
-        <v>1.551432230187828</v>
+        <v>1.881751526663351</v>
       </c>
       <c r="Z422">
-        <v>6.690048242610942</v>
+        <v>7.678939538912914</v>
       </c>
       <c r="AA422">
-        <v>0.009314541371148718</v>
+        <v>0.01129772355135745</v>
       </c>
       <c r="AB422">
-        <v>0.01339852258036981</v>
+        <v>0.01537902883122789</v>
       </c>
     </row>
     <row r="423" spans="1:28">
@@ -42606,13 +42606,13 @@
         <v>72</v>
       </c>
       <c r="I488">
-        <v>1040.654309623293</v>
+        <v>1029.072056326351</v>
       </c>
       <c r="J488">
-        <v>1040.654309623293</v>
+        <v>1029.072056326351</v>
       </c>
       <c r="K488">
-        <v>122645.504239072</v>
+        <v>121287.6493802097</v>
       </c>
       <c r="L488">
         <v>0.5</v>
@@ -42645,7 +42645,7 @@
         <v>8545.199999999999</v>
       </c>
       <c r="V488">
-        <v>80.62191010265349</v>
+        <v>79.72460599747927</v>
       </c>
       <c r="W488">
         <v>1012.884668579939</v>
@@ -42654,16 +42654,16 @@
         <v>116864</v>
       </c>
       <c r="Y488">
-        <v>27.76964104335434</v>
+        <v>16.18738774641247</v>
       </c>
       <c r="Z488">
-        <v>5781.504239072048</v>
+        <v>4423.649380209739</v>
       </c>
       <c r="AA488">
-        <v>0.02741638994525141</v>
+        <v>0.01598147177911888</v>
       </c>
       <c r="AB488">
-        <v>0.0494720721443049</v>
+        <v>0.03785296909407293</v>
       </c>
     </row>
     <row r="489" spans="1:28">
@@ -42692,13 +42692,13 @@
         <v>73</v>
       </c>
       <c r="I489">
-        <v>124.9976660760898</v>
+        <v>123.6064695792013</v>
       </c>
       <c r="J489">
-        <v>124.9976660760898</v>
+        <v>123.6064695792013</v>
       </c>
       <c r="K489">
-        <v>14731.50271213371</v>
+        <v>14568.40466251404</v>
       </c>
       <c r="L489">
         <v>0.06005724711856415</v>
@@ -42722,7 +42722,7 @@
         <v>106</v>
       </c>
       <c r="S489">
-        <v>145166.9927431315</v>
+        <v>145166.9927431316</v>
       </c>
       <c r="T489">
         <v>14220</v>
@@ -42731,7 +42731,7 @@
         <v>879.3</v>
       </c>
       <c r="V489">
-        <v>9.31981580579151</v>
+        <v>9.216088308249514</v>
       </c>
       <c r="W489">
         <v>121.365141036183</v>
@@ -42740,16 +42740,16 @@
         <v>14002.79447603577</v>
       </c>
       <c r="Y489">
-        <v>3.632525039906795</v>
+        <v>2.241328543018298</v>
       </c>
       <c r="Z489">
-        <v>728.7082360979457</v>
+        <v>565.6101864782704</v>
       </c>
       <c r="AA489">
-        <v>0.02993054685137159</v>
+        <v>0.01846764667253247</v>
       </c>
       <c r="AB489">
-        <v>0.05204020078599662</v>
+        <v>0.04039266501027703</v>
       </c>
     </row>
     <row r="490" spans="1:28">
@@ -42778,16 +42778,16 @@
         <v>74</v>
       </c>
       <c r="I490">
-        <v>102.9879512469645</v>
+        <v>101.8417180292236</v>
       </c>
       <c r="J490">
-        <v>102.9879512469645</v>
+        <v>101.8417180292236</v>
       </c>
       <c r="K490">
-        <v>12137.56489011729</v>
+        <v>12003.18530920191</v>
       </c>
       <c r="L490">
-        <v>0.04948230660969691</v>
+        <v>0.04948230660969692</v>
       </c>
       <c r="M490">
         <v>0.04939073923639327</v>
@@ -42817,7 +42817,7 @@
         <v>787.1000000000001</v>
       </c>
       <c r="V490">
-        <v>8.399882156956137</v>
+        <v>8.306393318341183</v>
       </c>
       <c r="W490">
         <v>100.0542450847448</v>
@@ -42826,16 +42826,16 @@
         <v>11543.99870024373</v>
       </c>
       <c r="Y490">
-        <v>2.93370616221975</v>
+        <v>1.787472944478864</v>
       </c>
       <c r="Z490">
-        <v>593.5661898735652</v>
+        <v>459.1866089581854</v>
       </c>
       <c r="AA490">
-        <v>0.02932115633609484</v>
+        <v>0.01786503853949321</v>
       </c>
       <c r="AB490">
-        <v>0.05141772840471936</v>
+        <v>0.03977708425664416</v>
       </c>
     </row>
     <row r="491" spans="1:28">
@@ -42864,16 +42864,16 @@
         <v>75</v>
       </c>
       <c r="I491">
-        <v>102.5715363472132</v>
+        <v>101.4299377356052</v>
       </c>
       <c r="J491">
-        <v>102.5715363472132</v>
+        <v>101.4299377356052</v>
       </c>
       <c r="K491">
-        <v>12088.48863599488</v>
+        <v>11954.6523968883</v>
       </c>
       <c r="L491">
-        <v>0.0492822330137388</v>
+        <v>0.04928223301373881</v>
       </c>
       <c r="M491">
         <v>0.04711616571892772</v>
@@ -42903,7 +42903,7 @@
         <v>335.8</v>
       </c>
       <c r="V491">
-        <v>6.527581378895714</v>
+        <v>6.4549308356292</v>
       </c>
       <c r="W491">
         <v>95.44648379794715</v>
@@ -42912,16 +42912,16 @@
         <v>11012.36718115353</v>
       </c>
       <c r="Y491">
-        <v>7.125052549266073</v>
+        <v>5.983453937658027</v>
       </c>
       <c r="Z491">
-        <v>1076.121454841345</v>
+        <v>942.2852157347643</v>
       </c>
       <c r="AA491">
-        <v>0.07464971223402278</v>
+        <v>0.06268909759236954</v>
       </c>
       <c r="AB491">
-        <v>0.09771935834858551</v>
+        <v>0.08556609130754221</v>
       </c>
     </row>
     <row r="492" spans="1:28">
@@ -42950,16 +42950,16 @@
         <v>76</v>
       </c>
       <c r="I492">
-        <v>416.7006213448368</v>
+        <v>412.0628351935873</v>
       </c>
       <c r="J492">
-        <v>416.7006213448368</v>
+        <v>412.0628351935873</v>
       </c>
       <c r="K492">
-        <v>49109.92761858852</v>
+        <v>48566.2129977469</v>
       </c>
       <c r="L492">
-        <v>0.2002108757401286</v>
+        <v>0.2002108757401285</v>
       </c>
       <c r="M492">
         <v>0.2000812347684821</v>
@@ -42980,7 +42980,7 @@
         <v>106</v>
       </c>
       <c r="S492">
-        <v>98006.38342974753</v>
+        <v>98006.38342974757</v>
       </c>
       <c r="T492">
         <v>51120</v>
@@ -42989,7 +42989,7 @@
         <v>177.1</v>
       </c>
       <c r="V492">
-        <v>27.75511677184015</v>
+        <v>27.446208434302</v>
       </c>
       <c r="W492">
         <v>405.3184303350778</v>
@@ -42998,16 +42998,16 @@
         <v>46764.58683996776</v>
       </c>
       <c r="Y492">
-        <v>11.38219100975903</v>
+        <v>6.744404858509483</v>
       </c>
       <c r="Z492">
-        <v>2345.340778620761</v>
+        <v>1801.626157779137</v>
       </c>
       <c r="AA492">
-        <v>0.02808209584831694</v>
+        <v>0.01663976852208242</v>
       </c>
       <c r="AB492">
-        <v>0.05015206884317632</v>
+        <v>0.03852543729177912</v>
       </c>
     </row>
     <row r="493" spans="1:28">
@@ -43036,16 +43036,16 @@
         <v>77</v>
       </c>
       <c r="I493">
-        <v>48.41317285075228</v>
+        <v>47.87434489829895</v>
       </c>
       <c r="J493">
-        <v>48.41317285075228</v>
+        <v>47.87434489829895</v>
       </c>
       <c r="K493">
-        <v>5705.696830528902</v>
+        <v>5642.526898515522</v>
       </c>
       <c r="L493">
-        <v>0.02326092939944552</v>
+        <v>0.02326092939944551</v>
       </c>
       <c r="M493">
         <v>0.02303005686433759</v>
@@ -43066,7 +43066,7 @@
         <v>106</v>
       </c>
       <c r="S493">
-        <v>86803.58760628867</v>
+        <v>86803.58760628865</v>
       </c>
       <c r="T493">
         <v>5220</v>
@@ -43075,7 +43075,7 @@
         <v>95.29999999999998</v>
       </c>
       <c r="V493">
-        <v>3.884245457009263</v>
+        <v>3.841014660447374</v>
       </c>
       <c r="W493">
         <v>46.65358302882345</v>
@@ -43084,16 +43084,16 @@
         <v>5382.769130787897</v>
       </c>
       <c r="Y493">
-        <v>1.75958982192882</v>
+        <v>1.220761869475496</v>
       </c>
       <c r="Z493">
-        <v>322.9276997410052</v>
+        <v>259.7577677276249</v>
       </c>
       <c r="AA493">
-        <v>0.0377160704000315</v>
+        <v>0.02616651905859591</v>
       </c>
       <c r="AB493">
-        <v>0.05999285718831062</v>
+        <v>0.04825727453958316</v>
       </c>
     </row>
     <row r="494" spans="1:28">
@@ -43122,13 +43122,13 @@
         <v>78</v>
       </c>
       <c r="I494">
-        <v>2.190956731486788</v>
+        <v>2.166571865549985</v>
       </c>
       <c r="J494">
-        <v>2.190956731486788</v>
+        <v>2.166571865549985</v>
       </c>
       <c r="K494">
-        <v>258.2135014618419</v>
+        <v>255.3547219267979</v>
       </c>
       <c r="L494">
         <v>0.001052682293834873</v>
@@ -43152,7 +43152,7 @@
         <v>106</v>
       </c>
       <c r="S494">
-        <v>130933.6188795459</v>
+        <v>130933.618879546</v>
       </c>
       <c r="T494">
         <v>170</v>
@@ -43161,7 +43161,7 @@
         <v>70.8</v>
       </c>
       <c r="V494">
-        <v>0.111952177648435</v>
+        <v>0.1107061745649155</v>
       </c>
       <c r="W494">
         <v>2.139317740298675</v>
@@ -43170,16 +43170,16 @@
         <v>246.8289195775631</v>
       </c>
       <c r="Y494">
-        <v>0.05163899118811299</v>
+        <v>0.02725412525131032</v>
       </c>
       <c r="Z494">
-        <v>11.38458188427882</v>
+        <v>8.525802349234823</v>
       </c>
       <c r="AA494">
-        <v>0.02413806524172681</v>
+        <v>0.01273963410760354</v>
       </c>
       <c r="AB494">
-        <v>0.04612337121502225</v>
+        <v>0.03454134290190291</v>
       </c>
     </row>
     <row r="495" spans="1:28">
@@ -43208,13 +43208,13 @@
         <v>79</v>
       </c>
       <c r="I495">
-        <v>27.19840325242329</v>
+        <v>26.89569101375879</v>
       </c>
       <c r="J495">
-        <v>27.19840325242329</v>
+        <v>26.89569101375879</v>
       </c>
       <c r="K495">
-        <v>3205.44666037907</v>
+        <v>3169.957945569473</v>
       </c>
       <c r="L495">
         <v>0.01306793379939437</v>
@@ -43238,7 +43238,7 @@
         <v>106</v>
       </c>
       <c r="S495">
-        <v>73418.68129946689</v>
+        <v>73418.6812994669</v>
       </c>
       <c r="T495">
         <v>3940</v>
@@ -43247,7 +43247,7 @@
         <v>89.5</v>
       </c>
       <c r="V495">
-        <v>2.226319643208605</v>
+        <v>2.201541195851833</v>
       </c>
       <c r="W495">
         <v>26.57690885063502</v>
@@ -43256,16 +43256,16 @@
         <v>3066.374654752204</v>
       </c>
       <c r="Y495">
-        <v>0.6214944017882686</v>
+        <v>0.318782163123764</v>
       </c>
       <c r="Z495">
-        <v>139.0720056268656</v>
+        <v>103.5832908172688</v>
       </c>
       <c r="AA495">
-        <v>0.02338475122449836</v>
+        <v>0.01199470430949486</v>
       </c>
       <c r="AB495">
-        <v>0.04535388570712801</v>
+        <v>0.03378037665969406</v>
       </c>
     </row>
     <row r="496" spans="1:28">
@@ -43294,13 +43294,13 @@
         <v>80</v>
       </c>
       <c r="I496">
-        <v>7.56858777311584</v>
+        <v>7.484351057928356</v>
       </c>
       <c r="J496">
-        <v>7.56858777311584</v>
+        <v>7.484351057928356</v>
       </c>
       <c r="K496">
-        <v>891.9900251482035</v>
+        <v>882.1144655244017</v>
       </c>
       <c r="L496">
         <v>0.003636456267526339</v>
@@ -43324,7 +43324,7 @@
         <v>106</v>
       </c>
       <c r="S496">
-        <v>65551.7105719573</v>
+        <v>65551.71057195732</v>
       </c>
       <c r="T496">
         <v>320</v>
@@ -43333,7 +43333,7 @@
         <v>225.9</v>
       </c>
       <c r="V496">
-        <v>0.4758975142302919</v>
+        <v>0.4706008796973551</v>
       </c>
       <c r="W496">
         <v>7.32304918794593</v>
@@ -43342,16 +43342,16 @@
         <v>844.9143785540195</v>
       </c>
       <c r="Y496">
-        <v>0.2455385851699097</v>
+        <v>0.1613018699824256</v>
       </c>
       <c r="Z496">
-        <v>47.07564659418392</v>
+        <v>37.20008697038213</v>
       </c>
       <c r="AA496">
-        <v>0.03352955563566025</v>
+        <v>0.02202659928161288</v>
       </c>
       <c r="AB496">
-        <v>0.05571646996320367</v>
+        <v>0.04402823281815383</v>
       </c>
     </row>
     <row r="497" spans="1:28">
@@ -43380,13 +43380,13 @@
         <v>81</v>
       </c>
       <c r="I497">
-        <v>0.4829766091043229</v>
+        <v>0.477601185804371</v>
       </c>
       <c r="J497">
-        <v>0.4829766091043229</v>
+        <v>0.477601185804371</v>
       </c>
       <c r="K497">
-        <v>56.92083260647749</v>
+        <v>56.29064049625932</v>
       </c>
       <c r="L497">
         <v>0.0002320542973002994</v>
@@ -43419,7 +43419,7 @@
         <v>161</v>
       </c>
       <c r="V497">
-        <v>0.06148919347287363</v>
+        <v>0.06080483229045052</v>
       </c>
       <c r="W497">
         <v>0.4936887092996709</v>
@@ -43428,16 +43428,16 @@
         <v>56.96051990251186</v>
       </c>
       <c r="Y497">
-        <v>-0.01071210019534802</v>
+        <v>-0.0160875234952999</v>
       </c>
       <c r="Z497">
-        <v>-0.03968729603437282</v>
+        <v>-0.6698794062525408</v>
       </c>
       <c r="AA497">
-        <v>-0.02169808625063315</v>
+        <v>-0.03258637111251964</v>
       </c>
       <c r="AB497">
-        <v>-0.0006967509443786288</v>
+        <v>-0.01176041594070844</v>
       </c>
     </row>
     <row r="498" spans="1:28">
@@ -43466,13 +43466,13 @@
         <v>83</v>
       </c>
       <c r="I498">
-        <v>2.798360102349509</v>
+        <v>2.7672149706552</v>
       </c>
       <c r="J498">
-        <v>2.798360102349509</v>
+        <v>2.7672149706552</v>
       </c>
       <c r="K498">
-        <v>329.7985532961413</v>
+        <v>326.147228522214</v>
       </c>
       <c r="L498">
         <v>0.001344519537598652</v>
@@ -43496,7 +43496,7 @@
         <v>105</v>
       </c>
       <c r="S498">
-        <v>36699.89877873467</v>
+        <v>36699.89877873466</v>
       </c>
       <c r="T498">
         <v>230</v>
@@ -43505,7 +43505,7 @@
         <v>509.5</v>
       </c>
       <c r="V498">
-        <v>0.38597942294347</v>
+        <v>0.3816835569651155</v>
       </c>
       <c r="W498">
         <v>2.715287901148494</v>
@@ -43514,16 +43514,16 @@
         <v>313.2828594638503</v>
       </c>
       <c r="Y498">
-        <v>0.08307220120101544</v>
+        <v>0.05192706950670622</v>
       </c>
       <c r="Z498">
-        <v>16.51569383229105</v>
+        <v>12.86436905836376</v>
       </c>
       <c r="AA498">
-        <v>0.03059425159515429</v>
+        <v>0.01912396452867575</v>
       </c>
       <c r="AB498">
-        <v>0.05271815336643656</v>
+        <v>0.04106311172076168</v>
       </c>
     </row>
     <row r="499" spans="1:28">
@@ -43552,16 +43552,16 @@
         <v>84</v>
       </c>
       <c r="I499">
-        <v>30.12681384707669</v>
+        <v>29.79150904337779</v>
       </c>
       <c r="J499">
-        <v>30.12681384707669</v>
+        <v>29.79150904337779</v>
       </c>
       <c r="K499">
-        <v>3550.572213292331</v>
+        <v>3511.262482687265</v>
       </c>
       <c r="L499">
-        <v>0.0144749383001077</v>
+        <v>0.01447493830010771</v>
       </c>
       <c r="M499">
         <v>0.01474411047928502</v>
@@ -43582,7 +43582,7 @@
         <v>105</v>
       </c>
       <c r="S499">
-        <v>75016.92547298175</v>
+        <v>75016.92547298176</v>
       </c>
       <c r="T499">
         <v>3000</v>
@@ -43591,7 +43591,7 @@
         <v>975.6999999999999</v>
       </c>
       <c r="V499">
-        <v>2.829178938236031</v>
+        <v>2.797690799685118</v>
       </c>
       <c r="W499">
         <v>29.86816691263323</v>
@@ -43600,16 +43600,16 @@
         <v>3446.11145410233</v>
       </c>
       <c r="Y499">
-        <v>0.2586469344434619</v>
+        <v>-0.07665786925544182</v>
       </c>
       <c r="Z499">
-        <v>104.4607591900008</v>
+        <v>65.15102858493447</v>
       </c>
       <c r="AA499">
-        <v>0.008659618623400115</v>
+        <v>-0.00256654080846917</v>
       </c>
       <c r="AB499">
-        <v>0.03031264675599748</v>
+        <v>0.01890566496547208</v>
       </c>
     </row>
     <row r="500" spans="1:28">
@@ -43638,13 +43638,13 @@
         <v>85</v>
       </c>
       <c r="I500">
-        <v>56.4051225560799</v>
+        <v>55.77734596336483</v>
       </c>
       <c r="J500">
-        <v>56.4051225560799</v>
+        <v>55.77734596336483</v>
       </c>
       <c r="K500">
-        <v>6647.581846906745</v>
+        <v>6573.983948911953</v>
       </c>
       <c r="L500">
         <v>0.02710079708241347</v>
@@ -43677,7 +43677,7 @@
         <v>1492.6</v>
       </c>
       <c r="V500">
-        <v>6.153004504975638</v>
+        <v>6.084522919827878</v>
       </c>
       <c r="W500">
         <v>58.09070479426767</v>
@@ -43686,16 +43686,16 @@
         <v>6702.354508529632</v>
       </c>
       <c r="Y500">
-        <v>-1.68558223818777</v>
+        <v>-2.313358830902843</v>
       </c>
       <c r="Z500">
-        <v>-54.77266162288652</v>
+        <v>-128.3705596176787</v>
       </c>
       <c r="AA500">
-        <v>-0.02901638470659598</v>
+        <v>-0.03982321851827699</v>
       </c>
       <c r="AB500">
-        <v>-0.00817215227173989</v>
+        <v>-0.01915305426687148</v>
       </c>
     </row>
     <row r="501" spans="1:28">
@@ -43724,13 +43724,13 @@
         <v>86</v>
       </c>
       <c r="I501">
-        <v>12.06375379803311</v>
+        <v>11.92948687489766</v>
       </c>
       <c r="J501">
-        <v>12.06375379803311</v>
+        <v>11.92948687489766</v>
       </c>
       <c r="K501">
-        <v>1421.764320671847</v>
+        <v>1406.023429043091</v>
       </c>
       <c r="L501">
         <v>0.005796234967978979</v>
@@ -43763,7 +43763,7 @@
         <v>345.3</v>
       </c>
       <c r="V501">
-        <v>1.160408294874735</v>
+        <v>1.147493206093738</v>
       </c>
       <c r="W501">
         <v>12.01309192629321</v>
@@ -43772,16 +43772,16 @@
         <v>1386.039317627929</v>
       </c>
       <c r="Y501">
-        <v>0.05066187173990144</v>
+        <v>-0.08360505139554775</v>
       </c>
       <c r="Z501">
-        <v>35.72500304391792</v>
+        <v>19.98411141516249</v>
       </c>
       <c r="AA501">
-        <v>0.004217221682039838</v>
+        <v>-0.006959494850160956</v>
       </c>
       <c r="AB501">
-        <v>0.02577488429769639</v>
+        <v>0.01441814179511397</v>
       </c>
     </row>
     <row r="502" spans="1:28">
@@ -43810,16 +43810,16 @@
         <v>87</v>
       </c>
       <c r="I502">
-        <v>13.86853035696156</v>
+        <v>13.71417666816667</v>
       </c>
       <c r="J502">
-        <v>13.86853035696156</v>
+        <v>13.71417666816667</v>
       </c>
       <c r="K502">
-        <v>1634.464858268009</v>
+        <v>1616.369078376129</v>
       </c>
       <c r="L502">
-        <v>0.006663370452951778</v>
+        <v>0.006663370452951779</v>
       </c>
       <c r="M502">
         <v>0.006661251015434406</v>
@@ -43840,7 +43840,7 @@
         <v>107</v>
       </c>
       <c r="S502">
-        <v>57375.46466332144</v>
+        <v>57375.46466332142</v>
       </c>
       <c r="T502">
         <v>2540</v>
@@ -43849,7 +43849,7 @@
         <v>428</v>
       </c>
       <c r="V502">
-        <v>1.268085775144342</v>
+        <v>1.253972259720294</v>
       </c>
       <c r="W502">
         <v>13.49415805419212</v>
@@ -43858,16 +43858,16 @@
         <v>1556.920877335453</v>
       </c>
       <c r="Y502">
-        <v>0.3743723027694443</v>
+        <v>0.2200186139745544</v>
       </c>
       <c r="Z502">
-        <v>77.54398093255622</v>
+        <v>59.44820104067617</v>
       </c>
       <c r="AA502">
-        <v>0.02774328722592227</v>
+        <v>0.01630473076504414</v>
       </c>
       <c r="AB502">
-        <v>0.04980598697171215</v>
+        <v>0.03818318702387565</v>
       </c>
     </row>
     <row r="503" spans="1:28">
@@ -43896,13 +43896,13 @@
         <v>88</v>
       </c>
       <c r="I503">
-        <v>82.44824450782583</v>
+        <v>81.53061370291088</v>
       </c>
       <c r="J503">
-        <v>82.44824450782583</v>
+        <v>81.53061370291088</v>
       </c>
       <c r="K503">
-        <v>9716.873728173012</v>
+        <v>9609.294536529493</v>
       </c>
       <c r="L503">
         <v>0.03961365640126514</v>
@@ -43935,7 +43935,7 @@
         <v>563.9999999999999</v>
       </c>
       <c r="V503">
-        <v>8.832440675212686</v>
+        <v>8.734137555546026</v>
       </c>
       <c r="W503">
         <v>81.70548138910446</v>
@@ -43944,16 +43944,16 @@
         <v>9426.966043866742</v>
       </c>
       <c r="Y503">
-        <v>0.7427631187213706</v>
+        <v>-0.1748676861935792</v>
       </c>
       <c r="Z503">
-        <v>289.9076843062703</v>
+        <v>182.3284926627512</v>
       </c>
       <c r="AA503">
-        <v>0.009090737929614831</v>
+        <v>-0.00214021976519311</v>
       </c>
       <c r="AB503">
-        <v>0.03075302095682063</v>
+        <v>0.01934116361662038</v>
       </c>
     </row>
     <row r="504" spans="1:28">
@@ -43982,13 +43982,13 @@
         <v>89</v>
       </c>
       <c r="I504">
-        <v>9.831612222979782</v>
+        <v>9.722188544020453</v>
       </c>
       <c r="J504">
-        <v>9.831612222979782</v>
+        <v>9.722188544020453</v>
       </c>
       <c r="K504">
-        <v>1158.697011505068</v>
+        <v>1145.868637756003</v>
       </c>
       <c r="L504">
         <v>0.004723764718054515</v>
@@ -44012,7 +44012,7 @@
         <v>105</v>
       </c>
       <c r="S504">
-        <v>42341.65019286333</v>
+        <v>42341.65019286334</v>
       </c>
       <c r="T504">
         <v>1160</v>
@@ -44021,7 +44021,7 @@
         <v>1408.3</v>
       </c>
       <c r="V504">
-        <v>1.230512392213601</v>
+        <v>1.216817060267297</v>
       </c>
       <c r="W504">
         <v>9.626929831344395</v>
@@ -44030,16 +44030,16 @@
         <v>1110.730138099075</v>
       </c>
       <c r="Y504">
-        <v>0.2046823916353873</v>
+        <v>0.09525871267605801</v>
       </c>
       <c r="Z504">
-        <v>47.96687340599283</v>
+        <v>35.13849965692771</v>
       </c>
       <c r="AA504">
-        <v>0.02126144006669295</v>
+        <v>0.00989502513728774</v>
       </c>
       <c r="AB504">
-        <v>0.04318499315061736</v>
+        <v>0.03163549673466538</v>
       </c>
     </row>
     <row r="505" spans="1:28">
@@ -49916,13 +49916,13 @@
         <v>72</v>
       </c>
       <c r="I573">
-        <v>173161.8874805455</v>
+        <v>173488.2515894179</v>
       </c>
       <c r="J573">
-        <v>173161.8874805455</v>
+        <v>173488.2515894179</v>
       </c>
       <c r="K573">
-        <v>173161.8874805455</v>
+        <v>173488.2515894179</v>
       </c>
       <c r="L573">
         <v>0.4999999999999999</v>
@@ -49955,7 +49955,7 @@
         <v>6966</v>
       </c>
       <c r="V573">
-        <v>16754.29807541966</v>
+        <v>16785.87547181285</v>
       </c>
       <c r="W573">
         <v>166447</v>
@@ -49964,16 +49964,16 @@
         <v>166447</v>
       </c>
       <c r="Y573">
-        <v>6714.887480545469</v>
+        <v>7041.251589417865</v>
       </c>
       <c r="Z573">
-        <v>6714.887480545469</v>
+        <v>7041.251589417865</v>
       </c>
       <c r="AA573">
-        <v>0.0403424962933875</v>
+        <v>0.04230326524009363</v>
       </c>
       <c r="AB573">
-        <v>0.0403424962933875</v>
+        <v>0.04230326524009363</v>
       </c>
     </row>
     <row r="574" spans="1:28">
@@ -50002,16 +50002,16 @@
         <v>73</v>
       </c>
       <c r="I574">
-        <v>8963.789794265549</v>
+        <v>8980.684154282582</v>
       </c>
       <c r="J574">
-        <v>8963.789794265549</v>
+        <v>8980.684154282582</v>
       </c>
       <c r="K574">
-        <v>8963.789794265549</v>
+        <v>8980.684154282582</v>
       </c>
       <c r="L574">
-        <v>0.02588268678716215</v>
+        <v>0.02588268678716216</v>
       </c>
       <c r="M574">
         <v>0.02580183276059543</v>
@@ -50032,7 +50032,7 @@
         <v>106</v>
       </c>
       <c r="S574">
-        <v>133483.8156873132</v>
+        <v>133483.8156873131</v>
       </c>
       <c r="T574">
         <v>7780</v>
@@ -50041,7 +50041,7 @@
         <v>761.9</v>
       </c>
       <c r="V574">
-        <v>663.1305267241394</v>
+        <v>664.3803514203776</v>
       </c>
       <c r="W574">
         <v>8589.275315005656</v>
@@ -50050,16 +50050,16 @@
         <v>8589.275315005656</v>
       </c>
       <c r="Y574">
-        <v>374.5144792598931</v>
+        <v>391.4088392769263</v>
       </c>
       <c r="Z574">
-        <v>374.5144792598931</v>
+        <v>391.4088392769263</v>
       </c>
       <c r="AA574">
-        <v>0.04360257012667971</v>
+        <v>0.04556948344560877</v>
       </c>
       <c r="AB574">
-        <v>0.04360257012667971</v>
+        <v>0.04556948344560877</v>
       </c>
     </row>
     <row r="575" spans="1:28">
@@ -50088,16 +50088,16 @@
         <v>74</v>
       </c>
       <c r="I575">
-        <v>6123.574388335145</v>
+        <v>6135.115697611916</v>
       </c>
       <c r="J575">
-        <v>6123.574388335145</v>
+        <v>6135.115697611916</v>
       </c>
       <c r="K575">
-        <v>6123.574388335145</v>
+        <v>6135.115697611916</v>
       </c>
       <c r="L575">
-        <v>0.0176816459944834</v>
+        <v>0.01768164599448339</v>
       </c>
       <c r="M575">
         <v>0.01723940435280622</v>
@@ -50118,7 +50118,7 @@
         <v>106</v>
       </c>
       <c r="S575">
-        <v>82696.55999965468</v>
+        <v>82696.55999965471</v>
       </c>
       <c r="T575">
         <v>5340</v>
@@ -50127,7 +50127,7 @@
         <v>784.0000000000001</v>
       </c>
       <c r="V575">
-        <v>526.791234149254</v>
+        <v>527.7840955357657</v>
       </c>
       <c r="W575">
         <v>5738.894272623074</v>
@@ -50136,16 +50136,16 @@
         <v>5738.894272623074</v>
       </c>
       <c r="Y575">
-        <v>384.6801157120708</v>
+        <v>396.221424988842</v>
       </c>
       <c r="Z575">
-        <v>384.6801157120708</v>
+        <v>396.221424988842</v>
       </c>
       <c r="AA575">
-        <v>0.06703035418288777</v>
+        <v>0.06904142264459967</v>
       </c>
       <c r="AB575">
-        <v>0.06703035418288777</v>
+        <v>0.06904142264459967</v>
       </c>
     </row>
     <row r="576" spans="1:28">
@@ -50174,16 +50174,16 @@
         <v>75</v>
       </c>
       <c r="I576">
-        <v>2526.989141245651</v>
+        <v>2531.751843773397</v>
       </c>
       <c r="J576">
-        <v>2526.989141245651</v>
+        <v>2531.751843773397</v>
       </c>
       <c r="K576">
-        <v>2526.989141245651</v>
+        <v>2531.751843773397</v>
       </c>
       <c r="L576">
-        <v>0.007296608907458215</v>
+        <v>0.007296608907458216</v>
       </c>
       <c r="M576">
         <v>0.0070446735395187</v>
@@ -50213,7 +50213,7 @@
         <v>305.8</v>
       </c>
       <c r="V576">
-        <v>156.9270358347624</v>
+        <v>157.2228015656248</v>
       </c>
       <c r="W576">
         <v>2345.129553264538</v>
@@ -50222,16 +50222,16 @@
         <v>2345.129553264538</v>
       </c>
       <c r="Y576">
-        <v>181.8595879811128</v>
+        <v>186.6222905088589</v>
       </c>
       <c r="Z576">
-        <v>181.8595879811128</v>
+        <v>186.6222905088589</v>
       </c>
       <c r="AA576">
-        <v>0.07754777885424501</v>
+        <v>0.07957866986455878</v>
       </c>
       <c r="AB576">
-        <v>0.07754777885424501</v>
+        <v>0.07957866986455878</v>
       </c>
     </row>
     <row r="577" spans="1:28">
@@ -50260,16 +50260,16 @@
         <v>76</v>
       </c>
       <c r="I577">
-        <v>13684.57208370604</v>
+        <v>13710.36386293865</v>
       </c>
       <c r="J577">
-        <v>13684.57208370604</v>
+        <v>13710.36386293865</v>
       </c>
       <c r="K577">
-        <v>13684.57208370604</v>
+        <v>13710.36386293865</v>
       </c>
       <c r="L577">
-        <v>0.03951381069706659</v>
+        <v>0.0395138106970666</v>
       </c>
       <c r="M577">
         <v>0.03857388316151187</v>
@@ -50290,7 +50290,7 @@
         <v>106</v>
       </c>
       <c r="S577">
-        <v>96264.48604219811</v>
+        <v>96264.4860421981</v>
       </c>
       <c r="T577">
         <v>12260</v>
@@ -50299,7 +50299,7 @@
         <v>98.5</v>
       </c>
       <c r="V577">
-        <v>928.2604718600884</v>
+        <v>930.0099959967673</v>
       </c>
       <c r="W577">
         <v>12841.01426116833</v>
@@ -50308,16 +50308,16 @@
         <v>12841.01426116833</v>
       </c>
       <c r="Y577">
-        <v>843.5578225377067</v>
+        <v>869.3496017703128</v>
       </c>
       <c r="Z577">
-        <v>843.5578225377067</v>
+        <v>869.3496017703128</v>
       </c>
       <c r="AA577">
-        <v>0.06569246053161505</v>
+        <v>0.06770100741958178</v>
       </c>
       <c r="AB577">
-        <v>0.06569246053161505</v>
+        <v>0.06770100741958178</v>
       </c>
     </row>
     <row r="578" spans="1:28">
@@ -50346,16 +50346,16 @@
         <v>77</v>
       </c>
       <c r="I578">
-        <v>314.2632395388192</v>
+        <v>314.8555421731674</v>
       </c>
       <c r="J578">
-        <v>314.2632395388192</v>
+        <v>314.8555421731674</v>
       </c>
       <c r="K578">
-        <v>314.2632395388192</v>
+        <v>314.8555421731674</v>
       </c>
       <c r="L578">
-        <v>0.0009074261204681263</v>
+        <v>0.0009074261204681262</v>
       </c>
       <c r="M578">
         <v>0.0009163802978235566</v>
@@ -50376,7 +50376,7 @@
         <v>106</v>
       </c>
       <c r="S578">
-        <v>80104.62265309729</v>
+        <v>80104.62265309731</v>
       </c>
       <c r="T578">
         <v>230</v>
@@ -50385,7 +50385,7 @@
         <v>25.5</v>
       </c>
       <c r="V578">
-        <v>34.35789300699123</v>
+        <v>34.42264849849752</v>
       </c>
       <c r="W578">
         <v>305.057502863675</v>
@@ -50394,16 +50394,16 @@
         <v>305.057502863675</v>
       </c>
       <c r="Y578">
-        <v>9.20573667514418</v>
+        <v>9.798039309492367</v>
       </c>
       <c r="Z578">
-        <v>9.20573667514418</v>
+        <v>9.798039309492367</v>
       </c>
       <c r="AA578">
-        <v>0.03017705379715924</v>
+        <v>0.03211866358806111</v>
       </c>
       <c r="AB578">
-        <v>0.03017705379715924</v>
+        <v>0.03211866358806111</v>
       </c>
     </row>
     <row r="579" spans="1:28">
@@ -50432,13 +50432,13 @@
         <v>78</v>
       </c>
       <c r="I579">
-        <v>42.23575861076368</v>
+        <v>42.31536178396829</v>
       </c>
       <c r="J579">
-        <v>42.23575861076368</v>
+        <v>42.31536178396829</v>
       </c>
       <c r="K579">
-        <v>42.23575861076368</v>
+        <v>42.31536178396829</v>
       </c>
       <c r="L579">
         <v>0.0001219545456141693</v>
@@ -50471,7 +50471,7 @@
         <v>31.5</v>
       </c>
       <c r="V579">
-        <v>1.507138370137701</v>
+        <v>1.509978925171341</v>
       </c>
       <c r="W579">
         <v>38.13218785794481</v>
@@ -50480,16 +50480,16 @@
         <v>38.13218785794481</v>
       </c>
       <c r="Y579">
-        <v>4.103570752818868</v>
+        <v>4.183173926023478</v>
       </c>
       <c r="Z579">
-        <v>4.103570752818868</v>
+        <v>4.183173926023478</v>
       </c>
       <c r="AA579">
-        <v>0.1076143537345941</v>
+        <v>0.1097019122429378</v>
       </c>
       <c r="AB579">
-        <v>0.1076143537345941</v>
+        <v>0.1097019122429378</v>
       </c>
     </row>
     <row r="580" spans="1:28">
@@ -50518,16 +50518,16 @@
         <v>79</v>
       </c>
       <c r="I580">
-        <v>190.0609137485046</v>
+        <v>190.4191280279254</v>
       </c>
       <c r="J580">
-        <v>190.0609137485046</v>
+        <v>190.4191280279254</v>
       </c>
       <c r="K580">
-        <v>190.0609137485046</v>
+        <v>190.4191280279254</v>
       </c>
       <c r="L580">
-        <v>0.0005487954552639583</v>
+        <v>0.0005487954552639582</v>
       </c>
       <c r="M580">
         <v>0.0005154639175257037</v>
@@ -50557,7 +50557,7 @@
         <v>30.1</v>
       </c>
       <c r="V580">
-        <v>15.48702984000279</v>
+        <v>15.5162187727775</v>
       </c>
       <c r="W580">
         <v>171.5948453608016</v>
@@ -50566,16 +50566,16 @@
         <v>171.5948453608016</v>
       </c>
       <c r="Y580">
-        <v>18.46606838770296</v>
+        <v>18.82428266712384</v>
       </c>
       <c r="Z580">
-        <v>18.46606838770296</v>
+        <v>18.82428266712384</v>
       </c>
       <c r="AA580">
-        <v>0.107614353734668</v>
+        <v>0.1097019122430118</v>
       </c>
       <c r="AB580">
-        <v>0.107614353734668</v>
+        <v>0.1097019122430118</v>
       </c>
     </row>
     <row r="581" spans="1:28">
@@ -50604,16 +50604,16 @@
         <v>80</v>
       </c>
       <c r="I581">
-        <v>95.03045687424594</v>
+        <v>95.20956401395638</v>
       </c>
       <c r="J581">
-        <v>95.03045687424594</v>
+        <v>95.20956401395638</v>
       </c>
       <c r="K581">
-        <v>95.03045687424594</v>
+        <v>95.20956401395638</v>
       </c>
       <c r="L581">
-        <v>0.0002743977276319608</v>
+        <v>0.0002743977276319609</v>
       </c>
       <c r="M581">
         <v>0.0002577319587628519</v>
@@ -50634,7 +50634,7 @@
         <v>106</v>
       </c>
       <c r="S581">
-        <v>93600</v>
+        <v>93599.99999999999</v>
       </c>
       <c r="T581">
         <v>110</v>
@@ -50643,7 +50643,7 @@
         <v>189.1</v>
       </c>
       <c r="V581">
-        <v>5.172711790250546</v>
+        <v>5.182460976393302</v>
       </c>
       <c r="W581">
         <v>85.7974226804008</v>
@@ -50652,16 +50652,16 @@
         <v>85.7974226804008</v>
       </c>
       <c r="Y581">
-        <v>9.233034193845143</v>
+        <v>9.412141333555581</v>
       </c>
       <c r="Z581">
-        <v>9.233034193845143</v>
+        <v>9.412141333555581</v>
       </c>
       <c r="AA581">
-        <v>0.1076143537345941</v>
+        <v>0.1097019122429379</v>
       </c>
       <c r="AB581">
-        <v>0.1076143537345941</v>
+        <v>0.1097019122429379</v>
       </c>
     </row>
     <row r="582" spans="1:28">
@@ -50690,13 +50690,13 @@
         <v>81</v>
       </c>
       <c r="I582">
-        <v>116.9912148746524</v>
+        <v>117.2117122031581</v>
       </c>
       <c r="J582">
-        <v>116.9912148746524</v>
+        <v>117.2117122031581</v>
       </c>
       <c r="K582">
-        <v>116.9912148746524</v>
+        <v>117.2117122031581</v>
       </c>
       <c r="L582">
         <v>0.0003378087885759395</v>
@@ -50729,7 +50729,7 @@
         <v>161</v>
       </c>
       <c r="V582">
-        <v>14.89450070759058</v>
+        <v>14.92257288052227</v>
       </c>
       <c r="W582">
         <v>123.9296105383623</v>
@@ -50738,16 +50738,16 @@
         <v>123.9296105383623</v>
       </c>
       <c r="Y582">
-        <v>-6.938395663709841</v>
+        <v>-6.717898335204154</v>
       </c>
       <c r="Z582">
-        <v>-6.938395663709841</v>
+        <v>-6.717898335204154</v>
       </c>
       <c r="AA582">
-        <v>-0.05598658491355517</v>
+        <v>-0.05420737066808289</v>
       </c>
       <c r="AB582">
-        <v>-0.05598658491355517</v>
+        <v>-0.05420737066808289</v>
       </c>
     </row>
     <row r="583" spans="1:28">
@@ -50776,13 +50776,13 @@
         <v>83</v>
       </c>
       <c r="I583">
-        <v>447.7199312647016</v>
+        <v>448.5637642727474</v>
       </c>
       <c r="J583">
-        <v>447.7199312647016</v>
+        <v>448.5637642727474</v>
       </c>
       <c r="K583">
-        <v>447.7199312647016</v>
+        <v>448.5637642727474</v>
       </c>
       <c r="L583">
         <v>0.001292778502760899</v>
@@ -50815,7 +50815,7 @@
         <v>351.3</v>
       </c>
       <c r="V583">
-        <v>63.63651555805538</v>
+        <v>63.75645346699149</v>
       </c>
       <c r="W583">
         <v>438.5201603665485</v>
@@ -50824,16 +50824,16 @@
         <v>438.5201603665485</v>
       </c>
       <c r="Y583">
-        <v>9.199770898153133</v>
+        <v>10.043603906199</v>
       </c>
       <c r="Z583">
-        <v>9.199770898153133</v>
+        <v>10.043603906199</v>
       </c>
       <c r="AA583">
-        <v>0.02097912873712184</v>
+        <v>0.02290340288529446</v>
       </c>
       <c r="AB583">
-        <v>0.02097912873712184</v>
+        <v>0.02290340288529446</v>
       </c>
     </row>
     <row r="584" spans="1:28">
@@ -50862,16 +50862,16 @@
         <v>84</v>
       </c>
       <c r="I584">
-        <v>1097.133669741201</v>
+        <v>1099.201474947351</v>
       </c>
       <c r="J584">
-        <v>1097.133669741201</v>
+        <v>1099.201474947351</v>
       </c>
       <c r="K584">
-        <v>1097.133669741201</v>
+        <v>1099.201474947351</v>
       </c>
       <c r="L584">
-        <v>0.003167942108116783</v>
+        <v>0.003167942108116782</v>
       </c>
       <c r="M584">
         <v>0.003235967926689523</v>
@@ -50901,7 +50901,7 @@
         <v>171.8</v>
       </c>
       <c r="V584">
-        <v>95.20289845836216</v>
+        <v>95.38233060460117</v>
       </c>
       <c r="W584">
         <v>1077.234306987382</v>
@@ -50910,16 +50910,16 @@
         <v>1077.234306987382</v>
       </c>
       <c r="Y584">
-        <v>19.89936275381888</v>
+        <v>21.96716795996849</v>
       </c>
       <c r="Z584">
-        <v>19.89936275381888</v>
+        <v>21.96716795996849</v>
       </c>
       <c r="AA584">
-        <v>0.01847264111878305</v>
+        <v>0.0203921912043466</v>
       </c>
       <c r="AB584">
-        <v>0.01847264111878305</v>
+        <v>0.0203921912043466</v>
       </c>
     </row>
     <row r="585" spans="1:28">
@@ -50948,13 +50948,13 @@
         <v>85</v>
       </c>
       <c r="I585">
-        <v>5327.151583309342</v>
+        <v>5337.191847391761</v>
       </c>
       <c r="J585">
-        <v>5327.151583309342</v>
+        <v>5337.191847391761</v>
       </c>
       <c r="K585">
-        <v>5327.151583309342</v>
+        <v>5337.191847391761</v>
       </c>
       <c r="L585">
         <v>0.01538199791194769</v>
@@ -50978,7 +50978,7 @@
         <v>105</v>
       </c>
       <c r="S585">
-        <v>49456.0303116584</v>
+        <v>49456.03031165841</v>
       </c>
       <c r="T585">
         <v>6000</v>
@@ -50987,7 +50987,7 @@
         <v>1316.8</v>
       </c>
       <c r="V585">
-        <v>509.6849693581096</v>
+        <v>510.6455899845677</v>
       </c>
       <c r="W585">
         <v>5424.303722794906</v>
@@ -50996,16 +50996,16 @@
         <v>5424.303722794906</v>
       </c>
       <c r="Y585">
-        <v>-97.15213948556448</v>
+        <v>-87.11187540314495</v>
       </c>
       <c r="Z585">
-        <v>-97.15213948556448</v>
+        <v>-87.11187540314495</v>
       </c>
       <c r="AA585">
-        <v>-0.01791052722164057</v>
+        <v>-0.01605954973300426</v>
       </c>
       <c r="AB585">
-        <v>-0.01791052722164057</v>
+        <v>-0.01605954973300426</v>
       </c>
     </row>
     <row r="586" spans="1:28">
@@ -51034,13 +51034,13 @@
         <v>86</v>
       </c>
       <c r="I586">
-        <v>4611.559434013263</v>
+        <v>4620.250997192042</v>
       </c>
       <c r="J586">
-        <v>4611.559434013263</v>
+        <v>4620.250997192042</v>
       </c>
       <c r="K586">
-        <v>4611.559434013263</v>
+        <v>4620.250997192042</v>
       </c>
       <c r="L586">
         <v>0.01331574603716238</v>
@@ -51073,7 +51073,7 @@
         <v>209.7</v>
       </c>
       <c r="V586">
-        <v>424.643129246743</v>
+        <v>425.4434686198107</v>
       </c>
       <c r="W586">
         <v>4242.205899198167</v>
@@ -51082,16 +51082,16 @@
         <v>4242.205899198167</v>
       </c>
       <c r="Y586">
-        <v>369.3535348150963</v>
+        <v>378.0450979938751</v>
       </c>
       <c r="Z586">
-        <v>369.3535348150963</v>
+        <v>378.0450979938751</v>
       </c>
       <c r="AA586">
-        <v>0.08706638564736073</v>
+        <v>0.08911521670019143</v>
       </c>
       <c r="AB586">
-        <v>0.08706638564736073</v>
+        <v>0.08911521670019143</v>
       </c>
     </row>
     <row r="587" spans="1:28">
@@ -51120,13 +51120,13 @@
         <v>87</v>
       </c>
       <c r="I587">
-        <v>9022.255200688029</v>
+        <v>9039.25975244843</v>
       </c>
       <c r="J587">
-        <v>9022.255200688029</v>
+        <v>9039.25975244843</v>
       </c>
       <c r="K587">
-        <v>9022.255200688029</v>
+        <v>9039.25975244843</v>
       </c>
       <c r="L587">
         <v>0.0260515039768831</v>
@@ -51150,7 +51150,7 @@
         <v>105</v>
       </c>
       <c r="S587">
-        <v>62605.9453785056</v>
+        <v>62605.94537850562</v>
       </c>
       <c r="T587">
         <v>8690</v>
@@ -51159,7 +51159,7 @@
         <v>450.5000000000001</v>
       </c>
       <c r="V587">
-        <v>831.9227255098467</v>
+        <v>833.4906786138012</v>
       </c>
       <c r="W587">
         <v>8227.019530355046</v>
@@ -51168,16 +51168,16 @@
         <v>8227.019530355046</v>
       </c>
       <c r="Y587">
-        <v>795.2356703329824</v>
+        <v>812.2402220933836</v>
       </c>
       <c r="Z587">
-        <v>795.2356703329824</v>
+        <v>812.2402220933836</v>
       </c>
       <c r="AA587">
-        <v>0.09666145405378211</v>
+        <v>0.09872836925893751</v>
       </c>
       <c r="AB587">
-        <v>0.09666145405378211</v>
+        <v>0.09872836925893751</v>
       </c>
     </row>
     <row r="588" spans="1:28">
@@ -51206,16 +51206,16 @@
         <v>88</v>
       </c>
       <c r="I588">
-        <v>112285.1104369347</v>
+        <v>112496.738010072</v>
       </c>
       <c r="J588">
-        <v>112285.1104369347</v>
+        <v>112496.738010072</v>
       </c>
       <c r="K588">
-        <v>112285.1104369347</v>
+        <v>112496.738010072</v>
       </c>
       <c r="L588">
-        <v>0.3242200465432953</v>
+        <v>0.3242200465432954</v>
       </c>
       <c r="M588">
         <v>0.3262313860252019</v>
@@ -51236,7 +51236,7 @@
         <v>105</v>
       </c>
       <c r="S588">
-        <v>45779.90475517937</v>
+        <v>45779.90475517936</v>
       </c>
       <c r="T588">
         <v>112020</v>
@@ -51245,7 +51245,7 @@
         <v>647.7000000000002</v>
       </c>
       <c r="V588">
-        <v>11497.68665739803</v>
+        <v>11519.35673916159</v>
       </c>
       <c r="W588">
         <v>108600.4710194736</v>
@@ -51254,16 +51254,16 @@
         <v>108600.4710194736</v>
       </c>
       <c r="Y588">
-        <v>3684.63941746109</v>
+        <v>3896.266990598451</v>
       </c>
       <c r="Z588">
-        <v>3684.63941746109</v>
+        <v>3896.266990598451</v>
       </c>
       <c r="AA588">
-        <v>0.03392839260154207</v>
+        <v>0.03587707266849512</v>
       </c>
       <c r="AB588">
-        <v>0.03392839260154207</v>
+        <v>0.03587707266849512</v>
       </c>
     </row>
     <row r="589" spans="1:28">
@@ -51292,16 +51292,16 @@
         <v>89</v>
       </c>
       <c r="I589">
-        <v>8313.450233394924</v>
+        <v>8329.118876284841</v>
       </c>
       <c r="J589">
-        <v>8313.450233394924</v>
+        <v>8329.118876284841</v>
       </c>
       <c r="K589">
-        <v>8313.450233394924</v>
+        <v>8329.118876284841</v>
       </c>
       <c r="L589">
-        <v>0.0240048498961093</v>
+        <v>0.02400484989610929</v>
       </c>
       <c r="M589">
         <v>0.02462772050400913</v>
@@ -51331,7 +51331,7 @@
         <v>1430.8</v>
       </c>
       <c r="V589">
-        <v>984.9926376072985</v>
+        <v>986.8490867895973</v>
       </c>
       <c r="W589">
         <v>8198.420389461615</v>
@@ -51340,16 +51340,16 @@
         <v>8198.420389461615</v>
       </c>
       <c r="Y589">
-        <v>115.0298439333092</v>
+        <v>130.6984868232266</v>
       </c>
       <c r="Z589">
-        <v>115.0298439333092</v>
+        <v>130.6984868232266</v>
       </c>
       <c r="AA589">
-        <v>0.01403073256418644</v>
+        <v>0.01594191083336354</v>
       </c>
       <c r="AB589">
-        <v>0.01403073256418644</v>
+        <v>0.01594191083336354</v>
       </c>
     </row>
     <row r="590" spans="1:28">
@@ -56968,16 +56968,16 @@
         <v>72</v>
       </c>
       <c r="I655">
-        <v>117202.5096448162</v>
+        <v>117848.0717981594</v>
       </c>
       <c r="J655">
-        <v>117202.5096448162</v>
+        <v>117848.0717981594</v>
       </c>
       <c r="K655">
-        <v>117202.5096448162</v>
+        <v>117848.0717981594</v>
       </c>
       <c r="L655">
-        <v>0.5</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="M655">
         <v>0.5</v>
@@ -56998,7 +56998,7 @@
         <v>105</v>
       </c>
       <c r="S655">
-        <v>56720.79032533331</v>
+        <v>56720.7903253333</v>
       </c>
       <c r="T655">
         <v>100620</v>
@@ -57007,7 +57007,7 @@
         <v>9805.299999999999</v>
       </c>
       <c r="V655">
-        <v>13313.70556435575</v>
+        <v>13387.03867351144</v>
       </c>
       <c r="W655">
         <v>116571</v>
@@ -57016,16 +57016,16 @@
         <v>116571</v>
       </c>
       <c r="Y655">
-        <v>631.5096448161639</v>
+        <v>1277.071798159421</v>
       </c>
       <c r="Z655">
-        <v>631.5096448161639</v>
+        <v>1277.071798159421</v>
       </c>
       <c r="AA655">
-        <v>0.0054173820660041</v>
+        <v>0.0109553130552146</v>
       </c>
       <c r="AB655">
-        <v>0.0054173820660041</v>
+        <v>0.0109553130552146</v>
       </c>
     </row>
     <row r="656" spans="1:28">
@@ -57054,13 +57054,13 @@
         <v>73</v>
       </c>
       <c r="I656">
-        <v>9079.560347730112</v>
+        <v>9129.571397384712</v>
       </c>
       <c r="J656">
-        <v>9079.560347730112</v>
+        <v>9129.571397384712</v>
       </c>
       <c r="K656">
-        <v>9079.560347730112</v>
+        <v>9129.571397384712</v>
       </c>
       <c r="L656">
         <v>0.0387344962801814</v>
@@ -57093,7 +57093,7 @@
         <v>808.6999999999999</v>
       </c>
       <c r="V656">
-        <v>712.2263333626904</v>
+        <v>716.1493412131775</v>
       </c>
       <c r="W656">
         <v>8843.898121387236</v>
@@ -57102,16 +57102,16 @@
         <v>8843.898121387236</v>
       </c>
       <c r="Y656">
-        <v>235.6622263428762</v>
+        <v>285.6732759974766</v>
       </c>
       <c r="Z656">
-        <v>235.6622263428762</v>
+        <v>285.6732759974766</v>
       </c>
       <c r="AA656">
-        <v>0.02664687257906932</v>
+        <v>0.03230173754564537</v>
       </c>
       <c r="AB656">
-        <v>0.02664687257906932</v>
+        <v>0.03230173754564537</v>
       </c>
     </row>
     <row r="657" spans="1:28">
@@ -57140,13 +57140,13 @@
         <v>74</v>
       </c>
       <c r="I657">
-        <v>5310.678843574451</v>
+        <v>5339.930548852452</v>
       </c>
       <c r="J657">
-        <v>5310.678843574451</v>
+        <v>5339.930548852452</v>
       </c>
       <c r="K657">
-        <v>5310.678843574451</v>
+        <v>5339.930548852452</v>
       </c>
       <c r="L657">
         <v>0.02265599456730294</v>
@@ -57170,7 +57170,7 @@
         <v>106</v>
       </c>
       <c r="S657">
-        <v>81417.76716217355</v>
+        <v>81417.76716217356</v>
       </c>
       <c r="T657">
         <v>3620</v>
@@ -57179,7 +57179,7 @@
         <v>742.2</v>
       </c>
       <c r="V657">
-        <v>459.2908148763381</v>
+        <v>461.8206307340436</v>
       </c>
       <c r="W657">
         <v>5095.769869942166</v>
@@ -57188,16 +57188,16 @@
         <v>5095.769869942166</v>
       </c>
       <c r="Y657">
-        <v>214.9089736322849</v>
+        <v>244.1606789102862</v>
       </c>
       <c r="Z657">
-        <v>214.9089736322849</v>
+        <v>244.1606789102862</v>
       </c>
       <c r="AA657">
-        <v>0.04217399512092251</v>
+        <v>0.04791438490001065</v>
       </c>
       <c r="AB657">
-        <v>0.04217399512092251</v>
+        <v>0.04791438490001065</v>
       </c>
     </row>
     <row r="658" spans="1:28">
@@ -57226,16 +57226,16 @@
         <v>75</v>
       </c>
       <c r="I658">
-        <v>1462.910113782804</v>
+        <v>1470.967956623058</v>
       </c>
       <c r="J658">
-        <v>1462.910113782804</v>
+        <v>1470.967956623058</v>
       </c>
       <c r="K658">
-        <v>1462.910113782804</v>
+        <v>1470.967956623058</v>
       </c>
       <c r="L658">
-        <v>0.006240950463501906</v>
+        <v>0.006240950463501907</v>
       </c>
       <c r="M658">
         <v>0.006096459537572039</v>
@@ -57265,7 +57265,7 @@
         <v>260.5</v>
       </c>
       <c r="V658">
-        <v>88.6917940693738</v>
+        <v>89.18031659109127</v>
       </c>
       <c r="W658">
         <v>1421.34076950862</v>
@@ -57274,16 +57274,16 @@
         <v>1421.34076950862</v>
       </c>
       <c r="Y658">
-        <v>41.569344274184</v>
+        <v>49.62718711443767</v>
       </c>
       <c r="Z658">
-        <v>41.569344274184</v>
+        <v>49.62718711443767</v>
       </c>
       <c r="AA658">
-        <v>0.02924657138242448</v>
+        <v>0.0349157557280191</v>
       </c>
       <c r="AB658">
-        <v>0.02924657138242448</v>
+        <v>0.0349157557280191</v>
       </c>
     </row>
     <row r="659" spans="1:28">
@@ -57312,16 +57312,16 @@
         <v>76</v>
       </c>
       <c r="I659">
-        <v>5910.312414743242</v>
+        <v>5942.86695662938</v>
       </c>
       <c r="J659">
-        <v>5910.312414743242</v>
+        <v>5942.86695662938</v>
       </c>
       <c r="K659">
-        <v>5910.312414743242</v>
+        <v>5942.86695662938</v>
       </c>
       <c r="L659">
-        <v>0.02521410348914254</v>
+        <v>0.02521410348914253</v>
       </c>
       <c r="M659">
         <v>0.0236632947976878</v>
@@ -57342,7 +57342,7 @@
         <v>106</v>
       </c>
       <c r="S659">
-        <v>98938.60040063692</v>
+        <v>98938.60040063695</v>
       </c>
       <c r="T659">
         <v>2900</v>
@@ -57351,7 +57351,7 @@
         <v>91.2</v>
       </c>
       <c r="V659">
-        <v>376.1855109277969</v>
+        <v>378.2575751628295</v>
       </c>
       <c r="W659">
         <v>5516.907875722529</v>
@@ -57360,16 +57360,16 @@
         <v>5516.907875722529</v>
       </c>
       <c r="Y659">
-        <v>393.4045390207129</v>
+        <v>425.9590809068513</v>
       </c>
       <c r="Z659">
-        <v>393.4045390207129</v>
+        <v>425.9590809068513</v>
       </c>
       <c r="AA659">
-        <v>0.07130888314302153</v>
+        <v>0.0772097505527161</v>
       </c>
       <c r="AB659">
-        <v>0.07130888314302153</v>
+        <v>0.0772097505527161</v>
       </c>
     </row>
     <row r="660" spans="1:28">
@@ -57398,16 +57398,16 @@
         <v>77</v>
       </c>
       <c r="I660">
-        <v>70.69571310321631</v>
+        <v>71.08511156338032</v>
       </c>
       <c r="J660">
-        <v>70.69571310321631</v>
+        <v>71.08511156338032</v>
       </c>
       <c r="K660">
-        <v>70.69571310321631</v>
+        <v>71.08511156338032</v>
       </c>
       <c r="L660">
-        <v>0.0003015964134106882</v>
+        <v>0.0003015964134106883</v>
       </c>
       <c r="M660">
         <v>0.0002709537572254017</v>
@@ -57437,7 +57437,7 @@
         <v>14.9</v>
       </c>
       <c r="V660">
-        <v>7.515990904301983</v>
+        <v>7.557389670312999</v>
       </c>
       <c r="W660">
         <v>63.17070086704461</v>
@@ -57446,16 +57446,16 @@
         <v>63.17070086704461</v>
       </c>
       <c r="Y660">
-        <v>7.525012236171698</v>
+        <v>7.914410696335715</v>
       </c>
       <c r="Z660">
-        <v>7.525012236171698</v>
+        <v>7.914410696335715</v>
       </c>
       <c r="AA660">
-        <v>0.1191218734775413</v>
+        <v>0.1252860992154128</v>
       </c>
       <c r="AB660">
-        <v>0.1191218734775413</v>
+        <v>0.1252860992154128</v>
       </c>
     </row>
     <row r="661" spans="1:28">
@@ -57484,16 +57484,16 @@
         <v>78</v>
       </c>
       <c r="I661">
-        <v>75.41460108279259</v>
+        <v>75.82999160997556</v>
       </c>
       <c r="J661">
-        <v>75.41460108279259</v>
+        <v>75.82999160997556</v>
       </c>
       <c r="K661">
-        <v>75.41460108279259</v>
+        <v>75.82999160997556</v>
       </c>
       <c r="L661">
-        <v>0.000321727756988044</v>
+        <v>0.0003217277569880439</v>
       </c>
       <c r="M661">
         <v>0.000316112716762952</v>
@@ -57514,7 +57514,7 @@
         <v>107</v>
       </c>
       <c r="S661">
-        <v>104849.7850486042</v>
+        <v>104849.7850486043</v>
       </c>
       <c r="T661">
         <v>30</v>
@@ -57523,7 +57523,7 @@
         <v>36.2</v>
       </c>
       <c r="V661">
-        <v>5.084655518849393</v>
+        <v>5.112662266961737</v>
       </c>
       <c r="W661">
         <v>73.69915101154815</v>
@@ -57532,16 +57532,16 @@
         <v>73.69915101154815</v>
       </c>
       <c r="Y661">
-        <v>1.715450071244433</v>
+        <v>2.130840598427412</v>
       </c>
       <c r="Z661">
-        <v>1.715450071244433</v>
+        <v>2.130840598427412</v>
       </c>
       <c r="AA661">
-        <v>0.02327638850243518</v>
+        <v>0.02891268853413961</v>
       </c>
       <c r="AB661">
-        <v>0.02327638850243518</v>
+        <v>0.02891268853413961</v>
       </c>
     </row>
     <row r="662" spans="1:28">
@@ -57570,13 +57570,13 @@
         <v>79</v>
       </c>
       <c r="I662">
-        <v>131.124017760193</v>
+        <v>131.846260854789</v>
       </c>
       <c r="J662">
-        <v>131.124017760193</v>
+        <v>131.846260854789</v>
       </c>
       <c r="K662">
-        <v>131.124017760193</v>
+        <v>131.846260854789</v>
       </c>
       <c r="L662">
         <v>0.0005593908277116512</v>
@@ -57600,7 +57600,7 @@
         <v>106</v>
       </c>
       <c r="S662">
-        <v>68870.07700872347</v>
+        <v>68870.07700872349</v>
       </c>
       <c r="T662">
         <v>80</v>
@@ -57609,7 +57609,7 @@
         <v>22.5</v>
       </c>
       <c r="V662">
-        <v>10.08547214602345</v>
+        <v>10.1410238499571</v>
       </c>
       <c r="W662">
         <v>126.3414017341009</v>
@@ -57618,16 +57618,16 @@
         <v>126.3414017341009</v>
       </c>
       <c r="Y662">
-        <v>4.782616026092143</v>
+        <v>5.50485912068811</v>
       </c>
       <c r="Z662">
-        <v>4.782616026092143</v>
+        <v>5.50485912068811</v>
       </c>
       <c r="AA662">
-        <v>0.03785470131285765</v>
+        <v>0.04357130002620741</v>
       </c>
       <c r="AB662">
-        <v>0.03785470131285765</v>
+        <v>0.04357130002620741</v>
       </c>
     </row>
     <row r="663" spans="1:28">
@@ -57656,16 +57656,16 @@
         <v>82</v>
       </c>
       <c r="I663">
-        <v>1738.686908893129</v>
+        <v>1748.263755568993</v>
       </c>
       <c r="J663">
-        <v>1738.686908893129</v>
+        <v>1748.263755568993</v>
       </c>
       <c r="K663">
-        <v>1738.686908893129</v>
+        <v>1748.263755568993</v>
       </c>
       <c r="L663">
-        <v>0.007417447434198483</v>
+        <v>0.007417447434198484</v>
       </c>
       <c r="M663">
         <v>0.008038294797687851</v>
@@ -57695,7 +57695,7 @@
         <v>1236.2</v>
       </c>
       <c r="V663">
-        <v>375.2886217071746</v>
+        <v>377.3557457942672</v>
       </c>
       <c r="W663">
         <v>1874.064125722541</v>
@@ -57704,16 +57704,16 @@
         <v>1874.064125722541</v>
       </c>
       <c r="Y663">
-        <v>-135.3772168294115</v>
+        <v>-125.8003701535483</v>
       </c>
       <c r="Z663">
-        <v>-135.3772168294115</v>
+        <v>-125.8003701535483</v>
       </c>
       <c r="AA663">
-        <v>-0.07223723829472332</v>
+        <v>-0.06712703606395876</v>
       </c>
       <c r="AB663">
-        <v>-0.07223723829472332</v>
+        <v>-0.06712703606395876</v>
       </c>
     </row>
     <row r="664" spans="1:28">
@@ -57742,13 +57742,13 @@
         <v>83</v>
       </c>
       <c r="I664">
-        <v>250.7943627781239</v>
+        <v>252.1757610892355</v>
       </c>
       <c r="J664">
-        <v>250.7943627781239</v>
+        <v>252.1757610892355</v>
       </c>
       <c r="K664">
-        <v>250.7943627781239</v>
+        <v>252.1757610892355</v>
       </c>
       <c r="L664">
         <v>0.001069918910175898</v>
@@ -57781,7 +57781,7 @@
         <v>509.5</v>
       </c>
       <c r="V664">
-        <v>34.89669774741029</v>
+        <v>35.08891195349392</v>
       </c>
       <c r="W664">
         <v>252.6828034682017</v>
@@ -57790,16 +57790,16 @@
         <v>252.6828034682017</v>
       </c>
       <c r="Y664">
-        <v>-1.888440690077886</v>
+        <v>-0.507042378966247</v>
       </c>
       <c r="Z664">
-        <v>-1.888440690077886</v>
+        <v>-0.507042378966247</v>
       </c>
       <c r="AA664">
-        <v>-0.007473562364189662</v>
+        <v>-0.002006635877102949</v>
       </c>
       <c r="AB664">
-        <v>-0.007473562364189662</v>
+        <v>-0.002006635877102949</v>
       </c>
     </row>
     <row r="665" spans="1:28">
@@ -57828,13 +57828,13 @@
         <v>84</v>
       </c>
       <c r="I665">
-        <v>41371.23520833544</v>
+        <v>41599.11175951597</v>
       </c>
       <c r="J665">
-        <v>41371.23520833544</v>
+        <v>41599.11175951597</v>
       </c>
       <c r="K665">
-        <v>41371.23520833544</v>
+        <v>41599.11175951597</v>
       </c>
       <c r="L665">
         <v>0.1764946643792507</v>
@@ -57867,7 +57867,7 @@
         <v>1594.4</v>
       </c>
       <c r="V665">
-        <v>5611.200417312408</v>
+        <v>5642.107422932155</v>
       </c>
       <c r="W665">
         <v>42671.80843569389</v>
@@ -57876,16 +57876,16 @@
         <v>42671.80843569389</v>
       </c>
       <c r="Y665">
-        <v>-1300.573227358444</v>
+        <v>-1072.696676177919</v>
       </c>
       <c r="Z665">
-        <v>-1300.573227358444</v>
+        <v>-1072.696676177919</v>
       </c>
       <c r="AA665">
-        <v>-0.03047851204427856</v>
+        <v>-0.02513829892619772</v>
       </c>
       <c r="AB665">
-        <v>-0.03047851204427856</v>
+        <v>-0.02513829892619772</v>
       </c>
     </row>
     <row r="666" spans="1:28">
@@ -57914,13 +57914,13 @@
         <v>85</v>
       </c>
       <c r="I666">
-        <v>9341.241811541766</v>
+        <v>9392.694226656713</v>
       </c>
       <c r="J666">
-        <v>9341.241811541766</v>
+        <v>9392.694226656713</v>
       </c>
       <c r="K666">
-        <v>9341.241811541766</v>
+        <v>9392.694226656713</v>
       </c>
       <c r="L666">
         <v>0.03985086087256377</v>
@@ -57944,7 +57944,7 @@
         <v>105</v>
       </c>
       <c r="S666">
-        <v>46851.19465993322</v>
+        <v>46851.19465993323</v>
       </c>
       <c r="T666">
         <v>10940</v>
@@ -57953,7 +57953,7 @@
         <v>1538.1</v>
       </c>
       <c r="V666">
-        <v>973.4617694973942</v>
+        <v>978.8236860469505</v>
       </c>
       <c r="W666">
         <v>9612.474981936368</v>
@@ -57962,16 +57962,16 @@
         <v>9612.474981936368</v>
       </c>
       <c r="Y666">
-        <v>-271.233170394602</v>
+        <v>-219.7807552796548</v>
       </c>
       <c r="Z666">
-        <v>-271.233170394602</v>
+        <v>-219.7807552796548</v>
       </c>
       <c r="AA666">
-        <v>-0.02821678817414866</v>
+        <v>-0.02286411727392413</v>
       </c>
       <c r="AB666">
-        <v>-0.02821678817414866</v>
+        <v>-0.02286411727392413</v>
       </c>
     </row>
     <row r="667" spans="1:28">
@@ -58000,13 +58000,13 @@
         <v>86</v>
       </c>
       <c r="I667">
-        <v>403.8590241409386</v>
+        <v>406.0835166203372</v>
       </c>
       <c r="J667">
-        <v>403.8590241409386</v>
+        <v>406.0835166203372</v>
       </c>
       <c r="K667">
-        <v>403.8590241409386</v>
+        <v>406.0835166203372</v>
       </c>
       <c r="L667">
         <v>0.00172291116190617</v>
@@ -58030,7 +58030,7 @@
         <v>105</v>
       </c>
       <c r="S667">
-        <v>61549.01875824793</v>
+        <v>61549.01875824791</v>
       </c>
       <c r="T667">
         <v>50</v>
@@ -58039,7 +58039,7 @@
         <v>370.7</v>
       </c>
       <c r="V667">
-        <v>34.68172184700216</v>
+        <v>34.87275194614467</v>
       </c>
       <c r="W667">
         <v>389.5526553468061</v>
@@ -58048,16 +58048,16 @@
         <v>389.5526553468061</v>
       </c>
       <c r="Y667">
-        <v>14.30636879413248</v>
+        <v>16.530861273531</v>
       </c>
       <c r="Z667">
-        <v>14.30636879413248</v>
+        <v>16.530861273531</v>
       </c>
       <c r="AA667">
-        <v>0.03672512200281624</v>
+        <v>0.0424354988899103</v>
       </c>
       <c r="AB667">
-        <v>0.03672512200281624</v>
+        <v>0.0424354988899103</v>
       </c>
     </row>
     <row r="668" spans="1:28">
@@ -58086,13 +58086,13 @@
         <v>87</v>
       </c>
       <c r="I668">
-        <v>13200.97613212086</v>
+        <v>13273.68831724309</v>
       </c>
       <c r="J668">
-        <v>13200.97613212086</v>
+        <v>13273.68831724309</v>
       </c>
       <c r="K668">
-        <v>13200.97613212086</v>
+        <v>13273.68831724309</v>
       </c>
       <c r="L668">
         <v>0.0563169516255522</v>
@@ -58125,7 +58125,7 @@
         <v>421.5</v>
       </c>
       <c r="V668">
-        <v>1315.581499166034</v>
+        <v>1322.827842508629</v>
       </c>
       <c r="W668">
         <v>12528.85567196534</v>
@@ -58134,16 +58134,16 @@
         <v>12528.85567196534</v>
       </c>
       <c r="Y668">
-        <v>672.1204601555128</v>
+        <v>744.8326452777492</v>
       </c>
       <c r="Z668">
-        <v>672.1204601555128</v>
+        <v>744.8326452777492</v>
       </c>
       <c r="AA668">
-        <v>0.05364579796856103</v>
+        <v>0.05944937548800982</v>
       </c>
       <c r="AB668">
-        <v>0.05364579796856103</v>
+        <v>0.05944937548800982</v>
       </c>
     </row>
     <row r="669" spans="1:28">
@@ -58172,13 +58172,13 @@
         <v>88</v>
       </c>
       <c r="I669">
-        <v>7787.247690551758</v>
+        <v>7830.140563775758</v>
       </c>
       <c r="J669">
-        <v>7787.247690551758</v>
+        <v>7830.140563775758</v>
       </c>
       <c r="K669">
-        <v>7787.247690551758</v>
+        <v>7830.140563775758</v>
       </c>
       <c r="L669">
         <v>0.03322133508126712</v>
@@ -58202,7 +58202,7 @@
         <v>105</v>
       </c>
       <c r="S669">
-        <v>48299.29137843974</v>
+        <v>48299.29137843973</v>
       </c>
       <c r="T669">
         <v>7080</v>
@@ -58211,7 +58211,7 @@
         <v>607.1000000000001</v>
       </c>
       <c r="V669">
-        <v>789.0950143267563</v>
+        <v>793.4414219095371</v>
       </c>
       <c r="W669">
         <v>7633.12635476871</v>
@@ -58220,16 +58220,16 @@
         <v>7633.12635476871</v>
       </c>
       <c r="Y669">
-        <v>154.1213357830475</v>
+        <v>197.0142090070476</v>
       </c>
       <c r="Z669">
-        <v>154.1213357830475</v>
+        <v>197.0142090070476</v>
       </c>
       <c r="AA669">
-        <v>0.02019111549054365</v>
+        <v>0.02581042155603322</v>
       </c>
       <c r="AB669">
-        <v>0.02019111549054365</v>
+        <v>0.02581042155603322</v>
       </c>
     </row>
     <row r="670" spans="1:28">
@@ -58258,16 +58258,16 @@
         <v>89</v>
       </c>
       <c r="I670">
-        <v>21067.77245467734</v>
+        <v>21183.81567417155</v>
       </c>
       <c r="J670">
-        <v>21067.77245467734</v>
+        <v>21183.81567417155</v>
       </c>
       <c r="K670">
-        <v>21067.77245467734</v>
+        <v>21183.81567417155</v>
       </c>
       <c r="L670">
-        <v>0.08987765073684649</v>
+        <v>0.08987765073684646</v>
       </c>
       <c r="M670">
         <v>0.08778901734104071</v>
@@ -58288,7 +58288,7 @@
         <v>105</v>
       </c>
       <c r="S670">
-        <v>44800.04252012866</v>
+        <v>44800.04252012869</v>
       </c>
       <c r="T670">
         <v>14660</v>
@@ -58297,7 +58297,7 @@
         <v>1551.6</v>
       </c>
       <c r="V670">
-        <v>2520.419250946196</v>
+        <v>2534.301950931884</v>
       </c>
       <c r="W670">
         <v>20467.30708092491</v>
@@ -58306,16 +58306,16 @@
         <v>20467.30708092491</v>
       </c>
       <c r="Y670">
-        <v>600.4653737524277</v>
+        <v>716.5085932466427</v>
       </c>
       <c r="Z670">
-        <v>600.4653737524277</v>
+        <v>716.5085932466427</v>
       </c>
       <c r="AA670">
-        <v>0.0293377810465378</v>
+        <v>0.03500746778331251</v>
       </c>
       <c r="AB670">
-        <v>0.0293377810465378</v>
+        <v>0.03500746778331251</v>
       </c>
     </row>
     <row r="671" spans="1:28">
@@ -62816,13 +62816,13 @@
         <v>72</v>
       </c>
       <c r="I723">
-        <v>73517.83418432807</v>
+        <v>73378.95941994213</v>
       </c>
       <c r="J723">
-        <v>73517.83418432807</v>
+        <v>73378.95941994213</v>
       </c>
       <c r="K723">
-        <v>73517.83418432807</v>
+        <v>73378.95941994213</v>
       </c>
       <c r="L723">
         <v>0.5</v>
@@ -62855,7 +62855,7 @@
         <v>6510.3</v>
       </c>
       <c r="V723">
-        <v>7787.469577130457</v>
+        <v>7772.759092053121</v>
       </c>
       <c r="W723">
         <v>72444</v>
@@ -62864,16 +62864,16 @@
         <v>72444</v>
       </c>
       <c r="Y723">
-        <v>1073.834184328065</v>
+        <v>934.9594199421263</v>
       </c>
       <c r="Z723">
-        <v>1073.834184328065</v>
+        <v>934.9594199421263</v>
       </c>
       <c r="AA723">
-        <v>0.01482295544597296</v>
+        <v>0.01290596074129157</v>
       </c>
       <c r="AB723">
-        <v>0.01482295544597296</v>
+        <v>0.01290596074129157</v>
       </c>
     </row>
     <row r="724" spans="1:28">
@@ -62902,16 +62902,16 @@
         <v>73</v>
       </c>
       <c r="I724">
-        <v>4451.049470630633</v>
+        <v>4442.641463874693</v>
       </c>
       <c r="J724">
-        <v>4451.049470630633</v>
+        <v>4442.641463874693</v>
       </c>
       <c r="K724">
-        <v>4451.049470630633</v>
+        <v>4442.641463874693</v>
       </c>
       <c r="L724">
-        <v>0.03027190286557347</v>
+        <v>0.03027190286557348</v>
       </c>
       <c r="M724">
         <v>0.03046203177379395</v>
@@ -62932,7 +62932,7 @@
         <v>106</v>
       </c>
       <c r="S724">
-        <v>114882.3061921342</v>
+        <v>114882.3061921341</v>
       </c>
       <c r="T724">
         <v>2970</v>
@@ -62941,7 +62941,7 @@
         <v>539</v>
       </c>
       <c r="V724">
-        <v>357.4499713612042</v>
+        <v>356.7747504287149</v>
       </c>
       <c r="W724">
         <v>4413.582859641458</v>
@@ -62950,16 +62950,16 @@
         <v>4413.582859641458</v>
       </c>
       <c r="Y724">
-        <v>37.46661098917502</v>
+        <v>29.0586042332352</v>
       </c>
       <c r="Z724">
-        <v>37.46661098917502</v>
+        <v>29.0586042332352</v>
       </c>
       <c r="AA724">
-        <v>0.00848893340867711</v>
+        <v>0.006583903635060747</v>
       </c>
       <c r="AB724">
-        <v>0.00848893340867711</v>
+        <v>0.006583903635060747</v>
       </c>
     </row>
     <row r="725" spans="1:28">
@@ -62988,13 +62988,13 @@
         <v>74</v>
       </c>
       <c r="I725">
-        <v>1683.666281362207</v>
+        <v>1680.485845475828</v>
       </c>
       <c r="J725">
-        <v>1683.666281362207</v>
+        <v>1680.485845475828</v>
       </c>
       <c r="K725">
-        <v>1683.666281362207</v>
+        <v>1680.485845475828</v>
       </c>
       <c r="L725">
         <v>0.01145073368960261</v>
@@ -63027,7 +63027,7 @@
         <v>362.3</v>
       </c>
       <c r="V725">
-        <v>137.4925182393594</v>
+        <v>137.2327956660931</v>
       </c>
       <c r="W725">
         <v>1657.733275032783</v>
@@ -63036,16 +63036,16 @@
         <v>1657.733275032783</v>
       </c>
       <c r="Y725">
-        <v>25.93300632942396</v>
+        <v>22.75257044304476</v>
       </c>
       <c r="Z725">
-        <v>25.93300632942396</v>
+        <v>22.75257044304476</v>
       </c>
       <c r="AA725">
-        <v>0.0156436543320946</v>
+        <v>0.01372510933195499</v>
       </c>
       <c r="AB725">
-        <v>0.0156436543320946</v>
+        <v>0.01372510933195499</v>
       </c>
     </row>
     <row r="726" spans="1:28">
@@ -63074,13 +63074,13 @@
         <v>75</v>
       </c>
       <c r="I726">
-        <v>158.6247885268963</v>
+        <v>158.3251472170448</v>
       </c>
       <c r="J726">
-        <v>158.6247885268963</v>
+        <v>158.3251472170448</v>
       </c>
       <c r="K726">
-        <v>158.6247885268963</v>
+        <v>158.3251472170448</v>
       </c>
       <c r="L726">
         <v>0.001078818427438867</v>
@@ -63113,7 +63113,7 @@
         <v>55.09999999999999</v>
       </c>
       <c r="V726">
-        <v>8.492057628174809</v>
+        <v>8.476016180336346</v>
       </c>
       <c r="W726">
         <v>158.382160034969</v>
@@ -63122,16 +63122,16 @@
         <v>158.382160034969</v>
       </c>
       <c r="Y726">
-        <v>0.2426284919272632</v>
+        <v>-0.05701281792428858</v>
       </c>
       <c r="Z726">
-        <v>0.2426284919272632</v>
+        <v>-0.05701281792428858</v>
       </c>
       <c r="AA726">
-        <v>0.001531918063711806</v>
+        <v>-0.0003599699480781218</v>
       </c>
       <c r="AB726">
-        <v>0.001531918063711806</v>
+        <v>-0.0003599699480781218</v>
       </c>
     </row>
     <row r="727" spans="1:28">
@@ -63160,13 +63160,13 @@
         <v>78</v>
       </c>
       <c r="I727">
-        <v>52.87492950896797</v>
+        <v>52.77504907235078</v>
       </c>
       <c r="J727">
-        <v>52.87492950896797</v>
+        <v>52.77504907235078</v>
       </c>
       <c r="K727">
-        <v>52.87492950896797</v>
+        <v>52.77504907235078</v>
       </c>
       <c r="L727">
         <v>0.0003596061424796394</v>
@@ -63199,7 +63199,7 @@
         <v>4.7</v>
       </c>
       <c r="V727">
-        <v>4.872787621414695</v>
+        <v>4.863582953726445</v>
       </c>
       <c r="W727">
         <v>52.79405334498968</v>
@@ -63208,16 +63208,16 @@
         <v>52.79405334498968</v>
       </c>
       <c r="Y727">
-        <v>0.08087616397828157</v>
+        <v>-0.01900427263890947</v>
       </c>
       <c r="Z727">
-        <v>0.08087616397828157</v>
+        <v>-0.01900427263890947</v>
       </c>
       <c r="AA727">
-        <v>0.001531918063759675</v>
+        <v>-0.000359969948030388</v>
       </c>
       <c r="AB727">
-        <v>0.001531918063759675</v>
+        <v>-0.000359969948030388</v>
       </c>
     </row>
     <row r="728" spans="1:28">
@@ -63246,13 +63246,13 @@
         <v>79</v>
       </c>
       <c r="I728">
-        <v>55.27924242994914</v>
+        <v>55.17482026010332</v>
       </c>
       <c r="J728">
-        <v>55.27924242994914</v>
+        <v>55.17482026010332</v>
       </c>
       <c r="K728">
-        <v>55.27924242994914</v>
+        <v>55.17482026010332</v>
       </c>
       <c r="L728">
         <v>0.0003759580450326509</v>
@@ -63276,7 +63276,7 @@
         <v>105</v>
       </c>
       <c r="S728">
-        <v>42520</v>
+        <v>42520.00000000001</v>
       </c>
       <c r="T728">
         <v>0</v>
@@ -63285,7 +63285,7 @@
         <v>12.7</v>
       </c>
       <c r="V728">
-        <v>4.60056604757768</v>
+        <v>4.591875604870984</v>
       </c>
       <c r="W728">
         <v>52.79405334498968</v>
@@ -63294,16 +63294,16 @@
         <v>52.79405334498968</v>
       </c>
       <c r="Y728">
-        <v>2.485189084959451</v>
+        <v>2.380766915113639</v>
       </c>
       <c r="Z728">
-        <v>2.485189084959451</v>
+        <v>2.380766915113639</v>
       </c>
       <c r="AA728">
-        <v>0.04707327677076917</v>
+        <v>0.04509536139527315</v>
       </c>
       <c r="AB728">
-        <v>0.04707327677076917</v>
+        <v>0.04509536139527315</v>
       </c>
     </row>
     <row r="729" spans="1:28">
@@ -63332,13 +63332,13 @@
         <v>83</v>
       </c>
       <c r="I729">
-        <v>355.6094750775002</v>
+        <v>354.9377308318662</v>
       </c>
       <c r="J729">
-        <v>355.6094750775002</v>
+        <v>354.9377308318662</v>
       </c>
       <c r="K729">
-        <v>355.6094750775002</v>
+        <v>354.9377308318662</v>
       </c>
       <c r="L729">
         <v>0.002418525239643867</v>
@@ -63371,7 +63371,7 @@
         <v>351.3</v>
       </c>
       <c r="V729">
-        <v>50.54442814157866</v>
+        <v>50.44895000859145</v>
       </c>
       <c r="W729">
         <v>348.4407520769551</v>
@@ -63380,16 +63380,16 @@
         <v>348.4407520769551</v>
       </c>
       <c r="Y729">
-        <v>7.168723000545185</v>
+        <v>6.496978754911197</v>
       </c>
       <c r="Z729">
-        <v>7.168723000545185</v>
+        <v>6.496978754911197</v>
       </c>
       <c r="AA729">
-        <v>0.02057372152314128</v>
+        <v>0.0186458636545369</v>
       </c>
       <c r="AB729">
-        <v>0.02057372152314128</v>
+        <v>0.0186458636545369</v>
       </c>
     </row>
     <row r="730" spans="1:28">
@@ -63418,13 +63418,13 @@
         <v>84</v>
       </c>
       <c r="I730">
-        <v>14748.19257112902</v>
+        <v>14720.33332049741</v>
       </c>
       <c r="J730">
-        <v>14748.19257112902</v>
+        <v>14720.33332049741</v>
       </c>
       <c r="K730">
-        <v>14748.19257112902</v>
+        <v>14720.33332049741</v>
       </c>
       <c r="L730">
         <v>0.1003035027810498</v>
@@ -63457,7 +63457,7 @@
         <v>1575.5</v>
       </c>
       <c r="V730">
-        <v>1848.602746265573</v>
+        <v>1845.110746349102</v>
       </c>
       <c r="W730">
         <v>14497.24704853521</v>
@@ -63466,16 +63466,16 @@
         <v>14497.24704853521</v>
       </c>
       <c r="Y730">
-        <v>250.9455225938054</v>
+        <v>223.0862719622</v>
       </c>
       <c r="Z730">
-        <v>250.9455225938054</v>
+        <v>223.0862719622</v>
       </c>
       <c r="AA730">
-        <v>0.01730987419567778</v>
+        <v>0.01538818171583415</v>
       </c>
       <c r="AB730">
-        <v>0.01730987419567778</v>
+        <v>0.01538818171583415</v>
       </c>
     </row>
     <row r="731" spans="1:28">
@@ -63504,13 +63504,13 @@
         <v>85</v>
       </c>
       <c r="I731">
-        <v>8047.716476426571</v>
+        <v>8032.514386458763</v>
       </c>
       <c r="J731">
-        <v>8047.716476426571</v>
+        <v>8032.514386458763</v>
       </c>
       <c r="K731">
-        <v>8047.716476426571</v>
+        <v>8032.514386458763</v>
       </c>
       <c r="L731">
         <v>0.05473309004349123</v>
@@ -63534,7 +63534,7 @@
         <v>105</v>
       </c>
       <c r="S731">
-        <v>45654.35794260444</v>
+        <v>45654.35794260445</v>
       </c>
       <c r="T731">
         <v>6780</v>
@@ -63543,7 +63543,7 @@
         <v>1455.2</v>
       </c>
       <c r="V731">
-        <v>883.1983222717786</v>
+        <v>881.5299657393484</v>
       </c>
       <c r="W731">
         <v>8330.90161783994</v>
@@ -63552,16 +63552,16 @@
         <v>8330.90161783994</v>
       </c>
       <c r="Y731">
-        <v>-283.1851414133689</v>
+        <v>-298.3872313811771</v>
       </c>
       <c r="Z731">
-        <v>-283.1851414133689</v>
+        <v>-298.3872313811771</v>
       </c>
       <c r="AA731">
-        <v>-0.03399213607407765</v>
+        <v>-0.03581691935266711</v>
       </c>
       <c r="AB731">
-        <v>-0.03399213607407765</v>
+        <v>-0.03581691935266711</v>
       </c>
     </row>
     <row r="732" spans="1:28">
@@ -63590,13 +63590,13 @@
         <v>87</v>
       </c>
       <c r="I732">
-        <v>27706.78941145763</v>
+        <v>27654.4514461993</v>
       </c>
       <c r="J732">
-        <v>27706.78941145763</v>
+        <v>27654.4514461993</v>
       </c>
       <c r="K732">
-        <v>27706.78941145763</v>
+        <v>27654.4514461993</v>
       </c>
       <c r="L732">
         <v>0.1884358381803632</v>
@@ -63629,7 +63629,7 @@
         <v>376.1000000000001</v>
       </c>
       <c r="V732">
-        <v>2379.980834871013</v>
+        <v>2375.485064812593</v>
       </c>
       <c r="W732">
         <v>27009.43769129869</v>
@@ -63638,16 +63638,16 @@
         <v>27009.43769129869</v>
       </c>
       <c r="Y732">
-        <v>697.351720158942</v>
+        <v>645.013754900614</v>
       </c>
       <c r="Z732">
-        <v>697.351720158942</v>
+        <v>645.013754900614</v>
       </c>
       <c r="AA732">
-        <v>0.02581881667175913</v>
+        <v>0.02388105084869688</v>
       </c>
       <c r="AB732">
-        <v>0.02581881667175913</v>
+        <v>0.02388105084869688</v>
       </c>
     </row>
     <row r="733" spans="1:28">
@@ -63676,16 +63676,16 @@
         <v>88</v>
       </c>
       <c r="I733">
-        <v>1084.362673216778</v>
+        <v>1082.314318386652</v>
       </c>
       <c r="J733">
-        <v>1084.362673216778</v>
+        <v>1082.314318386652</v>
       </c>
       <c r="K733">
-        <v>1084.362673216778</v>
+        <v>1082.314318386652</v>
       </c>
       <c r="L733">
-        <v>0.007374827382006406</v>
+        <v>0.007374827382006405</v>
       </c>
       <c r="M733">
         <v>0.007360443084098373</v>
@@ -63706,7 +63706,7 @@
         <v>105</v>
       </c>
       <c r="S733">
-        <v>48881.49169144663</v>
+        <v>48881.49169144664</v>
       </c>
       <c r="T733">
         <v>960</v>
@@ -63715,7 +63715,7 @@
         <v>314.9</v>
       </c>
       <c r="V733">
-        <v>104.2828230421292</v>
+        <v>104.0858333913845</v>
       </c>
       <c r="W733">
         <v>1066.439877568845</v>
@@ -63724,16 +63724,16 @@
         <v>1066.439877568845</v>
       </c>
       <c r="Y733">
-        <v>17.9227956479333</v>
+        <v>15.874440817807</v>
       </c>
       <c r="Z733">
-        <v>17.9227956479333</v>
+        <v>15.874440817807</v>
       </c>
       <c r="AA733">
-        <v>0.01680619416519922</v>
+        <v>0.01488545313402556</v>
       </c>
       <c r="AB733">
-        <v>0.01680619416519922</v>
+        <v>0.01488545313402556</v>
       </c>
     </row>
     <row r="734" spans="1:28">
@@ -63762,13 +63762,13 @@
         <v>89</v>
       </c>
       <c r="I734">
-        <v>15173.66886456191</v>
+        <v>15145.00589166812</v>
       </c>
       <c r="J734">
-        <v>15173.66886456191</v>
+        <v>15145.00589166812</v>
       </c>
       <c r="K734">
-        <v>15173.66886456191</v>
+        <v>15145.00589166812</v>
       </c>
       <c r="L734">
         <v>0.1031971972033183</v>
@@ -63801,7 +63801,7 @@
         <v>1463.5</v>
       </c>
       <c r="V734">
-        <v>2007.952521640655</v>
+        <v>2004.159510918361</v>
       </c>
       <c r="W734">
         <v>14856.24661128118</v>
@@ -63810,16 +63810,16 @@
         <v>14856.24661128118</v>
       </c>
       <c r="Y734">
-        <v>317.422253280738</v>
+        <v>288.7592803869393</v>
       </c>
       <c r="Z734">
-        <v>317.422253280738</v>
+        <v>288.7592803869393</v>
       </c>
       <c r="AA734">
-        <v>0.02136624825813686</v>
+        <v>0.01943689331110512</v>
       </c>
       <c r="AB734">
-        <v>0.02136624825813686</v>
+        <v>0.01943689331110512</v>
       </c>
     </row>
     <row r="735" spans="1:28">
@@ -67718,13 +67718,13 @@
         <v>72</v>
       </c>
       <c r="I780">
-        <v>40127.20459683537</v>
+        <v>40346.86608507662</v>
       </c>
       <c r="J780">
-        <v>40127.20459683537</v>
+        <v>40346.86608507662</v>
       </c>
       <c r="K780">
-        <v>40127.20459683537</v>
+        <v>40346.86608507662</v>
       </c>
       <c r="L780">
         <v>0.5</v>
@@ -67748,7 +67748,7 @@
         <v>107</v>
       </c>
       <c r="S780">
-        <v>58896.13676266556</v>
+        <v>58896.13676266558</v>
       </c>
       <c r="T780">
         <v>45070</v>
@@ -67757,7 +67757,7 @@
         <v>5282.5</v>
       </c>
       <c r="V780">
-        <v>4105.585041497729</v>
+        <v>4128.059543008048</v>
       </c>
       <c r="W780">
         <v>45204.99999999999</v>
@@ -67766,16 +67766,16 @@
         <v>45204.99999999999</v>
       </c>
       <c r="Y780">
-        <v>-5077.795403164622</v>
+        <v>-4858.133914923368</v>
       </c>
       <c r="Z780">
-        <v>-5077.795403164622</v>
+        <v>-4858.133914923368</v>
       </c>
       <c r="AA780">
-        <v>-0.1123281805810115</v>
+        <v>-0.1074689506674786</v>
       </c>
       <c r="AB780">
-        <v>-0.1123281805810115</v>
+        <v>-0.1074689506674786</v>
       </c>
     </row>
     <row r="781" spans="1:28">
@@ -67804,16 +67804,16 @@
         <v>73</v>
       </c>
       <c r="I781">
-        <v>2157.23114658908</v>
+        <v>2169.040107838714</v>
       </c>
       <c r="J781">
-        <v>2157.23114658908</v>
+        <v>2169.040107838714</v>
       </c>
       <c r="K781">
-        <v>2157.23114658908</v>
+        <v>2169.040107838714</v>
       </c>
       <c r="L781">
-        <v>0.02687990813543002</v>
+        <v>0.02687990813543003</v>
       </c>
       <c r="M781">
         <v>0.02629897785349225</v>
@@ -67834,7 +67834,7 @@
         <v>106</v>
       </c>
       <c r="S781">
-        <v>112677.318459448</v>
+        <v>112677.3184594481</v>
       </c>
       <c r="T781">
         <v>1820</v>
@@ -67843,7 +67843,7 @@
         <v>654.2</v>
       </c>
       <c r="V781">
-        <v>176.0178916654137</v>
+        <v>176.9814362838037</v>
       </c>
       <c r="W781">
         <v>2377.690587734235</v>
@@ -67852,16 +67852,16 @@
         <v>2377.690587734235</v>
       </c>
       <c r="Y781">
-        <v>-220.4594411451544</v>
+        <v>-208.6504798955207</v>
       </c>
       <c r="Z781">
-        <v>-220.4594411451544</v>
+        <v>-208.6504798955207</v>
       </c>
       <c r="AA781">
-        <v>-0.09271998731981193</v>
+        <v>-0.08775341962990624</v>
       </c>
       <c r="AB781">
-        <v>-0.09271998731981193</v>
+        <v>-0.08775341962990624</v>
       </c>
     </row>
     <row r="782" spans="1:28">
@@ -67890,16 +67890,16 @@
         <v>74</v>
       </c>
       <c r="I782">
-        <v>2063.677994828457</v>
+        <v>2074.974834071291</v>
       </c>
       <c r="J782">
-        <v>2063.677994828457</v>
+        <v>2074.974834071291</v>
       </c>
       <c r="K782">
-        <v>2063.677994828457</v>
+        <v>2074.974834071291</v>
       </c>
       <c r="L782">
-        <v>0.02571420082164419</v>
+        <v>0.0257142008216442</v>
       </c>
       <c r="M782">
         <v>0.0248083475298125</v>
@@ -67920,7 +67920,7 @@
         <v>106</v>
       </c>
       <c r="S782">
-        <v>80048.69266138092</v>
+        <v>80048.69266138093</v>
       </c>
       <c r="T782">
         <v>440</v>
@@ -67929,7 +67929,7 @@
         <v>583.2</v>
       </c>
       <c r="V782">
-        <v>190.5721010776114</v>
+        <v>191.615317313593</v>
       </c>
       <c r="W782">
         <v>2242.922700170348</v>
@@ -67938,16 +67938,16 @@
         <v>2242.922700170348</v>
       </c>
       <c r="Y782">
-        <v>-179.2447053418909</v>
+        <v>-167.9478660990571</v>
       </c>
       <c r="Z782">
-        <v>-179.2447053418909</v>
+        <v>-167.9478660990571</v>
       </c>
       <c r="AA782">
-        <v>-0.07991568560444702</v>
+        <v>-0.07487902551715296</v>
       </c>
       <c r="AB782">
-        <v>-0.07991568560444702</v>
+        <v>-0.07487902551715296</v>
       </c>
     </row>
     <row r="783" spans="1:28">
@@ -67976,13 +67976,13 @@
         <v>75</v>
       </c>
       <c r="I783">
-        <v>155.417248463851</v>
+        <v>156.2680225070202</v>
       </c>
       <c r="J783">
-        <v>155.417248463851</v>
+        <v>156.2680225070202</v>
       </c>
       <c r="K783">
-        <v>155.417248463851</v>
+        <v>156.2680225070202</v>
       </c>
       <c r="L783">
         <v>0.00193655713156889</v>
@@ -68015,7 +68015,7 @@
         <v>170.3</v>
       </c>
       <c r="V783">
-        <v>8.864752491077894</v>
+        <v>8.913279288412642</v>
       </c>
       <c r="W783">
         <v>173.2729982964196</v>
@@ -68024,16 +68024,16 @@
         <v>173.2729982964196</v>
       </c>
       <c r="Y783">
-        <v>-17.85574983256868</v>
+        <v>-17.0049757893994</v>
       </c>
       <c r="Z783">
-        <v>-17.85574983256868</v>
+        <v>-17.0049757893994</v>
       </c>
       <c r="AA783">
-        <v>-0.1030498116159027</v>
+        <v>-0.09813979071516286</v>
       </c>
       <c r="AB783">
-        <v>-0.1030498116159027</v>
+        <v>-0.09813979071516286</v>
       </c>
     </row>
     <row r="784" spans="1:28">
@@ -68062,13 +68062,13 @@
         <v>77</v>
       </c>
       <c r="I784">
-        <v>135.6709496842324</v>
+        <v>136.4136299436267</v>
       </c>
       <c r="J784">
-        <v>135.6709496842324</v>
+        <v>136.4136299436267</v>
       </c>
       <c r="K784">
-        <v>135.6709496842324</v>
+        <v>136.4136299436267</v>
       </c>
       <c r="L784">
         <v>0.001690510852267692</v>
@@ -68101,7 +68101,7 @@
         <v>14.9</v>
       </c>
       <c r="V784">
-        <v>14.42381127574073</v>
+        <v>14.50276907713191</v>
       </c>
       <c r="W784">
         <v>144.3941652470164</v>
@@ -68110,16 +68110,16 @@
         <v>144.3941652470164</v>
       </c>
       <c r="Y784">
-        <v>-8.723215562783992</v>
+        <v>-7.980535303389729</v>
       </c>
       <c r="Z784">
-        <v>-8.723215562783992</v>
+        <v>-7.980535303389729</v>
       </c>
       <c r="AA784">
-        <v>-0.0604125211559699</v>
+        <v>-0.05526909823355643</v>
       </c>
       <c r="AB784">
-        <v>-0.0604125211559699</v>
+        <v>-0.05526909823355643</v>
       </c>
     </row>
     <row r="785" spans="1:28">
@@ -68148,16 +68148,16 @@
         <v>83</v>
       </c>
       <c r="I785">
-        <v>68.18473505858157</v>
+        <v>68.55798708370483</v>
       </c>
       <c r="J785">
-        <v>68.18473505858157</v>
+        <v>68.55798708370483</v>
       </c>
       <c r="K785">
-        <v>68.18473505858157</v>
+        <v>68.55798708370483</v>
       </c>
       <c r="L785">
-        <v>0.0008496073392558094</v>
+        <v>0.0008496073392558096</v>
       </c>
       <c r="M785">
         <v>0.0008517887563884018</v>
@@ -68187,7 +68187,7 @@
         <v>351.3</v>
       </c>
       <c r="V785">
-        <v>9.691413426962171</v>
+        <v>9.744465472772903</v>
       </c>
       <c r="W785">
         <v>77.0102214650754</v>
@@ -68196,16 +68196,16 @@
         <v>77.0102214650754</v>
       </c>
       <c r="Y785">
-        <v>-8.825486406493837</v>
+        <v>-8.452234381370573</v>
       </c>
       <c r="Z785">
-        <v>-8.825486406493837</v>
+        <v>-8.452234381370573</v>
       </c>
       <c r="AA785">
-        <v>-0.1146014936536217</v>
+        <v>-0.109754708148758</v>
       </c>
       <c r="AB785">
-        <v>-0.1146014936536217</v>
+        <v>-0.109754708148758</v>
       </c>
     </row>
     <row r="786" spans="1:28">
@@ -68234,13 +68234,13 @@
         <v>84</v>
       </c>
       <c r="I786">
-        <v>428.3681909808013</v>
+        <v>430.7131336522746</v>
       </c>
       <c r="J786">
-        <v>428.3681909808013</v>
+        <v>430.7131336522746</v>
       </c>
       <c r="K786">
-        <v>428.3681909808013</v>
+        <v>430.7131336522746</v>
       </c>
       <c r="L786">
         <v>0.005337628116444779</v>
@@ -68273,7 +68273,7 @@
         <v>237.8</v>
       </c>
       <c r="V786">
-        <v>41.17077049813971</v>
+        <v>41.39614460058527</v>
       </c>
       <c r="W786">
         <v>490.9401618398603</v>
@@ -68282,16 +68282,16 @@
         <v>490.9401618398603</v>
       </c>
       <c r="Y786">
-        <v>-62.57197085905898</v>
+        <v>-60.22702818758569</v>
       </c>
       <c r="Z786">
-        <v>-62.57197085905898</v>
+        <v>-60.22702818758569</v>
       </c>
       <c r="AA786">
-        <v>-0.1274533552613879</v>
+        <v>-0.1226769225028918</v>
       </c>
       <c r="AB786">
-        <v>-0.1274533552613879</v>
+        <v>-0.1226769225028918</v>
       </c>
     </row>
     <row r="787" spans="1:28">
@@ -68320,16 +68320,16 @@
         <v>85</v>
       </c>
       <c r="I787">
-        <v>3953.149193330207</v>
+        <v>3974.789241366724</v>
       </c>
       <c r="J787">
-        <v>3953.149193330207</v>
+        <v>3974.789241366724</v>
       </c>
       <c r="K787">
-        <v>3953.149193330207</v>
+        <v>3974.789241366724</v>
       </c>
       <c r="L787">
-        <v>0.04925771970721793</v>
+        <v>0.04925771970721794</v>
       </c>
       <c r="M787">
         <v>0.05163969335604755</v>
@@ -68359,7 +68359,7 @@
         <v>1302.2</v>
       </c>
       <c r="V787">
-        <v>385.3983238854635</v>
+        <v>387.5080439679097</v>
       </c>
       <c r="W787">
         <v>4668.744676320259</v>
@@ -68368,16 +68368,16 @@
         <v>4668.744676320259</v>
       </c>
       <c r="Y787">
-        <v>-715.595482990052</v>
+        <v>-693.9554349535351</v>
       </c>
       <c r="Z787">
-        <v>-715.595482990052</v>
+        <v>-693.9554349535351</v>
       </c>
       <c r="AA787">
-        <v>-0.1532736383335615</v>
+        <v>-0.1486385491314737</v>
       </c>
       <c r="AB787">
-        <v>-0.1532736383335615</v>
+        <v>-0.1486385491314737</v>
       </c>
     </row>
     <row r="788" spans="1:28">
@@ -68406,16 +68406,16 @@
         <v>86</v>
       </c>
       <c r="I788">
-        <v>239.5356685671678</v>
+        <v>240.846917680406</v>
       </c>
       <c r="J788">
-        <v>239.5356685671678</v>
+        <v>240.846917680406</v>
       </c>
       <c r="K788">
-        <v>239.5356685671678</v>
+        <v>240.846917680406</v>
       </c>
       <c r="L788">
-        <v>0.002984704154872262</v>
+        <v>0.002984704154872263</v>
       </c>
       <c r="M788">
         <v>0.002981260647359406</v>
@@ -68445,7 +68445,7 @@
         <v>248.8</v>
       </c>
       <c r="V788">
-        <v>20.36787724881155</v>
+        <v>20.47937363321561</v>
       </c>
       <c r="W788">
         <v>269.5357751277639</v>
@@ -68454,16 +68454,16 @@
         <v>269.5357751277639</v>
       </c>
       <c r="Y788">
-        <v>-30.00010656059618</v>
+        <v>-28.68885744735795</v>
       </c>
       <c r="Z788">
-        <v>-30.00010656059618</v>
+        <v>-28.68885744735795</v>
       </c>
       <c r="AA788">
-        <v>-0.1113028745307583</v>
+        <v>-0.1064380319597983</v>
       </c>
       <c r="AB788">
-        <v>-0.1113028745307583</v>
+        <v>-0.1064380319597983</v>
       </c>
     </row>
     <row r="789" spans="1:28">
@@ -68492,13 +68492,13 @@
         <v>87</v>
       </c>
       <c r="I789">
-        <v>2131.815477335485</v>
+        <v>2143.485309936886</v>
       </c>
       <c r="J789">
-        <v>2131.815477335485</v>
+        <v>2143.485309936886</v>
       </c>
       <c r="K789">
-        <v>2131.815477335485</v>
+        <v>2143.485309936886</v>
       </c>
       <c r="L789">
         <v>0.02656321937640792</v>
@@ -68522,7 +68522,7 @@
         <v>105</v>
       </c>
       <c r="S789">
-        <v>60244.21636625826</v>
+        <v>60244.21636625828</v>
       </c>
       <c r="T789">
         <v>1970</v>
@@ -68531,7 +68531,7 @@
         <v>260.2</v>
       </c>
       <c r="V789">
-        <v>178.025100747606</v>
+        <v>178.9996330871352</v>
       </c>
       <c r="W789">
         <v>2396.943143100508</v>
@@ -68540,16 +68540,16 @@
         <v>2396.943143100508</v>
       </c>
       <c r="Y789">
-        <v>-265.1276657650233</v>
+        <v>-253.4578331636217</v>
       </c>
       <c r="Z789">
-        <v>-265.1276657650233</v>
+        <v>-253.4578331636217</v>
       </c>
       <c r="AA789">
-        <v>-0.1106107445761412</v>
+        <v>-0.1057421131966307</v>
       </c>
       <c r="AB789">
-        <v>-0.1106107445761412</v>
+        <v>-0.1057421131966307</v>
       </c>
     </row>
     <row r="790" spans="1:28">
@@ -68578,13 +68578,13 @@
         <v>89</v>
       </c>
       <c r="I790">
-        <v>28794.15399199751</v>
+        <v>28951.77690099598</v>
       </c>
       <c r="J790">
-        <v>28794.15399199751</v>
+        <v>28951.77690099598</v>
       </c>
       <c r="K790">
-        <v>28794.15399199751</v>
+        <v>28951.77690099598</v>
       </c>
       <c r="L790">
         <v>0.3587859443648905</v>
@@ -68608,7 +68608,7 @@
         <v>107</v>
       </c>
       <c r="S790">
-        <v>54325.30273433256</v>
+        <v>54325.30273433257</v>
       </c>
       <c r="T790">
         <v>35090</v>
@@ -68617,7 +68617,7 @@
         <v>1459.6</v>
       </c>
       <c r="V790">
-        <v>3081.052999180902</v>
+        <v>3097.919080283487</v>
       </c>
       <c r="W790">
         <v>32363.54557069852</v>
@@ -68626,16 +68626,16 @@
         <v>32363.54557069852</v>
       </c>
       <c r="Y790">
-        <v>-3569.391578701008</v>
+        <v>-3411.768669702535</v>
       </c>
       <c r="Z790">
-        <v>-3569.391578701008</v>
+        <v>-3411.768669702535</v>
       </c>
       <c r="AA790">
-        <v>-0.1102904986384645</v>
+        <v>-0.1054201141914284</v>
       </c>
       <c r="AB790">
-        <v>-0.1102904986384645</v>
+        <v>-0.1054201141914284</v>
       </c>
     </row>
     <row r="791" spans="1:28">
